--- a/docs/dosyalar/durunday-villa-mahal-listesi.xlsx
+++ b/docs/dosyalar/durunday-villa-mahal-listesi.xlsx
@@ -12,12 +12,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mahal Listesi" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="İmalat Tanımları" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Yönetmelik Uygunluk" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tasarım Kontrolü" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Mahal Programı'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Mahal Listesi'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'İmalat Tanımları'!$3:$3</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Yönetmelik Uygunluk'!$3:$3</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Tasarım Kontrolü'!$3:$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -28,7 +30,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -130,6 +132,18 @@
       <color rgb="009C6500"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C6500"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -214,7 +228,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -313,6 +327,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -795,7 +815,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Bodrum + Zemin + 1. Normal kat (dubleks) + çatı arası</t>
+          <t>Bodrum + Zemin + 1. kat (dubleks) + kullanılmayan çatı arası · Hmax 6,50 m</t>
         </is>
       </c>
       <c r="C11" s="6" t="n"/>
@@ -808,7 +828,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Bodrum 2.90 m (net 2.55 m) · Zemin 3.20 m (net 2.85 m) · 1. Kat 3.10 m (net 2.75 m)</t>
+          <t>Bodrum 3.06 m (net 2.66 m) · Zemin 3.20 m (net 2.80 m) · 1. Kat 3.00 m (net 2.60 m)</t>
         </is>
       </c>
       <c r="C12" s="6" t="n"/>
@@ -829,12 +849,12 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>Toplam net alan</t>
+          <t>Toplam net kullanım alanı</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>747.5 m² kapalı + 68.5 m² açık teras/balkon</t>
+          <t>725.8 m² (merdiven, asansör, şaft ve galeri boşluğu hariç: 54.0 m²) · teras 80 m², balkon 19 m²</t>
         </is>
       </c>
       <c r="C14" s="6" t="n"/>
@@ -860,7 +880,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>19.09.2026 · R01 (çizimlerle birlikte)</t>
+          <t>21.09.2026 · R1 (yeniden düzenlenen plan kurgusu ile)</t>
         </is>
       </c>
       <c r="C16" s="6" t="n"/>
@@ -931,12 +951,12 @@
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>19 cm gaz beton veya tuğla + 8 cm XPS mantolama (λ ≤ 0,033) + kaplama. TS 825 3. bölge şartını sağlar.</t>
+          <t>25 cm gazbeton (G2/04) + 8 cm taşyünü mantolama (λ ≤ 0,035) + zemin katta doğal taş, 1. katta ince silikon sıva. TS 825 3. bölge şartını sağlar.</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>XPS Dow Styrofoam veya Austrotherm · sistem Baumit openSystem ya da Weber therm</t>
+          <t>Gazbeton Akg / Türk Ytong · taşyünü İzocam veya Knauf Insulation · sistem Baumit ya da Weber therm</t>
         </is>
       </c>
     </row>
@@ -948,12 +968,12 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Doğal taş (traverten/andezit) + ısı yalıtım sıvası, antrasit alüminyum denizlik ve damlalık profilleri.</t>
+          <t>Zemin kat ve baca: 3 cm bej doğal taş (Sille taşı / traverten) mekanik ankrajlı; 1. kat: ince silikon sıva; kat silmesi beyaz GRC; antrasit alüminyum denizlik ve damlalık.</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Taş: bölge ocakları (Afyon/Burdur/Nevşehir) · profil Asaş</t>
+          <t>Taş: Sille (Konya) veya Afyon/Burdur ocakları · ankraj Halfen · sıva Baumit SilikonTop</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1036,7 @@
       </c>
       <c r="B27" s="9" t="inlineStr">
         <is>
-          <t>4 duraklı (bodrum-zemin-1.kat-çatı arası), 4–6 kişilik, makine dairesiz, kuyu su yalıtımlı.</t>
+          <t>3 duraklı (bodrum-zemin-1. kat), 630 kg / 8 kişi, makine dairesiz; kuyu betonarme perde, su yalıtımlı.</t>
         </is>
       </c>
       <c r="C27" s="9" t="inlineStr">
@@ -1145,7 +1165,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1216,21 +1236,21 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>Garaj (3 araçlık)</t>
+          <t>Ev sineması</t>
         </is>
       </c>
       <c r="C5" s="13" t="n">
-        <v>48</v>
+        <v>35.2</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>5.75</v>
+        <v>4.78</v>
       </c>
       <c r="E5" s="14" t="n">
-        <v>8.35</v>
+        <v>7.38</v>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>teknik</t>
+          <t>ikincil</t>
         </is>
       </c>
       <c r="G5" s="9" t="inlineStr"/>
@@ -1243,17 +1263,17 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Hobi ve oyun salonu</t>
+          <t>Oyun ve bar salonu</t>
         </is>
       </c>
       <c r="C6" s="13" t="n">
-        <v>43.8</v>
+        <v>34.3</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>5.25</v>
+        <v>4.65</v>
       </c>
       <c r="E6" s="14" t="n">
-        <v>8.35</v>
+        <v>7.38</v>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
@@ -1270,21 +1290,21 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Ev sineması</t>
+          <t>Misafir / hizmetli odası</t>
         </is>
       </c>
       <c r="C7" s="13" t="n">
-        <v>28</v>
+        <v>20.9</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>3.35</v>
+        <v>4.58</v>
       </c>
       <c r="E7" s="14" t="n">
-        <v>8.35</v>
+        <v>4.58</v>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>yasam</t>
+          <t>yatak</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr"/>
@@ -1297,21 +1317,21 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Kazan dairesi / teknik hacim</t>
+          <t>Oda holü ve dolap</t>
         </is>
       </c>
       <c r="C8" s="13" t="n">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>3.25</v>
+        <v>2.45</v>
       </c>
       <c r="E8" s="14" t="n">
-        <v>3.55</v>
+        <v>2.65</v>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>teknik</t>
+          <t>sirkulasyon</t>
         </is>
       </c>
       <c r="G8" s="9" t="inlineStr"/>
@@ -1324,21 +1344,21 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Merdiven ve hol</t>
+          <t>Oda banyosu</t>
         </is>
       </c>
       <c r="C9" s="13" t="n">
-        <v>17.7</v>
+        <v>5.2</v>
       </c>
       <c r="D9" s="14" t="n">
-        <v>3.25</v>
+        <v>1.98</v>
       </c>
       <c r="E9" s="14" t="n">
-        <v>5.45</v>
+        <v>2.65</v>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>sirkulasyon</t>
+          <t>islak</t>
         </is>
       </c>
       <c r="G9" s="9" t="inlineStr"/>
@@ -1351,21 +1371,21 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Çamaşırhane ve ütü odası</t>
+          <t>Bodrum holü</t>
         </is>
       </c>
       <c r="C10" s="13" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D10" s="14" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="E10" s="14" t="n">
-        <v>3.25</v>
+        <v>9.25</v>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>islak</t>
+          <t>sirkulasyon</t>
         </is>
       </c>
       <c r="G10" s="9" t="inlineStr"/>
@@ -1378,24 +1398,28 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>Depo</t>
+          <t>Merdiven</t>
         </is>
       </c>
       <c r="C11" s="13" t="n">
-        <v>4.7</v>
+        <v>11.4</v>
       </c>
       <c r="D11" s="14" t="n">
-        <v>1.45</v>
+        <v>2.45</v>
       </c>
       <c r="E11" s="14" t="n">
-        <v>3.25</v>
+        <v>4.65</v>
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>teknik</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr"/>
+          <t>merdiven</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>Düşey sirkülasyon / boşluk — net kullanım alanına dahil değil</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="12" t="inlineStr">
@@ -1405,24 +1429,28 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>Kiler / soğuk oda</t>
+          <t>Asansör</t>
         </is>
       </c>
       <c r="C12" s="13" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="D12" s="14" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="E12" s="14" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>teknik</t>
-        </is>
-      </c>
-      <c r="G12" s="9" t="inlineStr"/>
+          <t>asansor</t>
+        </is>
+      </c>
+      <c r="G12" s="9" t="inlineStr">
+        <is>
+          <t>Düşey sirkülasyon / boşluk — net kullanım alanına dahil değil</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -1432,24 +1460,28 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>Su deposu ve hidrofor</t>
+          <t>Tesisat şaftı</t>
         </is>
       </c>
       <c r="C13" s="13" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="D13" s="14" t="n">
-        <v>2.35</v>
+        <v>0.45</v>
       </c>
       <c r="E13" s="14" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>teknik</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr"/>
+          <t>saft</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>Düşey sirkülasyon / boşluk — net kullanım alanına dahil değil</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="12" t="inlineStr">
@@ -1459,17 +1491,17 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>Elektrik panosu / depo</t>
+          <t>Genel depo</t>
         </is>
       </c>
       <c r="C14" s="13" t="n">
-        <v>2.6</v>
+        <v>12.9</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>1.05</v>
+        <v>2.77</v>
       </c>
       <c r="E14" s="14" t="n">
-        <v>2.45</v>
+        <v>4.65</v>
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
@@ -1486,17 +1518,17 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>Asansör ve tesisat şaftı</t>
+          <t>Elektrik ve zayıf akım odası</t>
         </is>
       </c>
       <c r="C15" s="13" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>2.05</v>
+        <v>1.25</v>
       </c>
       <c r="E15" s="14" t="n">
-        <v>2.45</v>
+        <v>2.77</v>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
@@ -1513,21 +1545,21 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>WC + duş</t>
+          <t>Koridor</t>
         </is>
       </c>
       <c r="C16" s="13" t="n">
-        <v>4</v>
+        <v>8.1</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="E16" s="14" t="n">
-        <v>2.45</v>
+        <v>6.45</v>
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>islak</t>
+          <t>sirkulasyon</t>
         </is>
       </c>
       <c r="G16" s="9" t="inlineStr"/>
@@ -1540,21 +1572,21 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>Koridor</t>
+          <t>Isı merkezi (kazan / ısı pompası)</t>
         </is>
       </c>
       <c r="C17" s="13" t="n">
-        <v>3.6</v>
+        <v>13.6</v>
       </c>
       <c r="D17" s="14" t="n">
-        <v>1.45</v>
+        <v>3.25</v>
       </c>
       <c r="E17" s="14" t="n">
-        <v>2.45</v>
+        <v>4.17</v>
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>sirkulasyon</t>
+          <t>teknik</t>
         </is>
       </c>
       <c r="G17" s="9" t="inlineStr"/>
@@ -1567,21 +1599,21 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>Şarap mahzeni ve bar</t>
+          <t>Su deposu ve hidrofor</t>
         </is>
       </c>
       <c r="C18" s="13" t="n">
-        <v>13.1</v>
+        <v>9.1</v>
       </c>
       <c r="D18" s="14" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="E18" s="14" t="n">
-        <v>5.35</v>
+        <v>4.17</v>
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>ikincil</t>
+          <t>teknik</t>
         </is>
       </c>
       <c r="G18" s="9" t="inlineStr"/>
@@ -1594,21 +1626,21 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>Spor salonu (fitness)</t>
+          <t>Kiler ve soğuk depo</t>
         </is>
       </c>
       <c r="C19" s="13" t="n">
-        <v>18.3</v>
+        <v>13.7</v>
       </c>
       <c r="D19" s="14" t="n">
-        <v>3.55</v>
+        <v>2.45</v>
       </c>
       <c r="E19" s="14" t="n">
-        <v>5.15</v>
+        <v>5.57</v>
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>yasam</t>
+          <t>teknik</t>
         </is>
       </c>
       <c r="G19" s="9" t="inlineStr"/>
@@ -1621,21 +1653,21 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>Sauna ve dinlenme</t>
+          <t>Havuz makine dairesi</t>
         </is>
       </c>
       <c r="C20" s="13" t="n">
-        <v>10.4</v>
+        <v>13.7</v>
       </c>
       <c r="D20" s="14" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="E20" s="14" t="n">
-        <v>3.65</v>
+        <v>5.57</v>
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>islak</t>
+          <t>teknik</t>
         </is>
       </c>
       <c r="G20" s="9" t="inlineStr"/>
@@ -1652,13 +1684,13 @@
         </is>
       </c>
       <c r="C21" s="13" t="n">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="D21" s="14" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="E21" s="14" t="n">
-        <v>3.65</v>
+        <v>2.65</v>
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
@@ -1675,21 +1707,21 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>Hizmet / misafir odası</t>
+          <t>Sauna</t>
         </is>
       </c>
       <c r="C22" s="13" t="n">
-        <v>10.4</v>
+        <v>5.8</v>
       </c>
       <c r="D22" s="14" t="n">
-        <v>2.85</v>
+        <v>2.18</v>
       </c>
       <c r="E22" s="14" t="n">
-        <v>3.65</v>
+        <v>2.65</v>
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>yatak</t>
+          <t>islak</t>
         </is>
       </c>
       <c r="G22" s="9" t="inlineStr"/>
@@ -1702,21 +1734,21 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Hizmet banyosu</t>
+          <t>Fitness salonu</t>
         </is>
       </c>
       <c r="C23" s="13" t="n">
-        <v>4.8</v>
+        <v>19.9</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>2.15</v>
+        <v>4.17</v>
       </c>
       <c r="E23" s="14" t="n">
-        <v>2.25</v>
+        <v>4.78</v>
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>islak</t>
+          <t>yasam</t>
         </is>
       </c>
       <c r="G23" s="9" t="inlineStr"/>
@@ -1729,17 +1761,17 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Temizlik deposu</t>
+          <t>Depo</t>
         </is>
       </c>
       <c r="C24" s="13" t="n">
-        <v>2.7</v>
+        <v>5.5</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>1.25</v>
+        <v>2.25</v>
       </c>
       <c r="E24" s="14" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
@@ -1756,28 +1788,24 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>Işıklık / İngiliz bahçesi</t>
+          <t>Şarap mahzeni</t>
         </is>
       </c>
       <c r="C25" s="13" t="n">
-        <v>17.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>3.35</v>
+        <v>1.98</v>
       </c>
       <c r="E25" s="14" t="n">
-        <v>5.15</v>
+        <v>4.65</v>
       </c>
       <c r="F25" s="14" t="inlineStr">
         <is>
-          <t>acik</t>
-        </is>
-      </c>
-      <c r="G25" s="9" t="inlineStr">
-        <is>
-          <t>Açık alan — kapalı alana dahil değil</t>
-        </is>
-      </c>
+          <t>ikincil</t>
+        </is>
+      </c>
+      <c r="G25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="15" t="n"/>
@@ -1787,7 +1815,7 @@
         </is>
       </c>
       <c r="C26" s="17">
-        <f>SUM(C5:C25)</f>
+        <f>SUMIF(G5:G25,"",C5:C25)</f>
         <v/>
       </c>
       <c r="D26" s="15" t="n"/>
@@ -1810,21 +1838,21 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>Salon / oturma alanı</t>
+          <t>Antre / giriş holü</t>
         </is>
       </c>
       <c r="C29" s="13" t="n">
-        <v>61.4</v>
+        <v>16.8</v>
       </c>
       <c r="D29" s="14" t="n">
-        <v>7.35</v>
+        <v>2.77</v>
       </c>
       <c r="E29" s="14" t="n">
-        <v>8.35</v>
+        <v>6.05</v>
       </c>
       <c r="F29" s="14" t="inlineStr">
         <is>
-          <t>yasam</t>
+          <t>sirkulasyon</t>
         </is>
       </c>
       <c r="G29" s="9" t="inlineStr"/>
@@ -1837,21 +1865,21 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>Yemek alanı</t>
+          <t>Hol</t>
         </is>
       </c>
       <c r="C30" s="13" t="n">
-        <v>30.5</v>
+        <v>14</v>
       </c>
       <c r="D30" s="14" t="n">
-        <v>3.65</v>
+        <v>2.05</v>
       </c>
       <c r="E30" s="14" t="n">
-        <v>8.35</v>
+        <v>6.85</v>
       </c>
       <c r="F30" s="14" t="inlineStr">
         <is>
-          <t>yasam</t>
+          <t>sirkulasyon</t>
         </is>
       </c>
       <c r="G30" s="9" t="inlineStr"/>
@@ -1864,24 +1892,28 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>Kapalı veranda</t>
+          <t>Merdiven</t>
         </is>
       </c>
       <c r="C31" s="13" t="n">
-        <v>28</v>
+        <v>11.4</v>
       </c>
       <c r="D31" s="14" t="n">
-        <v>3.35</v>
+        <v>2.45</v>
       </c>
       <c r="E31" s="14" t="n">
-        <v>8.35</v>
+        <v>4.65</v>
       </c>
       <c r="F31" s="14" t="inlineStr">
         <is>
-          <t>yasam</t>
-        </is>
-      </c>
-      <c r="G31" s="9" t="inlineStr"/>
+          <t>merdiven</t>
+        </is>
+      </c>
+      <c r="G31" s="9" t="inlineStr">
+        <is>
+          <t>Düşey sirkülasyon / boşluk — net kullanım alanına dahil değil</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="18" customHeight="1">
       <c r="A32" s="12" t="inlineStr">
@@ -1891,24 +1923,28 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>Antre / giriş holü</t>
+          <t>Asansör</t>
         </is>
       </c>
       <c r="C32" s="13" t="n">
-        <v>11.5</v>
+        <v>3.8</v>
       </c>
       <c r="D32" s="14" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="E32" s="14" t="n">
-        <v>3.55</v>
+        <v>2.05</v>
       </c>
       <c r="F32" s="14" t="inlineStr">
         <is>
-          <t>sirkulasyon</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr"/>
+          <t>asansor</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>Düşey sirkülasyon / boşluk — net kullanım alanına dahil değil</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="12" t="inlineStr">
@@ -1918,24 +1954,28 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>Merdiven, hol ve galeri</t>
+          <t>Tesisat şaftı</t>
         </is>
       </c>
       <c r="C33" s="13" t="n">
-        <v>17.7</v>
+        <v>0.9</v>
       </c>
       <c r="D33" s="14" t="n">
-        <v>3.25</v>
+        <v>0.45</v>
       </c>
       <c r="E33" s="14" t="n">
-        <v>5.45</v>
+        <v>2.05</v>
       </c>
       <c r="F33" s="14" t="inlineStr">
         <is>
-          <t>sirkulasyon</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr"/>
+          <t>saft</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>Düşey sirkülasyon / boşluk — net kullanım alanına dahil değil</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="18" customHeight="1">
       <c r="A34" s="12" t="inlineStr">
@@ -1945,21 +1985,21 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>Mutfak (ankastre)</t>
+          <t>Misafir yatak odası</t>
         </is>
       </c>
       <c r="C34" s="13" t="n">
-        <v>20.2</v>
+        <v>25.7</v>
       </c>
       <c r="D34" s="14" t="n">
-        <v>3.45</v>
+        <v>4.78</v>
       </c>
       <c r="E34" s="14" t="n">
-        <v>5.85</v>
+        <v>5.38</v>
       </c>
       <c r="F34" s="14" t="inlineStr">
         <is>
-          <t>mutfak</t>
+          <t>yatak</t>
         </is>
       </c>
       <c r="G34" s="9" t="inlineStr"/>
@@ -1972,21 +2012,21 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>Kiler / arka mutfak</t>
+          <t>Misafir banyosu</t>
         </is>
       </c>
       <c r="C35" s="13" t="n">
-        <v>10.2</v>
+        <v>5.1</v>
       </c>
       <c r="D35" s="14" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="E35" s="14" t="n">
-        <v>5.85</v>
+        <v>2.77</v>
       </c>
       <c r="F35" s="14" t="inlineStr">
         <is>
-          <t>mutfak</t>
+          <t>islak</t>
         </is>
       </c>
       <c r="G35" s="9" t="inlineStr"/>
@@ -1999,21 +2039,21 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>Misafir WC</t>
+          <t>Misafir süit holü</t>
         </is>
       </c>
       <c r="C36" s="13" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="D36" s="14" t="n">
-        <v>2.35</v>
+        <v>1.85</v>
       </c>
       <c r="E36" s="14" t="n">
-        <v>2.45</v>
+        <v>1.85</v>
       </c>
       <c r="F36" s="14" t="inlineStr">
         <is>
-          <t>islak</t>
+          <t>sirkulasyon</t>
         </is>
       </c>
       <c r="G36" s="9" t="inlineStr"/>
@@ -2026,21 +2066,21 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>Vestiyer</t>
+          <t>Salon (şömineli)</t>
         </is>
       </c>
       <c r="C37" s="13" t="n">
-        <v>2.6</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D37" s="14" t="n">
-        <v>1.05</v>
+        <v>7.38</v>
       </c>
       <c r="E37" s="14" t="n">
-        <v>2.45</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="F37" s="14" t="inlineStr">
         <is>
-          <t>teknik</t>
+          <t>yasam</t>
         </is>
       </c>
       <c r="G37" s="9" t="inlineStr"/>
@@ -2053,21 +2093,21 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>Asansör ve tesisat şaftı</t>
+          <t>Yemek alanı</t>
         </is>
       </c>
       <c r="C38" s="13" t="n">
-        <v>5</v>
+        <v>20.3</v>
       </c>
       <c r="D38" s="14" t="n">
-        <v>2.05</v>
+        <v>4.38</v>
       </c>
       <c r="E38" s="14" t="n">
-        <v>2.45</v>
+        <v>4.65</v>
       </c>
       <c r="F38" s="14" t="inlineStr">
         <is>
-          <t>teknik</t>
+          <t>yasam</t>
         </is>
       </c>
       <c r="G38" s="9" t="inlineStr"/>
@@ -2080,21 +2120,21 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>Koridor</t>
+          <t>Mutfak (adalı)</t>
         </is>
       </c>
       <c r="C39" s="13" t="n">
-        <v>8</v>
+        <v>33.3</v>
       </c>
       <c r="D39" s="14" t="n">
-        <v>2.45</v>
+        <v>4.78</v>
       </c>
       <c r="E39" s="14" t="n">
-        <v>3.25</v>
+        <v>6.97</v>
       </c>
       <c r="F39" s="14" t="inlineStr">
         <is>
-          <t>sirkulasyon</t>
+          <t>mutfak</t>
         </is>
       </c>
       <c r="G39" s="9" t="inlineStr"/>
@@ -2107,21 +2147,21 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>Misafir yatak odası (süit)</t>
+          <t>Servis koridoru</t>
         </is>
       </c>
       <c r="C40" s="13" t="n">
-        <v>18.3</v>
+        <v>8.1</v>
       </c>
       <c r="D40" s="14" t="n">
-        <v>3.55</v>
+        <v>1.25</v>
       </c>
       <c r="E40" s="14" t="n">
-        <v>5.15</v>
+        <v>6.45</v>
       </c>
       <c r="F40" s="14" t="inlineStr">
         <is>
-          <t>yatak</t>
+          <t>sirkulasyon</t>
         </is>
       </c>
       <c r="G40" s="9" t="inlineStr"/>
@@ -2134,21 +2174,21 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Misafir banyosu</t>
+          <t>Garaj (2 araç)</t>
         </is>
       </c>
       <c r="C41" s="13" t="n">
-        <v>5.8</v>
+        <v>31.1</v>
       </c>
       <c r="D41" s="14" t="n">
-        <v>2.05</v>
+        <v>5.57</v>
       </c>
       <c r="E41" s="14" t="n">
-        <v>2.85</v>
+        <v>5.58</v>
       </c>
       <c r="F41" s="14" t="inlineStr">
         <is>
-          <t>islak</t>
+          <t>garaj</t>
         </is>
       </c>
       <c r="G41" s="9" t="inlineStr"/>
@@ -2161,21 +2201,21 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>Misafir giyinme odası</t>
+          <t>Misafir WC</t>
         </is>
       </c>
       <c r="C42" s="13" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="D42" s="14" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="E42" s="14" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="F42" s="14" t="inlineStr">
         <is>
-          <t>teknik</t>
+          <t>islak</t>
         </is>
       </c>
       <c r="G42" s="9" t="inlineStr"/>
@@ -2188,21 +2228,21 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>Çalışma odası / ofis</t>
+          <t>Kiler</t>
         </is>
       </c>
       <c r="C43" s="13" t="n">
-        <v>16.7</v>
+        <v>4.5</v>
       </c>
       <c r="D43" s="14" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="E43" s="14" t="n">
-        <v>5.15</v>
+        <v>2.45</v>
       </c>
       <c r="F43" s="14" t="inlineStr">
         <is>
-          <t>yasam</t>
+          <t>teknik</t>
         </is>
       </c>
       <c r="G43" s="9" t="inlineStr"/>
@@ -2215,28 +2255,24 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>Üstü örtülü teras (barbekü)</t>
+          <t>Arka mutfak / servis girişi</t>
         </is>
       </c>
       <c r="C44" s="13" t="n">
-        <v>27.6</v>
+        <v>10.9</v>
       </c>
       <c r="D44" s="14" t="n">
-        <v>5.15</v>
+        <v>2.97</v>
       </c>
       <c r="E44" s="14" t="n">
-        <v>5.35</v>
+        <v>3.65</v>
       </c>
       <c r="F44" s="14" t="inlineStr">
         <is>
-          <t>acik</t>
-        </is>
-      </c>
-      <c r="G44" s="9" t="inlineStr">
-        <is>
-          <t>Açık alan — kapalı alana dahil değil</t>
-        </is>
-      </c>
+          <t>mutfak</t>
+        </is>
+      </c>
+      <c r="G44" s="9" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="15" t="n"/>
@@ -2246,7 +2282,7 @@
         </is>
       </c>
       <c r="C45" s="17">
-        <f>SUM(C29:C44)</f>
+        <f>SUMIF(G29:G44,"",C29:C44)</f>
         <v/>
       </c>
       <c r="D45" s="15" t="n"/>
@@ -2269,21 +2305,21 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>Ebeveyn yatak odası</t>
+          <t>Üst hol ve okuma köşesi</t>
         </is>
       </c>
       <c r="C48" s="13" t="n">
-        <v>29.6</v>
+        <v>20.8</v>
       </c>
       <c r="D48" s="14" t="n">
-        <v>3.55</v>
+        <v>2.05</v>
       </c>
       <c r="E48" s="14" t="n">
-        <v>8.35</v>
+        <v>6.85</v>
       </c>
       <c r="F48" s="14" t="inlineStr">
         <is>
-          <t>yatak</t>
+          <t>sirkulasyon</t>
         </is>
       </c>
       <c r="G48" s="9" t="inlineStr"/>
@@ -2296,24 +2332,28 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>Ebeveyn giyinme odası</t>
+          <t>Galeri boşluğu</t>
         </is>
       </c>
       <c r="C49" s="13" t="n">
-        <v>15.9</v>
+        <v>5.7</v>
       </c>
       <c r="D49" s="14" t="n">
-        <v>3.65</v>
+        <v>2.05</v>
       </c>
       <c r="E49" s="14" t="n">
-        <v>4.35</v>
+        <v>2.77</v>
       </c>
       <c r="F49" s="14" t="inlineStr">
         <is>
-          <t>teknik</t>
-        </is>
-      </c>
-      <c r="G49" s="9" t="inlineStr"/>
+          <t>bosluk</t>
+        </is>
+      </c>
+      <c r="G49" s="9" t="inlineStr">
+        <is>
+          <t>Düşey sirkülasyon / boşluk — net kullanım alanına dahil değil</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="18" customHeight="1">
       <c r="A50" s="12" t="inlineStr">
@@ -2323,24 +2363,28 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>Ebeveyn banyosu</t>
+          <t>Merdiven</t>
         </is>
       </c>
       <c r="C50" s="13" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="D50" s="14" t="n">
-        <v>3.65</v>
+        <v>2.45</v>
       </c>
       <c r="E50" s="14" t="n">
-        <v>3.85</v>
+        <v>4.65</v>
       </c>
       <c r="F50" s="14" t="inlineStr">
         <is>
-          <t>islak</t>
-        </is>
-      </c>
-      <c r="G50" s="9" t="inlineStr"/>
+          <t>merdiven</t>
+        </is>
+      </c>
+      <c r="G50" s="9" t="inlineStr">
+        <is>
+          <t>Düşey sirkülasyon / boşluk — net kullanım alanına dahil değil</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="18" customHeight="1">
       <c r="A51" s="12" t="inlineStr">
@@ -2350,24 +2394,28 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Aile oturma odası / TV</t>
+          <t>Asansör</t>
         </is>
       </c>
       <c r="C51" s="13" t="n">
-        <v>26</v>
+        <v>3.8</v>
       </c>
       <c r="D51" s="14" t="n">
-        <v>4.95</v>
+        <v>1.85</v>
       </c>
       <c r="E51" s="14" t="n">
-        <v>5.25</v>
+        <v>2.05</v>
       </c>
       <c r="F51" s="14" t="inlineStr">
         <is>
-          <t>yasam</t>
-        </is>
-      </c>
-      <c r="G51" s="9" t="inlineStr"/>
+          <t>asansor</t>
+        </is>
+      </c>
+      <c r="G51" s="9" t="inlineStr">
+        <is>
+          <t>Düşey sirkülasyon / boşluk — net kullanım alanına dahil değil</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="18" customHeight="1">
       <c r="A52" s="12" t="inlineStr">
@@ -2377,24 +2425,28 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Çalışma odası / kütüphane</t>
+          <t>Tesisat şaftı</t>
         </is>
       </c>
       <c r="C52" s="13" t="n">
-        <v>17.1</v>
+        <v>0.9</v>
       </c>
       <c r="D52" s="14" t="n">
-        <v>3.25</v>
+        <v>0.45</v>
       </c>
       <c r="E52" s="14" t="n">
-        <v>5.25</v>
+        <v>2.05</v>
       </c>
       <c r="F52" s="14" t="inlineStr">
         <is>
-          <t>yasam</t>
-        </is>
-      </c>
-      <c r="G52" s="9" t="inlineStr"/>
+          <t>saft</t>
+        </is>
+      </c>
+      <c r="G52" s="9" t="inlineStr">
+        <is>
+          <t>Düşey sirkülasyon / boşluk — net kullanım alanına dahil değil</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="18" customHeight="1">
       <c r="A53" s="12" t="inlineStr">
@@ -2404,28 +2456,24 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Ebeveyn balkonu</t>
+          <t>Yatak odası 2</t>
         </is>
       </c>
       <c r="C53" s="13" t="n">
-        <v>14.6</v>
+        <v>25.7</v>
       </c>
       <c r="D53" s="14" t="n">
-        <v>1.75</v>
+        <v>4.78</v>
       </c>
       <c r="E53" s="14" t="n">
-        <v>8.35</v>
+        <v>5.38</v>
       </c>
       <c r="F53" s="14" t="inlineStr">
         <is>
-          <t>acik</t>
-        </is>
-      </c>
-      <c r="G53" s="9" t="inlineStr">
-        <is>
-          <t>Açık alan — kapalı alana dahil değil</t>
-        </is>
-      </c>
+          <t>yatak</t>
+        </is>
+      </c>
+      <c r="G53" s="9" t="inlineStr"/>
     </row>
     <row r="54" ht="18" customHeight="1">
       <c r="A54" s="12" t="inlineStr">
@@ -2435,21 +2483,21 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Üst hol, merdiven ve galeri</t>
+          <t>Yatak odası 2 banyosu</t>
         </is>
       </c>
       <c r="C54" s="13" t="n">
-        <v>29.7</v>
+        <v>5.1</v>
       </c>
       <c r="D54" s="14" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="E54" s="14" t="n">
-        <v>9.15</v>
+        <v>2.77</v>
       </c>
       <c r="F54" s="14" t="inlineStr">
         <is>
-          <t>sirkulasyon</t>
+          <t>islak</t>
         </is>
       </c>
       <c r="G54" s="9" t="inlineStr"/>
@@ -2462,21 +2510,21 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Çamaşır ve ütü nişi</t>
+          <t>Yatak odası 2 holü</t>
         </is>
       </c>
       <c r="C55" s="13" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="D55" s="14" t="n">
         <v>1.85</v>
       </c>
       <c r="E55" s="14" t="n">
-        <v>3.25</v>
+        <v>1.85</v>
       </c>
       <c r="F55" s="14" t="inlineStr">
         <is>
-          <t>islak</t>
+          <t>sirkulasyon</t>
         </is>
       </c>
       <c r="G55" s="9" t="inlineStr"/>
@@ -2489,21 +2537,21 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>Yatak odası 4</t>
+          <t>Ebeveyn banyosu</t>
         </is>
       </c>
       <c r="C56" s="13" t="n">
-        <v>19.6</v>
+        <v>17.6</v>
       </c>
       <c r="D56" s="14" t="n">
-        <v>3.35</v>
+        <v>3.77</v>
       </c>
       <c r="E56" s="14" t="n">
-        <v>5.85</v>
+        <v>4.65</v>
       </c>
       <c r="F56" s="14" t="inlineStr">
         <is>
-          <t>yatak</t>
+          <t>islak</t>
         </is>
       </c>
       <c r="G56" s="9" t="inlineStr"/>
@@ -2516,21 +2564,21 @@
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>Yatak odası 2</t>
+          <t>Ebeveyn giyinme odası</t>
         </is>
       </c>
       <c r="C57" s="13" t="n">
-        <v>19.3</v>
+        <v>16</v>
       </c>
       <c r="D57" s="14" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="E57" s="14" t="n">
-        <v>5.45</v>
+        <v>4.65</v>
       </c>
       <c r="F57" s="14" t="inlineStr">
         <is>
-          <t>yatak</t>
+          <t>giyinme</t>
         </is>
       </c>
       <c r="G57" s="9" t="inlineStr"/>
@@ -2543,21 +2591,21 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>Yatak odası 2 banyosu</t>
+          <t>Ebeveyn yatak odası</t>
         </is>
       </c>
       <c r="C58" s="13" t="n">
-        <v>7.6</v>
+        <v>33.7</v>
       </c>
       <c r="D58" s="14" t="n">
-        <v>2.15</v>
+        <v>4.58</v>
       </c>
       <c r="E58" s="14" t="n">
-        <v>3.55</v>
+        <v>7.38</v>
       </c>
       <c r="F58" s="14" t="inlineStr">
         <is>
-          <t>islak</t>
+          <t>yatak</t>
         </is>
       </c>
       <c r="G58" s="9" t="inlineStr"/>
@@ -2570,21 +2618,21 @@
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>Asansör ve tesisat şaftı</t>
+          <t>Yatak odası 4</t>
         </is>
       </c>
       <c r="C59" s="13" t="n">
-        <v>5</v>
+        <v>15.2</v>
       </c>
       <c r="D59" s="14" t="n">
-        <v>2.05</v>
+        <v>2.65</v>
       </c>
       <c r="E59" s="14" t="n">
-        <v>2.45</v>
+        <v>4.38</v>
       </c>
       <c r="F59" s="14" t="inlineStr">
         <is>
-          <t>teknik</t>
+          <t>yatak</t>
         </is>
       </c>
       <c r="G59" s="9" t="inlineStr"/>
@@ -2597,21 +2645,21 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Koridor</t>
+          <t>Yatak odası 4 banyosu</t>
         </is>
       </c>
       <c r="C60" s="13" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="D60" s="14" t="n">
-        <v>1.45</v>
+        <v>1.85</v>
       </c>
       <c r="E60" s="14" t="n">
         <v>2.45</v>
       </c>
       <c r="F60" s="14" t="inlineStr">
         <is>
-          <t>sirkulasyon</t>
+          <t>islak</t>
         </is>
       </c>
       <c r="G60" s="9" t="inlineStr"/>
@@ -2624,21 +2672,21 @@
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Ortak banyo</t>
+          <t>Koridor</t>
         </is>
       </c>
       <c r="C61" s="13" t="n">
-        <v>8.9</v>
+        <v>11.7</v>
       </c>
       <c r="D61" s="14" t="n">
-        <v>2.45</v>
+        <v>1.25</v>
       </c>
       <c r="E61" s="14" t="n">
-        <v>3.65</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="F61" s="14" t="inlineStr">
         <is>
-          <t>islak</t>
+          <t>sirkulasyon</t>
         </is>
       </c>
       <c r="G61" s="9" t="inlineStr"/>
@@ -2655,13 +2703,13 @@
         </is>
       </c>
       <c r="C62" s="13" t="n">
-        <v>18.8</v>
+        <v>23.3</v>
       </c>
       <c r="D62" s="14" t="n">
-        <v>3.65</v>
+        <v>4.17</v>
       </c>
       <c r="E62" s="14" t="n">
-        <v>5.15</v>
+        <v>5.57</v>
       </c>
       <c r="F62" s="14" t="inlineStr">
         <is>
@@ -2682,17 +2730,17 @@
         </is>
       </c>
       <c r="C63" s="13" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="D63" s="14" t="n">
-        <v>1.65</v>
+        <v>2.45</v>
       </c>
       <c r="E63" s="14" t="n">
-        <v>5.15</v>
+        <v>2.45</v>
       </c>
       <c r="F63" s="14" t="inlineStr">
         <is>
-          <t>teknik</t>
+          <t>giyinme</t>
         </is>
       </c>
       <c r="G63" s="9" t="inlineStr"/>
@@ -2705,21 +2753,21 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Yatak odası 5</t>
+          <t>Yatak odası 3 banyosu</t>
         </is>
       </c>
       <c r="C64" s="13" t="n">
-        <v>17.8</v>
+        <v>7.3</v>
       </c>
       <c r="D64" s="14" t="n">
-        <v>3.45</v>
+        <v>2.45</v>
       </c>
       <c r="E64" s="14" t="n">
-        <v>5.15</v>
+        <v>2.97</v>
       </c>
       <c r="F64" s="14" t="inlineStr">
         <is>
-          <t>yatak</t>
+          <t>islak</t>
         </is>
       </c>
       <c r="G64" s="9" t="inlineStr"/>
@@ -2732,103 +2780,153 @@
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Balkon 2</t>
+          <t>Çamaşır ve ütü odası</t>
         </is>
       </c>
       <c r="C65" s="13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D65" s="14" t="n">
-        <v>1.75</v>
+        <v>2.45</v>
       </c>
       <c r="E65" s="14" t="n">
-        <v>5.15</v>
+        <v>3.25</v>
       </c>
       <c r="F65" s="14" t="inlineStr">
         <is>
-          <t>acik</t>
-        </is>
-      </c>
-      <c r="G65" s="9" t="inlineStr">
-        <is>
-          <t>Açık alan — kapalı alana dahil değil</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="15" t="n"/>
-      <c r="B66" s="16" t="inlineStr">
+          <t>islak</t>
+        </is>
+      </c>
+      <c r="G65" s="9" t="inlineStr"/>
+    </row>
+    <row r="66" ht="18" customHeight="1">
+      <c r="A66" s="12" t="inlineStr">
+        <is>
+          <t>K-19</t>
+        </is>
+      </c>
+      <c r="B66" s="8" t="inlineStr">
+        <is>
+          <t>Aile WC</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D66" s="14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="E66" s="14" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="F66" s="14" t="inlineStr">
+        <is>
+          <t>islak</t>
+        </is>
+      </c>
+      <c r="G66" s="9" t="inlineStr"/>
+    </row>
+    <row r="67" ht="18" customHeight="1">
+      <c r="A67" s="12" t="inlineStr">
+        <is>
+          <t>K-20</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Aile oturma odası</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D67" s="14" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="E67" s="14" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="F67" s="14" t="inlineStr">
+        <is>
+          <t>yasam</t>
+        </is>
+      </c>
+      <c r="G67" s="9" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="15" t="n"/>
+      <c r="B68" s="16" t="inlineStr">
         <is>
           <t>1. Kat — TOPLAM</t>
         </is>
       </c>
-      <c r="C66" s="17">
-        <f>SUM(C48:C65)</f>
+      <c r="C68" s="17">
+        <f>SUMIF(G48:G67,"",C48:C67)</f>
         <v/>
       </c>
-      <c r="D66" s="15" t="n"/>
-      <c r="E66" s="15" t="n"/>
-      <c r="F66" s="15" t="n"/>
-      <c r="G66" s="16" t="n"/>
-    </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="D68" s="15" t="n"/>
+      <c r="E68" s="15" t="n"/>
+      <c r="F68" s="15" t="n"/>
+      <c r="G68" s="16" t="n"/>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>GENEL TOPLAM</t>
         </is>
       </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="18" t="n"/>
-      <c r="B69" s="19" t="inlineStr">
-        <is>
-          <t>Toplam net alan (kapalı + açık)</t>
-        </is>
-      </c>
-      <c r="C69" s="20">
-        <f>C26+C45+C66</f>
-        <v/>
-      </c>
-      <c r="D69" s="18" t="n"/>
-      <c r="E69" s="18" t="n"/>
-      <c r="F69" s="18" t="n"/>
-      <c r="G69" s="19" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="18" t="n"/>
-      <c r="B70" s="19" t="inlineStr">
-        <is>
-          <t>Toplam brüt inşaat alanı</t>
-        </is>
-      </c>
-      <c r="C70" s="20" t="n">
-        <v>900</v>
-      </c>
-      <c r="D70" s="18" t="n"/>
-      <c r="E70" s="18" t="n"/>
-      <c r="F70" s="18" t="n"/>
-      <c r="G70" s="19" t="n"/>
     </row>
     <row r="71">
       <c r="A71" s="18" t="n"/>
       <c r="B71" s="19" t="inlineStr">
         <is>
-          <t>Oturum (taban) alanı</t>
-        </is>
-      </c>
-      <c r="C71" s="20" t="n">
-        <v>300</v>
+          <t>Toplam net kullanım alanı</t>
+        </is>
+      </c>
+      <c r="C71" s="20">
+        <f>C26+C45+C68</f>
+        <v/>
       </c>
       <c r="D71" s="18" t="n"/>
       <c r="E71" s="18" t="n"/>
       <c r="F71" s="18" t="n"/>
       <c r="G71" s="19" t="n"/>
     </row>
+    <row r="72">
+      <c r="A72" s="18" t="n"/>
+      <c r="B72" s="19" t="inlineStr">
+        <is>
+          <t>Toplam brüt inşaat alanı</t>
+        </is>
+      </c>
+      <c r="C72" s="20" t="n">
+        <v>900</v>
+      </c>
+      <c r="D72" s="18" t="n"/>
+      <c r="E72" s="18" t="n"/>
+      <c r="F72" s="18" t="n"/>
+      <c r="G72" s="19" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="18" t="n"/>
+      <c r="B73" s="19" t="inlineStr">
+        <is>
+          <t>Oturum (taban) alanı</t>
+        </is>
+      </c>
+      <c r="C73" s="20" t="n">
+        <v>300</v>
+      </c>
+      <c r="D73" s="18" t="n"/>
+      <c r="E73" s="18" t="n"/>
+      <c r="F73" s="18" t="n"/>
+      <c r="G73" s="19" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A70:G70"/>
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A68:G68"/>
     <mergeCell ref="A47:G47"/>
     <mergeCell ref="A28:G28"/>
   </mergeCells>
@@ -2843,7 +2941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2957,60 +3055,60 @@
       </c>
       <c r="B6" s="23" t="inlineStr">
         <is>
-          <t>Garaj (3 araçlık)</t>
+          <t>Ev sineması</t>
         </is>
       </c>
       <c r="C6" s="24" t="n">
-        <v>48</v>
+        <v>35.2</v>
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>DK-06</t>
+          <t>DK-07</t>
         </is>
       </c>
       <c r="E6" s="25" t="inlineStr">
         <is>
-          <t>SP-04</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="F6" s="25" t="inlineStr">
         <is>
-          <t>DV-06</t>
+          <t>DV-07</t>
         </is>
       </c>
       <c r="G6" s="25" t="inlineStr">
         <is>
-          <t>TV-05</t>
+          <t>TV-06</t>
         </is>
       </c>
       <c r="H6" s="25" t="inlineStr">
         <is>
-          <t>KP-06</t>
+          <t>KP-02 (ses yalıtımlı)</t>
         </is>
       </c>
       <c r="I6" s="25" t="inlineStr">
         <is>
-          <t>DG-03</t>
+          <t>DG-07</t>
         </is>
       </c>
       <c r="J6" s="25" t="inlineStr">
         <is>
-          <t>EL-08</t>
+          <t>EL-07</t>
         </is>
       </c>
       <c r="K6" s="25" t="inlineStr">
         <is>
-          <t>MK-08</t>
+          <t>MK-01 + MK-04</t>
         </is>
       </c>
       <c r="L6" s="25" t="inlineStr">
         <is>
-          <t>ST-07</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="M6" s="26" t="inlineStr">
         <is>
-          <t>Zemin süzgece eğimli; elektrikli araç şarjı için 3 faz 11 kW hat. Kapı 5,00 m seksiyonel.</t>
+          <t>Penceresiz; duvar ve tavanda akustik dolgu, çift contalı kapı, 2 sıra 3'lü sinema koltuğu.</t>
         </is>
       </c>
     </row>
@@ -3022,11 +3120,11 @@
       </c>
       <c r="B7" s="23" t="inlineStr">
         <is>
-          <t>Hobi ve oyun salonu</t>
+          <t>Oyun ve bar salonu</t>
         </is>
       </c>
       <c r="C7" s="24" t="n">
-        <v>43.8</v>
+        <v>34.3</v>
       </c>
       <c r="D7" s="25" t="inlineStr">
         <is>
@@ -3055,7 +3153,7 @@
       </c>
       <c r="I7" s="25" t="inlineStr">
         <is>
-          <t>DG-01</t>
+          <t>DG-03</t>
         </is>
       </c>
       <c r="J7" s="25" t="inlineStr">
@@ -3065,17 +3163,17 @@
       </c>
       <c r="K7" s="25" t="inlineStr">
         <is>
-          <t>MK-01 + MK-03</t>
+          <t>MK-01 + MK-03 + MK-04</t>
         </is>
       </c>
       <c r="L7" s="25" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>ST-05 (bar eviyesi)</t>
         </is>
       </c>
       <c r="M7" s="26" t="inlineStr">
         <is>
-          <t>Mini bar için su/atık altyapısı bırakılacak (opsiyon); hol ile geniş açık geçiş.</t>
+          <t>Bilardo + bar; batı ışıklığına bakan 340 cm pencere. Hole çift kanatlı kapı.</t>
         </is>
       </c>
     </row>
@@ -3087,15 +3185,15 @@
       </c>
       <c r="B8" s="23" t="inlineStr">
         <is>
-          <t>Ev sineması</t>
+          <t>Misafir / hizmetli odası</t>
         </is>
       </c>
       <c r="C8" s="24" t="n">
-        <v>28</v>
+        <v>20.9</v>
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
-          <t>DK-07</t>
+          <t>DK-03</t>
         </is>
       </c>
       <c r="E8" s="25" t="inlineStr">
@@ -3105,32 +3203,32 @@
       </c>
       <c r="F8" s="25" t="inlineStr">
         <is>
-          <t>DV-07</t>
+          <t>DV-01 + DV-04</t>
         </is>
       </c>
       <c r="G8" s="25" t="inlineStr">
         <is>
-          <t>TV-06</t>
+          <t>TV-01</t>
         </is>
       </c>
       <c r="H8" s="25" t="inlineStr">
         <is>
-          <t>KP-02 (ses yalıtımlı)</t>
+          <t>KP-02</t>
         </is>
       </c>
       <c r="I8" s="25" t="inlineStr">
         <is>
-          <t>DG-07</t>
+          <t>DG-03 + DG-06</t>
         </is>
       </c>
       <c r="J8" s="25" t="inlineStr">
         <is>
-          <t>EL-07</t>
+          <t>EL-01</t>
         </is>
       </c>
       <c r="K8" s="25" t="inlineStr">
         <is>
-          <t>MK-01 + MK-04</t>
+          <t>MK-01 + MK-03</t>
         </is>
       </c>
       <c r="L8" s="25" t="inlineStr">
@@ -3140,7 +3238,7 @@
       </c>
       <c r="M8" s="26" t="inlineStr">
         <is>
-          <t>Duvar ve tavanda akustik dolgu; kapı çift contalı ve eşik fitilli.</t>
+          <t>Misafir veya ev çalışanı için; batı ışıklığında dikme kaçış merdiveni (acil çıkış).</t>
         </is>
       </c>
     </row>
@@ -3152,60 +3250,60 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>Kazan dairesi / teknik hacim</t>
+          <t>Oda holü ve dolap</t>
         </is>
       </c>
       <c r="C9" s="24" t="n">
-        <v>11.5</v>
+        <v>6.5</v>
       </c>
       <c r="D9" s="25" t="inlineStr">
         <is>
-          <t>DK-08</t>
+          <t>DK-03</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
         <is>
-          <t>SP-04</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="F9" s="25" t="inlineStr">
         <is>
-          <t>DV-06</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G9" s="25" t="inlineStr">
         <is>
-          <t>TV-05</t>
+          <t>TV-01</t>
         </is>
       </c>
       <c r="H9" s="25" t="inlineStr">
         <is>
-          <t>KP-05</t>
+          <t>KP-02</t>
         </is>
       </c>
       <c r="I9" s="25" t="inlineStr">
         <is>
-          <t>DG-03</t>
+          <t>DG-07</t>
         </is>
       </c>
       <c r="J9" s="25" t="inlineStr">
         <is>
-          <t>EL-05</t>
+          <t>EL-04</t>
         </is>
       </c>
       <c r="K9" s="25" t="inlineStr">
         <is>
-          <t>MK-06</t>
+          <t>MK-01</t>
         </is>
       </c>
       <c r="L9" s="25" t="inlineStr">
         <is>
-          <t>ST-07</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="M9" s="26" t="inlineStr">
         <is>
-          <t>Doğalgaz dedektörü + selenoid vana; taze hava menfezi yönetmelik ölçüsünde, yangın kapısı EI30.</t>
+          <t>Oda holü ve gömme dolap; oda ile banyoyu bodrum holünden ayırır.</t>
         </is>
       </c>
     </row>
@@ -3217,58 +3315,62 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>Merdiven ve hol</t>
+          <t>Oda banyosu</t>
         </is>
       </c>
       <c r="C10" s="24" t="n">
-        <v>17.7</v>
+        <v>5.2</v>
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>DK-02</t>
+          <t>DK-04</t>
         </is>
       </c>
       <c r="E10" s="25" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>SP-05</t>
         </is>
       </c>
       <c r="F10" s="25" t="inlineStr">
         <is>
-          <t>DV-01</t>
+          <t>DV-02</t>
         </is>
       </c>
       <c r="G10" s="25" t="inlineStr">
         <is>
-          <t>TV-01</t>
+          <t>TV-03</t>
         </is>
       </c>
       <c r="H10" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KP-03</t>
         </is>
       </c>
       <c r="I10" s="25" t="inlineStr">
         <is>
-          <t>DG-01</t>
+          <t>DG-07</t>
         </is>
       </c>
       <c r="J10" s="25" t="inlineStr">
         <is>
-          <t>EL-04</t>
+          <t>EL-02</t>
         </is>
       </c>
       <c r="K10" s="25" t="inlineStr">
         <is>
-          <t>MK-01</t>
+          <t>MK-02 + MK-04</t>
         </is>
       </c>
       <c r="L10" s="25" t="inlineStr">
         <is>
-          <t>ST-01</t>
-        </is>
-      </c>
-      <c r="M10" s="26" t="inlineStr"/>
+          <t>ST-02</t>
+        </is>
+      </c>
+      <c r="M10" s="26" t="inlineStr">
+        <is>
+          <t>Penceresiz; şafta bağlı mekanik havalandırma. Duş, lavabo, asma klozet.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="32" customHeight="1">
       <c r="A11" s="22" t="inlineStr">
@@ -3278,60 +3380,60 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>Çamaşırhane ve ütü odası</t>
+          <t>Bodrum holü</t>
         </is>
       </c>
       <c r="C11" s="24" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D11" s="25" t="inlineStr">
         <is>
-          <t>DK-04</t>
+          <t>DK-02</t>
         </is>
       </c>
       <c r="E11" s="25" t="inlineStr">
         <is>
-          <t>SP-05</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="F11" s="25" t="inlineStr">
         <is>
-          <t>DV-02 (h=150 cm)</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G11" s="25" t="inlineStr">
         <is>
-          <t>TV-03</t>
+          <t>TV-01</t>
         </is>
       </c>
       <c r="H11" s="25" t="inlineStr">
         <is>
-          <t>KP-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I11" s="25" t="inlineStr">
         <is>
-          <t>DG-03</t>
+          <t>DG-07</t>
         </is>
       </c>
       <c r="J11" s="25" t="inlineStr">
         <is>
-          <t>EL-02</t>
+          <t>EL-04</t>
         </is>
       </c>
       <c r="K11" s="25" t="inlineStr">
         <is>
-          <t>MK-04</t>
+          <t>MK-01</t>
         </is>
       </c>
       <c r="L11" s="25" t="inlineStr">
         <is>
-          <t>ST-06</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="M11" s="26" t="inlineStr">
         <is>
-          <t>Taşma koruma sensörü ve yer süzgeci zorunlu; tezgah altı makine yerleşimi.</t>
+          <t>Merdiven, asansör, depo ve odalara dağıtım holü; net genişlik 2,05 m.</t>
         </is>
       </c>
     </row>
@@ -3343,20 +3445,20 @@
       </c>
       <c r="B12" s="23" t="inlineStr">
         <is>
-          <t>Depo</t>
+          <t>Merdiven</t>
         </is>
       </c>
       <c r="C12" s="24" t="n">
-        <v>4.7</v>
+        <v>11.4</v>
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>DK-08</t>
+          <t>DK-02</t>
         </is>
       </c>
       <c r="E12" s="25" t="inlineStr">
         <is>
-          <t>SP-04</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="F12" s="25" t="inlineStr">
@@ -3366,27 +3468,27 @@
       </c>
       <c r="G12" s="25" t="inlineStr">
         <is>
-          <t>TV-05</t>
+          <t>TV-02</t>
         </is>
       </c>
       <c r="H12" s="25" t="inlineStr">
         <is>
-          <t>KP-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I12" s="25" t="inlineStr">
         <is>
-          <t>DG-07</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J12" s="25" t="inlineStr">
         <is>
-          <t>EL-05</t>
+          <t>EL-04</t>
         </is>
       </c>
       <c r="K12" s="25" t="inlineStr">
         <is>
-          <t>MK-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L12" s="25" t="inlineStr">
@@ -3394,11 +3496,7 @@
           <t>ST-01</t>
         </is>
       </c>
-      <c r="M12" s="26" t="inlineStr">
-        <is>
-          <t>Duvar boyu raf altyapısı.</t>
-        </is>
-      </c>
+      <c r="M12" s="26" t="inlineStr"/>
     </row>
     <row r="13" ht="32" customHeight="1">
       <c r="A13" s="22" t="inlineStr">
@@ -3408,25 +3506,25 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>Kiler / soğuk oda</t>
+          <t>Asansör</t>
         </is>
       </c>
       <c r="C13" s="24" t="n">
-        <v>5.7</v>
+        <v>3.8</v>
       </c>
       <c r="D13" s="25" t="inlineStr">
         <is>
-          <t>DK-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E13" s="25" t="inlineStr">
         <is>
-          <t>SP-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F13" s="25" t="inlineStr">
         <is>
-          <t>DV-01</t>
+          <t>DV-06</t>
         </is>
       </c>
       <c r="G13" s="25" t="inlineStr">
@@ -3436,7 +3534,7 @@
       </c>
       <c r="H13" s="25" t="inlineStr">
         <is>
-          <t>KP-08</t>
+          <t>Asansör kat kapısı</t>
         </is>
       </c>
       <c r="I13" s="25" t="inlineStr">
@@ -3451,7 +3549,7 @@
       </c>
       <c r="K13" s="25" t="inlineStr">
         <is>
-          <t>MK-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L13" s="25" t="inlineStr">
@@ -3459,11 +3557,7 @@
           <t>ST-01</t>
         </is>
       </c>
-      <c r="M13" s="26" t="inlineStr">
-        <is>
-          <t>Soğuk oda bölümü ayrı yalıtımlı, sabit havalandırmalı.</t>
-        </is>
-      </c>
+      <c r="M13" s="26" t="inlineStr"/>
     </row>
     <row r="14" ht="32" customHeight="1">
       <c r="A14" s="22" t="inlineStr">
@@ -3473,20 +3567,20 @@
       </c>
       <c r="B14" s="23" t="inlineStr">
         <is>
-          <t>Su deposu ve hidrofor</t>
+          <t>Tesisat şaftı</t>
         </is>
       </c>
       <c r="C14" s="24" t="n">
-        <v>5.8</v>
+        <v>0.9</v>
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t>DK-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E14" s="25" t="inlineStr">
         <is>
-          <t>SP-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="25" t="inlineStr">
@@ -3496,12 +3590,12 @@
       </c>
       <c r="G14" s="25" t="inlineStr">
         <is>
-          <t>TV-05</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H14" s="25" t="inlineStr">
         <is>
-          <t>KP-08</t>
+          <t>Servis kapağı</t>
         </is>
       </c>
       <c r="I14" s="25" t="inlineStr">
@@ -3511,24 +3605,20 @@
       </c>
       <c r="J14" s="25" t="inlineStr">
         <is>
-          <t>EL-05</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K14" s="25" t="inlineStr">
         <is>
-          <t>MK-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L14" s="25" t="inlineStr">
         <is>
-          <t>ST-07</t>
-        </is>
-      </c>
-      <c r="M14" s="26" t="inlineStr">
-        <is>
-          <t>Paslanmaz veya polyester depo, taşma-boşaltma hattı, hidrofor titreşim takozu.</t>
-        </is>
-      </c>
+          <t>Düşey tesisat</t>
+        </is>
+      </c>
+      <c r="M14" s="26" t="inlineStr"/>
     </row>
     <row r="15" ht="32" customHeight="1">
       <c r="A15" s="22" t="inlineStr">
@@ -3538,11 +3628,11 @@
       </c>
       <c r="B15" s="23" t="inlineStr">
         <is>
-          <t>Elektrik panosu / depo</t>
+          <t>Genel depo</t>
         </is>
       </c>
       <c r="C15" s="24" t="n">
-        <v>2.6</v>
+        <v>12.9</v>
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
@@ -3556,7 +3646,7 @@
       </c>
       <c r="F15" s="25" t="inlineStr">
         <is>
-          <t>DV-06</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G15" s="25" t="inlineStr">
@@ -3576,7 +3666,7 @@
       </c>
       <c r="J15" s="25" t="inlineStr">
         <is>
-          <t>EL-09</t>
+          <t>EL-05</t>
         </is>
       </c>
       <c r="K15" s="25" t="inlineStr">
@@ -3591,7 +3681,7 @@
       </c>
       <c r="M15" s="26" t="inlineStr">
         <is>
-          <t>Ana dağıtım panosu ve zayıf akım panosu; akıllı ev ana kabini.</t>
+          <t>Genel depo; duvar boyu raf, nem alma cihazı prizi.</t>
         </is>
       </c>
     </row>
@@ -3603,25 +3693,25 @@
       </c>
       <c r="B16" s="23" t="inlineStr">
         <is>
-          <t>Asansör ve tesisat şaftı</t>
+          <t>Elektrik ve zayıf akım odası</t>
         </is>
       </c>
       <c r="C16" s="24" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DK-08</t>
         </is>
       </c>
       <c r="E16" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SP-04</t>
         </is>
       </c>
       <c r="F16" s="25" t="inlineStr">
         <is>
-          <t>DV-06</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G16" s="25" t="inlineStr">
@@ -3631,7 +3721,7 @@
       </c>
       <c r="H16" s="25" t="inlineStr">
         <is>
-          <t>Asansör kabin kapısı</t>
+          <t>KP-08</t>
         </is>
       </c>
       <c r="I16" s="25" t="inlineStr">
@@ -3641,7 +3731,7 @@
       </c>
       <c r="J16" s="25" t="inlineStr">
         <is>
-          <t>EL-05</t>
+          <t>EL-09</t>
         </is>
       </c>
       <c r="K16" s="25" t="inlineStr">
@@ -3656,7 +3746,7 @@
       </c>
       <c r="M16" s="26" t="inlineStr">
         <is>
-          <t>4 duraklı makine dairesiz asansör; kuyu su yalıtımı ve süzgeci.</t>
+          <t>Ana dağıtım panosu, zayıf akım kabini, akıllı ev ve NVR.</t>
         </is>
       </c>
     </row>
@@ -3668,35 +3758,35 @@
       </c>
       <c r="B17" s="23" t="inlineStr">
         <is>
-          <t>WC + duş</t>
+          <t>Koridor</t>
         </is>
       </c>
       <c r="C17" s="24" t="n">
-        <v>4</v>
+        <v>8.1</v>
       </c>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t>DK-04</t>
+          <t>DK-01</t>
         </is>
       </c>
       <c r="E17" s="25" t="inlineStr">
         <is>
-          <t>SP-05</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="F17" s="25" t="inlineStr">
         <is>
-          <t>DV-02</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G17" s="25" t="inlineStr">
         <is>
-          <t>TV-03</t>
+          <t>TV-01</t>
         </is>
       </c>
       <c r="H17" s="25" t="inlineStr">
         <is>
-          <t>KP-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I17" s="25" t="inlineStr">
@@ -3706,22 +3796,22 @@
       </c>
       <c r="J17" s="25" t="inlineStr">
         <is>
-          <t>EL-02</t>
+          <t>EL-04</t>
         </is>
       </c>
       <c r="K17" s="25" t="inlineStr">
         <is>
-          <t>MK-02 + MK-04</t>
+          <t>MK-01</t>
         </is>
       </c>
       <c r="L17" s="25" t="inlineStr">
         <is>
-          <t>ST-02</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="M17" s="26" t="inlineStr">
         <is>
-          <t>Spor ve sauna bölümüne hizmet eder.</t>
+          <t>Teknik ve spa bölümüne servis koridoru; net genişlik 1,25 m.</t>
         </is>
       </c>
     </row>
@@ -3733,20 +3823,20 @@
       </c>
       <c r="B18" s="23" t="inlineStr">
         <is>
-          <t>Koridor</t>
+          <t>Isı merkezi (kazan / ısı pompası)</t>
         </is>
       </c>
       <c r="C18" s="24" t="n">
-        <v>3.6</v>
+        <v>13.6</v>
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>DK-01</t>
+          <t>DK-08</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>SP-04</t>
         </is>
       </c>
       <c r="F18" s="25" t="inlineStr">
@@ -3756,12 +3846,12 @@
       </c>
       <c r="G18" s="25" t="inlineStr">
         <is>
-          <t>TV-01</t>
+          <t>TV-05</t>
         </is>
       </c>
       <c r="H18" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KP-05</t>
         </is>
       </c>
       <c r="I18" s="25" t="inlineStr">
@@ -3771,22 +3861,22 @@
       </c>
       <c r="J18" s="25" t="inlineStr">
         <is>
-          <t>EL-04</t>
+          <t>EL-05</t>
         </is>
       </c>
       <c r="K18" s="25" t="inlineStr">
         <is>
-          <t>MK-01</t>
+          <t>MK-06</t>
         </is>
       </c>
       <c r="L18" s="25" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>ST-07</t>
         </is>
       </c>
       <c r="M18" s="26" t="inlineStr">
         <is>
-          <t>Net genişlik 1,45 m (yönetmelik asgarisi 1,20 m).</t>
+          <t>EI30 kapı; hermetik kazan veya ısı pompası iç ünitesi, boyler, kollektörler; baca şafttan çatıya.</t>
         </is>
       </c>
     </row>
@@ -3798,35 +3888,35 @@
       </c>
       <c r="B19" s="23" t="inlineStr">
         <is>
-          <t>Şarap mahzeni ve bar</t>
+          <t>Su deposu ve hidrofor</t>
         </is>
       </c>
       <c r="C19" s="24" t="n">
-        <v>13.1</v>
+        <v>9.1</v>
       </c>
       <c r="D19" s="25" t="inlineStr">
         <is>
-          <t>DK-02</t>
+          <t>DK-08</t>
         </is>
       </c>
       <c r="E19" s="25" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>SP-04</t>
         </is>
       </c>
       <c r="F19" s="25" t="inlineStr">
         <is>
-          <t>DV-01 + DV-04</t>
+          <t>DV-06</t>
         </is>
       </c>
       <c r="G19" s="25" t="inlineStr">
         <is>
-          <t>TV-01</t>
+          <t>TV-05</t>
         </is>
       </c>
       <c r="H19" s="25" t="inlineStr">
         <is>
-          <t>KP-02</t>
+          <t>KP-08</t>
         </is>
       </c>
       <c r="I19" s="25" t="inlineStr">
@@ -3836,22 +3926,22 @@
       </c>
       <c r="J19" s="25" t="inlineStr">
         <is>
-          <t>EL-01</t>
+          <t>EL-05</t>
         </is>
       </c>
       <c r="K19" s="25" t="inlineStr">
         <is>
-          <t>MK-04</t>
+          <t>MK-08</t>
         </is>
       </c>
       <c r="L19" s="25" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>ST-07</t>
         </is>
       </c>
       <c r="M19" s="26" t="inlineStr">
         <is>
-          <t>Sabit 14–16 °C için ayrı klima/nem kontrolü; ahşap şarap rafı.</t>
+          <t>2 × 2,5 ton su deposu, hidrofor, titreşim takozu, taşma-boşaltma hattı.</t>
         </is>
       </c>
     </row>
@@ -3863,50 +3953,50 @@
       </c>
       <c r="B20" s="23" t="inlineStr">
         <is>
-          <t>Spor salonu (fitness)</t>
+          <t>Kiler ve soğuk depo</t>
         </is>
       </c>
       <c r="C20" s="24" t="n">
-        <v>18.3</v>
+        <v>13.7</v>
       </c>
       <c r="D20" s="25" t="inlineStr">
         <is>
-          <t>DK-03</t>
+          <t>DK-08</t>
         </is>
       </c>
       <c r="E20" s="25" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>SP-04</t>
         </is>
       </c>
       <c r="F20" s="25" t="inlineStr">
         <is>
-          <t>DV-01 + ayna duvar</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G20" s="25" t="inlineStr">
         <is>
-          <t>TV-01</t>
+          <t>TV-05</t>
         </is>
       </c>
       <c r="H20" s="25" t="inlineStr">
         <is>
-          <t>KP-02</t>
+          <t>KP-08</t>
         </is>
       </c>
       <c r="I20" s="25" t="inlineStr">
         <is>
-          <t>DG-03</t>
+          <t>DG-07</t>
         </is>
       </c>
       <c r="J20" s="25" t="inlineStr">
         <is>
-          <t>EL-04</t>
+          <t>EL-05</t>
         </is>
       </c>
       <c r="K20" s="25" t="inlineStr">
         <is>
-          <t>MK-01 + MK-03 + MK-04</t>
+          <t>MK-04</t>
         </is>
       </c>
       <c r="L20" s="25" t="inlineStr">
@@ -3916,7 +4006,7 @@
       </c>
       <c r="M20" s="26" t="inlineStr">
         <is>
-          <t>8 mm kauçuk şok emici alt katman, tam boy ayna ve bale barı.</t>
+          <t>Soğuk depo bölümü ayrı yalıtımlı, sabit havalandırma; iki yanda raf.</t>
         </is>
       </c>
     </row>
@@ -3928,35 +4018,35 @@
       </c>
       <c r="B21" s="23" t="inlineStr">
         <is>
-          <t>Sauna ve dinlenme</t>
+          <t>Havuz makine dairesi</t>
         </is>
       </c>
       <c r="C21" s="24" t="n">
-        <v>10.4</v>
+        <v>13.7</v>
       </c>
       <c r="D21" s="25" t="inlineStr">
         <is>
-          <t>DK-04</t>
+          <t>DK-08</t>
         </is>
       </c>
       <c r="E21" s="25" t="inlineStr">
         <is>
-          <t>SP-05</t>
+          <t>SP-04</t>
         </is>
       </c>
       <c r="F21" s="25" t="inlineStr">
         <is>
-          <t>DV-02 + DV-08</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G21" s="25" t="inlineStr">
         <is>
-          <t>TV-03</t>
+          <t>TV-05</t>
         </is>
       </c>
       <c r="H21" s="25" t="inlineStr">
         <is>
-          <t>KP-07</t>
+          <t>KP-08</t>
         </is>
       </c>
       <c r="I21" s="25" t="inlineStr">
@@ -3966,22 +4056,22 @@
       </c>
       <c r="J21" s="25" t="inlineStr">
         <is>
-          <t>EL-02</t>
+          <t>EL-05</t>
         </is>
       </c>
       <c r="K21" s="25" t="inlineStr">
         <is>
-          <t>MK-07 + MK-04</t>
+          <t>MK-08</t>
         </is>
       </c>
       <c r="L21" s="25" t="inlineStr">
         <is>
-          <t>ST-02</t>
+          <t>ST-07</t>
         </is>
       </c>
       <c r="M21" s="26" t="inlineStr">
         <is>
-          <t>Sauna iç hacmi sedir kaplama; dinlenme alanı duştan ayrık.</t>
+          <t>Havuz filtre, pompa, denge deposu ve dozaj ünitesi; havuza en kısa hat.</t>
         </is>
       </c>
     </row>
@@ -3997,7 +4087,7 @@
         </is>
       </c>
       <c r="C22" s="24" t="n">
-        <v>7.8</v>
+        <v>6.5</v>
       </c>
       <c r="D22" s="25" t="inlineStr">
         <is>
@@ -4021,12 +4111,12 @@
       </c>
       <c r="H22" s="25" t="inlineStr">
         <is>
-          <t>KP-07</t>
+          <t>KP-03</t>
         </is>
       </c>
       <c r="I22" s="25" t="inlineStr">
         <is>
-          <t>DG-03</t>
+          <t>DG-07</t>
         </is>
       </c>
       <c r="J22" s="25" t="inlineStr">
@@ -4046,7 +4136,7 @@
       </c>
       <c r="M22" s="26" t="inlineStr">
         <is>
-          <t>Soyunma dolapları ve duş kabinleri.</t>
+          <t>Soyunma dolapları, duş, bank; saunaya cam sürme kapı.</t>
         </is>
       </c>
     </row>
@@ -4058,60 +4148,60 @@
       </c>
       <c r="B23" s="23" t="inlineStr">
         <is>
-          <t>Hizmet / misafir odası</t>
+          <t>Sauna</t>
         </is>
       </c>
       <c r="C23" s="24" t="n">
-        <v>10.4</v>
+        <v>5.8</v>
       </c>
       <c r="D23" s="25" t="inlineStr">
         <is>
-          <t>DK-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E23" s="25" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>SP-05</t>
         </is>
       </c>
       <c r="F23" s="25" t="inlineStr">
         <is>
-          <t>DV-01 + DV-04</t>
+          <t>DV-08</t>
         </is>
       </c>
       <c r="G23" s="25" t="inlineStr">
         <is>
-          <t>TV-01</t>
+          <t>DV-08</t>
         </is>
       </c>
       <c r="H23" s="25" t="inlineStr">
         <is>
-          <t>KP-02</t>
+          <t>KP-07</t>
         </is>
       </c>
       <c r="I23" s="25" t="inlineStr">
         <is>
-          <t>DG-03</t>
+          <t>DG-07</t>
         </is>
       </c>
       <c r="J23" s="25" t="inlineStr">
         <is>
-          <t>EL-01</t>
+          <t>EL-02</t>
         </is>
       </c>
       <c r="K23" s="25" t="inlineStr">
         <is>
-          <t>MK-01 + MK-03</t>
+          <t>MK-07 + MK-04</t>
         </is>
       </c>
       <c r="L23" s="25" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>ST-02</t>
         </is>
       </c>
       <c r="M23" s="26" t="inlineStr">
         <is>
-          <t>Hizmet personeli veya uzun süreli misafir için; ensuite banyolu.</t>
+          <t>Sedir kaplama, iki kademeli bank, elektrikli soba.</t>
         </is>
       </c>
     </row>
@@ -4123,35 +4213,35 @@
       </c>
       <c r="B24" s="23" t="inlineStr">
         <is>
-          <t>Hizmet banyosu</t>
+          <t>Fitness salonu</t>
         </is>
       </c>
       <c r="C24" s="24" t="n">
-        <v>4.8</v>
+        <v>19.9</v>
       </c>
       <c r="D24" s="25" t="inlineStr">
         <is>
-          <t>DK-04</t>
+          <t>DK-07</t>
         </is>
       </c>
       <c r="E24" s="25" t="inlineStr">
         <is>
-          <t>SP-05</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="F24" s="25" t="inlineStr">
         <is>
-          <t>DV-02</t>
+          <t>DV-01 + DV-04</t>
         </is>
       </c>
       <c r="G24" s="25" t="inlineStr">
         <is>
-          <t>TV-03</t>
+          <t>TV-01</t>
         </is>
       </c>
       <c r="H24" s="25" t="inlineStr">
         <is>
-          <t>KP-03</t>
+          <t>KP-02</t>
         </is>
       </c>
       <c r="I24" s="25" t="inlineStr">
@@ -4161,22 +4251,22 @@
       </c>
       <c r="J24" s="25" t="inlineStr">
         <is>
-          <t>EL-02</t>
+          <t>EL-04</t>
         </is>
       </c>
       <c r="K24" s="25" t="inlineStr">
         <is>
-          <t>MK-02 + MK-04</t>
+          <t>MK-01 + MK-03 + MK-04</t>
         </is>
       </c>
       <c r="L24" s="25" t="inlineStr">
         <is>
-          <t>ST-02</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="M24" s="26" t="inlineStr">
         <is>
-          <t>Duş kabinli.</t>
+          <t>Doğu ışıklığına bakan pencere; kauçuk şok emici zemin, ayna duvar.</t>
         </is>
       </c>
     </row>
@@ -4188,11 +4278,11 @@
       </c>
       <c r="B25" s="23" t="inlineStr">
         <is>
-          <t>Temizlik deposu</t>
+          <t>Depo</t>
         </is>
       </c>
       <c r="C25" s="24" t="n">
-        <v>2.7</v>
+        <v>5.5</v>
       </c>
       <c r="D25" s="25" t="inlineStr">
         <is>
@@ -4241,7 +4331,7 @@
       </c>
       <c r="M25" s="26" t="inlineStr">
         <is>
-          <t>Temizlik malzemesi ve süpürge dolabı, eviye bağlantısı.</t>
+          <t>Hol deposu (bavul, mevsimlik eşya).</t>
         </is>
       </c>
     </row>
@@ -4253,60 +4343,60 @@
       </c>
       <c r="B26" s="23" t="inlineStr">
         <is>
-          <t>Işıklık / İngiliz bahçesi</t>
+          <t>Şarap mahzeni</t>
         </is>
       </c>
       <c r="C26" s="24" t="n">
-        <v>17.3</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="D26" s="25" t="inlineStr">
         <is>
-          <t>DK-05</t>
+          <t>DK-02</t>
         </is>
       </c>
       <c r="E26" s="25" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="F26" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G26" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TV-01</t>
         </is>
       </c>
       <c r="H26" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KP-02</t>
         </is>
       </c>
       <c r="I26" s="25" t="inlineStr">
         <is>
-          <t>DG-03</t>
+          <t>DG-07</t>
         </is>
       </c>
       <c r="J26" s="25" t="inlineStr">
         <is>
-          <t>EL-06</t>
+          <t>EL-01</t>
         </is>
       </c>
       <c r="K26" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-04 + ayrı klima (14–16 °C)</t>
         </is>
       </c>
       <c r="L26" s="25" t="inlineStr">
         <is>
-          <t>ST-08</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="M26" s="26" t="inlineStr">
         <is>
-          <t>Işıklık tabanında drenaj, üstte galvaniz ızgara; bodruma doğal ışık ve havalandırma sağlar.</t>
+          <t>Şarap rafları ve tadım masası; sabit ısı ve nem.</t>
         </is>
       </c>
     </row>
@@ -4325,11 +4415,11 @@
       </c>
       <c r="B28" s="23" t="inlineStr">
         <is>
-          <t>Salon / oturma alanı</t>
+          <t>Antre / giriş holü</t>
         </is>
       </c>
       <c r="C28" s="24" t="n">
-        <v>61.4</v>
+        <v>16.8</v>
       </c>
       <c r="D28" s="25" t="inlineStr">
         <is>
@@ -4338,12 +4428,12 @@
       </c>
       <c r="E28" s="25" t="inlineStr">
         <is>
-          <t>SP-03</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="F28" s="25" t="inlineStr">
         <is>
-          <t>DV-01 + DV-03 (TV duvarı)</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G28" s="25" t="inlineStr">
@@ -4353,22 +4443,22 @@
       </c>
       <c r="H28" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KP-01</t>
         </is>
       </c>
       <c r="I28" s="25" t="inlineStr">
         <is>
-          <t>DG-01 + DG-02</t>
+          <t>DG-01 (sabit yan cam)</t>
         </is>
       </c>
       <c r="J28" s="25" t="inlineStr">
         <is>
-          <t>EL-04</t>
+          <t>EL-09</t>
         </is>
       </c>
       <c r="K28" s="25" t="inlineStr">
         <is>
-          <t>MK-01 + MK-03</t>
+          <t>MK-01</t>
         </is>
       </c>
       <c r="L28" s="25" t="inlineStr">
@@ -4378,7 +4468,7 @@
       </c>
       <c r="M28" s="26" t="inlineStr">
         <is>
-          <t>Galeri boşluğu; şömine için baca/tesisat opsiyonu. Yemek alanıyla açık geçiş.</t>
+          <t>Galeri altında çift yükseklik giriş; gömme vestiyer dolabı, görüntülü diyafon, akıllı ev paneli.</t>
         </is>
       </c>
     </row>
@@ -4390,11 +4480,11 @@
       </c>
       <c r="B29" s="23" t="inlineStr">
         <is>
-          <t>Yemek alanı</t>
+          <t>Hol</t>
         </is>
       </c>
       <c r="C29" s="24" t="n">
-        <v>30.5</v>
+        <v>14</v>
       </c>
       <c r="D29" s="25" t="inlineStr">
         <is>
@@ -4403,12 +4493,12 @@
       </c>
       <c r="E29" s="25" t="inlineStr">
         <is>
-          <t>SP-03</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="F29" s="25" t="inlineStr">
         <is>
-          <t>DV-01 + DV-04</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G29" s="25" t="inlineStr">
@@ -4423,7 +4513,7 @@
       </c>
       <c r="I29" s="25" t="inlineStr">
         <is>
-          <t>DG-01</t>
+          <t>DG-07</t>
         </is>
       </c>
       <c r="J29" s="25" t="inlineStr">
@@ -4433,7 +4523,7 @@
       </c>
       <c r="K29" s="25" t="inlineStr">
         <is>
-          <t>MK-01 + MK-03</t>
+          <t>MK-01</t>
         </is>
       </c>
       <c r="L29" s="25" t="inlineStr">
@@ -4443,7 +4533,7 @@
       </c>
       <c r="M29" s="26" t="inlineStr">
         <is>
-          <t>Avize için tavanda taşıyıcı ankraj; mutfak ve salonla açık geçiş.</t>
+          <t>Girişten bahçeye görsel aks; merdiven, asansör, salon ve misafir süitine dağıtım.</t>
         </is>
       </c>
     </row>
@@ -4455,15 +4545,15 @@
       </c>
       <c r="B30" s="23" t="inlineStr">
         <is>
-          <t>Kapalı veranda</t>
+          <t>Merdiven</t>
         </is>
       </c>
       <c r="C30" s="24" t="n">
-        <v>28</v>
+        <v>11.4</v>
       </c>
       <c r="D30" s="25" t="inlineStr">
         <is>
-          <t>DK-05</t>
+          <t>DK-02</t>
         </is>
       </c>
       <c r="E30" s="25" t="inlineStr">
@@ -4473,44 +4563,40 @@
       </c>
       <c r="F30" s="25" t="inlineStr">
         <is>
-          <t>DV-01 (dış cephe kaplaması)</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G30" s="25" t="inlineStr">
         <is>
-          <t>TV-04</t>
+          <t>TV-02</t>
         </is>
       </c>
       <c r="H30" s="25" t="inlineStr">
         <is>
-          <t>KP-07</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I30" s="25" t="inlineStr">
         <is>
-          <t>DG-02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J30" s="25" t="inlineStr">
         <is>
-          <t>EL-06</t>
+          <t>EL-04</t>
         </is>
       </c>
       <c r="K30" s="25" t="inlineStr">
         <is>
-          <t>MK-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L30" s="25" t="inlineStr">
         <is>
-          <t>ST-08</t>
-        </is>
-      </c>
-      <c r="M30" s="26" t="inlineStr">
-        <is>
-          <t>Katlanır/sürme cam sistemle dört mevsim kullanım; tavanda ısıtıcı opsiyonu.</t>
-        </is>
-      </c>
+          <t>ST-01</t>
+        </is>
+      </c>
+      <c r="M30" s="26" t="inlineStr"/>
     </row>
     <row r="31" ht="32" customHeight="1">
       <c r="A31" s="22" t="inlineStr">
@@ -4520,50 +4606,50 @@
       </c>
       <c r="B31" s="23" t="inlineStr">
         <is>
-          <t>Antre / giriş holü</t>
+          <t>Asansör</t>
         </is>
       </c>
       <c r="C31" s="24" t="n">
-        <v>11.5</v>
+        <v>3.8</v>
       </c>
       <c r="D31" s="25" t="inlineStr">
         <is>
-          <t>DK-02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E31" s="25" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F31" s="25" t="inlineStr">
         <is>
-          <t>DV-01</t>
+          <t>DV-06</t>
         </is>
       </c>
       <c r="G31" s="25" t="inlineStr">
         <is>
-          <t>TV-01</t>
+          <t>TV-05</t>
         </is>
       </c>
       <c r="H31" s="25" t="inlineStr">
         <is>
-          <t>KP-01</t>
+          <t>Asansör kat kapısı</t>
         </is>
       </c>
       <c r="I31" s="25" t="inlineStr">
         <is>
-          <t>DG-01</t>
+          <t>DG-07</t>
         </is>
       </c>
       <c r="J31" s="25" t="inlineStr">
         <is>
-          <t>EL-09</t>
+          <t>EL-05</t>
         </is>
       </c>
       <c r="K31" s="25" t="inlineStr">
         <is>
-          <t>MK-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L31" s="25" t="inlineStr">
@@ -4571,11 +4657,7 @@
           <t>ST-01</t>
         </is>
       </c>
-      <c r="M31" s="26" t="inlineStr">
-        <is>
-          <t>Görüntülü diyafon, akıllı ev ana paneli, gömme paspas nişi.</t>
-        </is>
-      </c>
+      <c r="M31" s="26" t="inlineStr"/>
     </row>
     <row r="32" ht="32" customHeight="1">
       <c r="A32" s="22" t="inlineStr">
@@ -4585,62 +4667,58 @@
       </c>
       <c r="B32" s="23" t="inlineStr">
         <is>
-          <t>Merdiven, hol ve galeri</t>
+          <t>Tesisat şaftı</t>
         </is>
       </c>
       <c r="C32" s="24" t="n">
-        <v>17.7</v>
+        <v>0.9</v>
       </c>
       <c r="D32" s="25" t="inlineStr">
         <is>
-          <t>DK-02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E32" s="25" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F32" s="25" t="inlineStr">
         <is>
-          <t>DV-01</t>
+          <t>DV-06</t>
         </is>
       </c>
       <c r="G32" s="25" t="inlineStr">
         <is>
-          <t>TV-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H32" s="25" t="inlineStr">
         <is>
+          <t>Servis kapağı</t>
+        </is>
+      </c>
+      <c r="I32" s="25" t="inlineStr">
+        <is>
+          <t>DG-07</t>
+        </is>
+      </c>
+      <c r="J32" s="25" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I32" s="25" t="inlineStr">
-        <is>
-          <t>DG-01</t>
-        </is>
-      </c>
-      <c r="J32" s="25" t="inlineStr">
-        <is>
-          <t>EL-04</t>
-        </is>
-      </c>
       <c r="K32" s="25" t="inlineStr">
         <is>
-          <t>MK-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L32" s="25" t="inlineStr">
         <is>
-          <t>ST-01</t>
-        </is>
-      </c>
-      <c r="M32" s="26" t="inlineStr">
-        <is>
-          <t>Doğal taş basamak + rıht, 10 mm temperli cam korkuluk (h=110 cm), paslanmaz küpeşte.</t>
-        </is>
-      </c>
+          <t>Düşey tesisat</t>
+        </is>
+      </c>
+      <c r="M32" s="26" t="inlineStr"/>
     </row>
     <row r="33" ht="32" customHeight="1">
       <c r="A33" s="22" t="inlineStr">
@@ -4650,25 +4728,25 @@
       </c>
       <c r="B33" s="23" t="inlineStr">
         <is>
-          <t>Mutfak (ankastre)</t>
+          <t>Misafir yatak odası</t>
         </is>
       </c>
       <c r="C33" s="24" t="n">
-        <v>20.2</v>
+        <v>25.7</v>
       </c>
       <c r="D33" s="25" t="inlineStr">
         <is>
-          <t>DK-01</t>
+          <t>DK-03</t>
         </is>
       </c>
       <c r="E33" s="25" t="inlineStr">
         <is>
-          <t>SP-04</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="F33" s="25" t="inlineStr">
         <is>
-          <t>DV-02 + DV-01</t>
+          <t>DV-01 + DV-04</t>
         </is>
       </c>
       <c r="G33" s="25" t="inlineStr">
@@ -4678,32 +4756,32 @@
       </c>
       <c r="H33" s="25" t="inlineStr">
         <is>
-          <t>KP-04</t>
+          <t>KP-02</t>
         </is>
       </c>
       <c r="I33" s="25" t="inlineStr">
         <is>
-          <t>DG-01</t>
+          <t>DG-01 + DG-05 + DG-06</t>
         </is>
       </c>
       <c r="J33" s="25" t="inlineStr">
         <is>
-          <t>EL-03</t>
+          <t>EL-01</t>
         </is>
       </c>
       <c r="K33" s="25" t="inlineStr">
         <is>
-          <t>MK-01 + MK-05</t>
+          <t>MK-01 + MK-03</t>
         </is>
       </c>
       <c r="L33" s="25" t="inlineStr">
         <is>
-          <t>ST-05</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="M33" s="26" t="inlineStr">
         <is>
-          <t>Ada tezgah; kuvars tezgah (Çimstone/Belenco), tezgah altı LED, çekmece içi priz.</t>
+          <t>Misafir süiti — hol ve banyo ile; 1. kattaki yatak 2 süitiyle aynı aksta.</t>
         </is>
       </c>
     </row>
@@ -4715,25 +4793,25 @@
       </c>
       <c r="B34" s="23" t="inlineStr">
         <is>
-          <t>Kiler / arka mutfak</t>
+          <t>Misafir banyosu</t>
         </is>
       </c>
       <c r="C34" s="24" t="n">
-        <v>10.2</v>
+        <v>5.1</v>
       </c>
       <c r="D34" s="25" t="inlineStr">
         <is>
-          <t>DK-01</t>
+          <t>DK-04</t>
         </is>
       </c>
       <c r="E34" s="25" t="inlineStr">
         <is>
-          <t>SP-04</t>
+          <t>SP-05</t>
         </is>
       </c>
       <c r="F34" s="25" t="inlineStr">
         <is>
-          <t>DV-02 + DV-01</t>
+          <t>DV-02</t>
         </is>
       </c>
       <c r="G34" s="25" t="inlineStr">
@@ -4743,32 +4821,32 @@
       </c>
       <c r="H34" s="25" t="inlineStr">
         <is>
-          <t>KP-02</t>
+          <t>KP-03</t>
         </is>
       </c>
       <c r="I34" s="25" t="inlineStr">
         <is>
-          <t>DG-01</t>
+          <t>DG-01 (buzlu)</t>
         </is>
       </c>
       <c r="J34" s="25" t="inlineStr">
         <is>
-          <t>EL-03</t>
+          <t>EL-02</t>
         </is>
       </c>
       <c r="K34" s="25" t="inlineStr">
         <is>
-          <t>MK-04</t>
+          <t>MK-02 + MK-04</t>
         </is>
       </c>
       <c r="L34" s="25" t="inlineStr">
         <is>
-          <t>ST-05</t>
+          <t>ST-02</t>
         </is>
       </c>
       <c r="M34" s="26" t="inlineStr">
         <is>
-          <t>Arka mutfak: bulaşık ve hazırlık alanı, derin raflı kiler.</t>
+          <t>Duş, lavabo, asma klozet; kuzeyde yüksek pencere.</t>
         </is>
       </c>
     </row>
@@ -4780,35 +4858,35 @@
       </c>
       <c r="B35" s="23" t="inlineStr">
         <is>
-          <t>Misafir WC</t>
+          <t>Misafir süit holü</t>
         </is>
       </c>
       <c r="C35" s="24" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="D35" s="25" t="inlineStr">
         <is>
-          <t>DK-04</t>
+          <t>DK-02</t>
         </is>
       </c>
       <c r="E35" s="25" t="inlineStr">
         <is>
-          <t>SP-05</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="F35" s="25" t="inlineStr">
         <is>
-          <t>DV-03</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G35" s="25" t="inlineStr">
         <is>
-          <t>TV-03</t>
+          <t>TV-01</t>
         </is>
       </c>
       <c r="H35" s="25" t="inlineStr">
         <is>
-          <t>KP-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I35" s="25" t="inlineStr">
@@ -4818,22 +4896,22 @@
       </c>
       <c r="J35" s="25" t="inlineStr">
         <is>
-          <t>EL-02</t>
+          <t>EL-04</t>
         </is>
       </c>
       <c r="K35" s="25" t="inlineStr">
         <is>
-          <t>MK-02 + MK-04</t>
+          <t>MK-01</t>
         </is>
       </c>
       <c r="L35" s="25" t="inlineStr">
         <is>
-          <t>ST-04</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="M35" s="26" t="inlineStr">
         <is>
-          <t>Tezgah üstü çanak lavabo, ankastre batarya, dekoratif aydınlatma.</t>
+          <t>Misafir süiti giriş holü, gömme dolap.</t>
         </is>
       </c>
     </row>
@@ -4845,50 +4923,50 @@
       </c>
       <c r="B36" s="23" t="inlineStr">
         <is>
-          <t>Vestiyer</t>
+          <t>Salon (şömineli)</t>
         </is>
       </c>
       <c r="C36" s="24" t="n">
-        <v>2.6</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D36" s="25" t="inlineStr">
         <is>
-          <t>DK-08</t>
+          <t>DK-02</t>
         </is>
       </c>
       <c r="E36" s="25" t="inlineStr">
         <is>
-          <t>SP-04</t>
+          <t>SP-03</t>
         </is>
       </c>
       <c r="F36" s="25" t="inlineStr">
         <is>
-          <t>DV-01</t>
+          <t>DV-01 + DV-03 (şömine duvarı)</t>
         </is>
       </c>
       <c r="G36" s="25" t="inlineStr">
         <is>
-          <t>TV-05</t>
+          <t>TV-01</t>
         </is>
       </c>
       <c r="H36" s="25" t="inlineStr">
         <is>
-          <t>KP-04</t>
+          <t>KP-02 (çift kanat)</t>
         </is>
       </c>
       <c r="I36" s="25" t="inlineStr">
         <is>
-          <t>DG-07</t>
+          <t>DG-01 + DG-02</t>
         </is>
       </c>
       <c r="J36" s="25" t="inlineStr">
         <is>
-          <t>EL-05</t>
+          <t>EL-04</t>
         </is>
       </c>
       <c r="K36" s="25" t="inlineStr">
         <is>
-          <t>MK-01</t>
+          <t>MK-01 + MK-03</t>
         </is>
       </c>
       <c r="L36" s="25" t="inlineStr">
@@ -4898,7 +4976,7 @@
       </c>
       <c r="M36" s="26" t="inlineStr">
         <is>
-          <t>Tavana kadar gardırop, havalandırma menfezi.</t>
+          <t>Şömine batı duvarında, baca dışta taş kütle; güneyde 540 cm kaldır-sür doğrama ile teras.</t>
         </is>
       </c>
     </row>
@@ -4910,50 +4988,50 @@
       </c>
       <c r="B37" s="23" t="inlineStr">
         <is>
-          <t>Asansör ve tesisat şaftı</t>
+          <t>Yemek alanı</t>
         </is>
       </c>
       <c r="C37" s="24" t="n">
-        <v>5</v>
+        <v>20.3</v>
       </c>
       <c r="D37" s="25" t="inlineStr">
         <is>
+          <t>DK-02</t>
+        </is>
+      </c>
+      <c r="E37" s="25" t="inlineStr">
+        <is>
+          <t>SP-03</t>
+        </is>
+      </c>
+      <c r="F37" s="25" t="inlineStr">
+        <is>
+          <t>DV-01 + DV-04</t>
+        </is>
+      </c>
+      <c r="G37" s="25" t="inlineStr">
+        <is>
+          <t>TV-01</t>
+        </is>
+      </c>
+      <c r="H37" s="25" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E37" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F37" s="25" t="inlineStr">
-        <is>
-          <t>DV-06</t>
-        </is>
-      </c>
-      <c r="G37" s="25" t="inlineStr">
-        <is>
-          <t>TV-05</t>
-        </is>
-      </c>
-      <c r="H37" s="25" t="inlineStr">
-        <is>
-          <t>Asansör kabin kapısı</t>
-        </is>
-      </c>
       <c r="I37" s="25" t="inlineStr">
         <is>
-          <t>DG-07</t>
+          <t>DG-02</t>
         </is>
       </c>
       <c r="J37" s="25" t="inlineStr">
         <is>
-          <t>EL-05</t>
+          <t>EL-04</t>
         </is>
       </c>
       <c r="K37" s="25" t="inlineStr">
         <is>
-          <t>MK-08</t>
+          <t>MK-01 + MK-03</t>
         </is>
       </c>
       <c r="L37" s="25" t="inlineStr">
@@ -4963,7 +5041,7 @@
       </c>
       <c r="M37" s="26" t="inlineStr">
         <is>
-          <t>Asansör kuyusu ve tesisat şaftı; şaft yangın durdurucu ile katlarda kesilir.</t>
+          <t>Salon ve mutfakla açık plan; 8 kişilik masa, büfe; güneyde 360 cm kaldır-sür.</t>
         </is>
       </c>
     </row>
@@ -4975,25 +5053,25 @@
       </c>
       <c r="B38" s="23" t="inlineStr">
         <is>
-          <t>Koridor</t>
+          <t>Mutfak (adalı)</t>
         </is>
       </c>
       <c r="C38" s="24" t="n">
-        <v>8</v>
+        <v>33.3</v>
       </c>
       <c r="D38" s="25" t="inlineStr">
         <is>
-          <t>DK-02</t>
+          <t>DK-01</t>
         </is>
       </c>
       <c r="E38" s="25" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>SP-04</t>
         </is>
       </c>
       <c r="F38" s="25" t="inlineStr">
         <is>
-          <t>DV-01</t>
+          <t>DV-02 + DV-01</t>
         </is>
       </c>
       <c r="G38" s="25" t="inlineStr">
@@ -5003,32 +5081,32 @@
       </c>
       <c r="H38" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KP-04</t>
         </is>
       </c>
       <c r="I38" s="25" t="inlineStr">
         <is>
-          <t>DG-07</t>
+          <t>DG-01 + DG-02</t>
         </is>
       </c>
       <c r="J38" s="25" t="inlineStr">
         <is>
-          <t>EL-04</t>
+          <t>EL-03</t>
         </is>
       </c>
       <c r="K38" s="25" t="inlineStr">
         <is>
-          <t>MK-01</t>
+          <t>MK-01 + MK-05</t>
         </is>
       </c>
       <c r="L38" s="25" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>ST-05</t>
         </is>
       </c>
       <c r="M38" s="26" t="inlineStr">
         <is>
-          <t>Misafir süitine ve ofise erişim; net genişlik 2,45 m.</t>
+          <t>Ada tezgah (ocak + kahvaltı barı), doğu duvarında eviye tezgahı; pergolaya 540 cm kaldır-sür.</t>
         </is>
       </c>
     </row>
@@ -5040,25 +5118,25 @@
       </c>
       <c r="B39" s="23" t="inlineStr">
         <is>
-          <t>Misafir yatak odası (süit)</t>
+          <t>Servis koridoru</t>
         </is>
       </c>
       <c r="C39" s="24" t="n">
-        <v>18.3</v>
+        <v>8.1</v>
       </c>
       <c r="D39" s="25" t="inlineStr">
         <is>
-          <t>DK-03</t>
+          <t>DK-01</t>
         </is>
       </c>
       <c r="E39" s="25" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="F39" s="25" t="inlineStr">
         <is>
-          <t>DV-01 + DV-04</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G39" s="25" t="inlineStr">
@@ -5068,22 +5146,22 @@
       </c>
       <c r="H39" s="25" t="inlineStr">
         <is>
-          <t>KP-02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I39" s="25" t="inlineStr">
         <is>
-          <t>DG-01 + DG-05 + DG-06</t>
+          <t>DG-07</t>
         </is>
       </c>
       <c r="J39" s="25" t="inlineStr">
         <is>
-          <t>EL-01</t>
+          <t>EL-04</t>
         </is>
       </c>
       <c r="K39" s="25" t="inlineStr">
         <is>
-          <t>MK-01 + MK-03</t>
+          <t>MK-01</t>
         </is>
       </c>
       <c r="L39" s="25" t="inlineStr">
@@ -5093,7 +5171,7 @@
       </c>
       <c r="M39" s="26" t="inlineStr">
         <is>
-          <t>Giyinme nişi ve ensuite banyo ile süit kurgusu.</t>
+          <t>Garaj, WC, kiler ve mutfağa servis koridoru; net 1,25 m.</t>
         </is>
       </c>
     </row>
@@ -5105,60 +5183,60 @@
       </c>
       <c r="B40" s="23" t="inlineStr">
         <is>
-          <t>Misafir banyosu</t>
+          <t>Garaj (2 araç)</t>
         </is>
       </c>
       <c r="C40" s="24" t="n">
-        <v>5.8</v>
+        <v>31.1</v>
       </c>
       <c r="D40" s="25" t="inlineStr">
         <is>
-          <t>DK-04</t>
+          <t>DK-06</t>
         </is>
       </c>
       <c r="E40" s="25" t="inlineStr">
         <is>
-          <t>SP-05</t>
+          <t>SP-04</t>
         </is>
       </c>
       <c r="F40" s="25" t="inlineStr">
         <is>
-          <t>DV-02</t>
+          <t>DV-06</t>
         </is>
       </c>
       <c r="G40" s="25" t="inlineStr">
         <is>
-          <t>TV-03</t>
+          <t>TV-05</t>
         </is>
       </c>
       <c r="H40" s="25" t="inlineStr">
         <is>
-          <t>KP-03</t>
+          <t>KP-06</t>
         </is>
       </c>
       <c r="I40" s="25" t="inlineStr">
         <is>
-          <t>DG-01</t>
+          <t>DG-01 (yüksek)</t>
         </is>
       </c>
       <c r="J40" s="25" t="inlineStr">
         <is>
-          <t>EL-02</t>
+          <t>EL-08</t>
         </is>
       </c>
       <c r="K40" s="25" t="inlineStr">
         <is>
-          <t>MK-02 + MK-04</t>
+          <t>MK-08</t>
         </is>
       </c>
       <c r="L40" s="25" t="inlineStr">
         <is>
-          <t>ST-02</t>
+          <t>ST-07</t>
         </is>
       </c>
       <c r="M40" s="26" t="inlineStr">
         <is>
-          <t>Duş nişi gizli süzgeçli, cam duş kabini.</t>
+          <t>2 araç; eve EI30 kapı ile bağlanır; elektrikli araç şarj hattı; seksiyonel kapı 480 × 240.</t>
         </is>
       </c>
     </row>
@@ -5170,35 +5248,35 @@
       </c>
       <c r="B41" s="23" t="inlineStr">
         <is>
-          <t>Misafir giyinme odası</t>
+          <t>Misafir WC</t>
         </is>
       </c>
       <c r="C41" s="24" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>DK-08</t>
+          <t>DK-04</t>
         </is>
       </c>
       <c r="E41" s="25" t="inlineStr">
         <is>
-          <t>SP-04</t>
+          <t>SP-05</t>
         </is>
       </c>
       <c r="F41" s="25" t="inlineStr">
         <is>
-          <t>DV-01</t>
+          <t>DV-02</t>
         </is>
       </c>
       <c r="G41" s="25" t="inlineStr">
         <is>
-          <t>TV-05</t>
+          <t>TV-03</t>
         </is>
       </c>
       <c r="H41" s="25" t="inlineStr">
         <is>
-          <t>KP-04</t>
+          <t>KP-03</t>
         </is>
       </c>
       <c r="I41" s="25" t="inlineStr">
@@ -5208,22 +5286,22 @@
       </c>
       <c r="J41" s="25" t="inlineStr">
         <is>
-          <t>EL-05</t>
+          <t>EL-02</t>
         </is>
       </c>
       <c r="K41" s="25" t="inlineStr">
         <is>
-          <t>MK-01 + MK-04</t>
+          <t>MK-02 + MK-04</t>
         </is>
       </c>
       <c r="L41" s="25" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>ST-04</t>
         </is>
       </c>
       <c r="M41" s="26" t="inlineStr">
         <is>
-          <t>Misafir süiti giyinme odası; sensörlü dolap içi aydınlatma.</t>
+          <t>Misafir WC; servis koridorundan girilir, salondan görünmez.</t>
         </is>
       </c>
     </row>
@@ -5235,50 +5313,50 @@
       </c>
       <c r="B42" s="23" t="inlineStr">
         <is>
-          <t>Çalışma odası / ofis</t>
+          <t>Kiler</t>
         </is>
       </c>
       <c r="C42" s="24" t="n">
-        <v>16.7</v>
+        <v>4.5</v>
       </c>
       <c r="D42" s="25" t="inlineStr">
         <is>
-          <t>DK-03</t>
+          <t>DK-08</t>
         </is>
       </c>
       <c r="E42" s="25" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>SP-04</t>
         </is>
       </c>
       <c r="F42" s="25" t="inlineStr">
         <is>
-          <t>DV-01 + DV-04</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G42" s="25" t="inlineStr">
         <is>
-          <t>TV-01</t>
+          <t>TV-05</t>
         </is>
       </c>
       <c r="H42" s="25" t="inlineStr">
         <is>
-          <t>KP-02</t>
+          <t>KP-08</t>
         </is>
       </c>
       <c r="I42" s="25" t="inlineStr">
         <is>
-          <t>DG-01</t>
+          <t>DG-07</t>
         </is>
       </c>
       <c r="J42" s="25" t="inlineStr">
         <is>
-          <t>EL-01</t>
+          <t>EL-05</t>
         </is>
       </c>
       <c r="K42" s="25" t="inlineStr">
         <is>
-          <t>MK-01 + MK-03</t>
+          <t>MK-08</t>
         </is>
       </c>
       <c r="L42" s="25" t="inlineStr">
@@ -5288,7 +5366,7 @@
       </c>
       <c r="M42" s="26" t="inlineStr">
         <is>
-          <t>CAT6 data ve ayrı sigortalı priz hattı; kitaplık ankrajı.</t>
+          <t>Kiler: derin raflar, mutfağa yakın.</t>
         </is>
       </c>
     </row>
@@ -5300,60 +5378,60 @@
       </c>
       <c r="B43" s="23" t="inlineStr">
         <is>
-          <t>Üstü örtülü teras (barbekü)</t>
+          <t>Arka mutfak / servis girişi</t>
         </is>
       </c>
       <c r="C43" s="24" t="n">
-        <v>27.6</v>
+        <v>10.9</v>
       </c>
       <c r="D43" s="25" t="inlineStr">
         <is>
-          <t>DK-05</t>
+          <t>DK-01</t>
         </is>
       </c>
       <c r="E43" s="25" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>SP-04</t>
         </is>
       </c>
       <c r="F43" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DV-02 + DV-01</t>
         </is>
       </c>
       <c r="G43" s="25" t="inlineStr">
         <is>
-          <t>TV-04</t>
+          <t>TV-01</t>
         </is>
       </c>
       <c r="H43" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KP-02 + KP-09 (dış servis kapısı)</t>
         </is>
       </c>
       <c r="I43" s="25" t="inlineStr">
         <is>
-          <t>DG-02</t>
+          <t>DG-01</t>
         </is>
       </c>
       <c r="J43" s="25" t="inlineStr">
         <is>
-          <t>EL-06</t>
+          <t>EL-03</t>
         </is>
       </c>
       <c r="K43" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-01 + MK-05</t>
         </is>
       </c>
       <c r="L43" s="25" t="inlineStr">
         <is>
-          <t>ST-08</t>
+          <t>ST-05</t>
         </is>
       </c>
       <c r="M43" s="26" t="inlineStr">
         <is>
-          <t>Yaz mutfağı ve barbekü; su-atık hattı, dış priz, üstü örtülü.</t>
+          <t>Arka mutfak ve servis girişi: bulaşık, hazırlık, market girişi doğu yan bahçeden.</t>
         </is>
       </c>
     </row>
@@ -5372,25 +5450,25 @@
       </c>
       <c r="B45" s="23" t="inlineStr">
         <is>
-          <t>Ebeveyn yatak odası</t>
+          <t>Üst hol ve okuma köşesi</t>
         </is>
       </c>
       <c r="C45" s="24" t="n">
-        <v>29.6</v>
+        <v>20.8</v>
       </c>
       <c r="D45" s="25" t="inlineStr">
         <is>
-          <t>DK-03</t>
+          <t>DK-02</t>
         </is>
       </c>
       <c r="E45" s="25" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="F45" s="25" t="inlineStr">
         <is>
-          <t>DV-01 + DV-04</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G45" s="25" t="inlineStr">
@@ -5400,22 +5478,22 @@
       </c>
       <c r="H45" s="25" t="inlineStr">
         <is>
-          <t>KP-02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I45" s="25" t="inlineStr">
         <is>
-          <t>DG-01 + DG-05 + DG-06</t>
+          <t>DG-07</t>
         </is>
       </c>
       <c r="J45" s="25" t="inlineStr">
         <is>
-          <t>EL-01</t>
+          <t>EL-04</t>
         </is>
       </c>
       <c r="K45" s="25" t="inlineStr">
         <is>
-          <t>MK-01 + MK-03</t>
+          <t>MK-01</t>
         </is>
       </c>
       <c r="L45" s="25" t="inlineStr">
@@ -5425,7 +5503,7 @@
       </c>
       <c r="M45" s="26" t="inlineStr">
         <is>
-          <t>Giyinme ve banyo ile süit kurgusu; yatak başı çift yönlü anahtar.</t>
+          <t>Galeriye bakan okuma köşesi; cam korkuluk h=110.</t>
         </is>
       </c>
     </row>
@@ -5437,20 +5515,20 @@
       </c>
       <c r="B46" s="23" t="inlineStr">
         <is>
-          <t>Ebeveyn giyinme odası</t>
+          <t>Galeri boşluğu</t>
         </is>
       </c>
       <c r="C46" s="24" t="n">
-        <v>15.9</v>
+        <v>5.7</v>
       </c>
       <c r="D46" s="25" t="inlineStr">
         <is>
-          <t>DK-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E46" s="25" t="inlineStr">
         <is>
-          <t>SP-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F46" s="25" t="inlineStr">
@@ -5460,12 +5538,12 @@
       </c>
       <c r="G46" s="25" t="inlineStr">
         <is>
-          <t>TV-05</t>
+          <t>TV-01</t>
         </is>
       </c>
       <c r="H46" s="25" t="inlineStr">
         <is>
-          <t>KP-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I46" s="25" t="inlineStr">
@@ -5475,12 +5553,12 @@
       </c>
       <c r="J46" s="25" t="inlineStr">
         <is>
-          <t>EL-05</t>
+          <t>EL-04</t>
         </is>
       </c>
       <c r="K46" s="25" t="inlineStr">
         <is>
-          <t>MK-01 + MK-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L46" s="25" t="inlineStr">
@@ -5488,11 +5566,7 @@
           <t>ST-01</t>
         </is>
       </c>
-      <c r="M46" s="26" t="inlineStr">
-        <is>
-          <t>Ada dolap, sensörlü dolap içi aydınlatma, tam boy ayna.</t>
-        </is>
-      </c>
+      <c r="M46" s="26" t="inlineStr"/>
     </row>
     <row r="47" ht="32" customHeight="1">
       <c r="A47" s="22" t="inlineStr">
@@ -5502,62 +5576,58 @@
       </c>
       <c r="B47" s="23" t="inlineStr">
         <is>
-          <t>Ebeveyn banyosu</t>
+          <t>Merdiven</t>
         </is>
       </c>
       <c r="C47" s="24" t="n">
-        <v>14.1</v>
+        <v>11.4</v>
       </c>
       <c r="D47" s="25" t="inlineStr">
         <is>
-          <t>DK-04</t>
+          <t>DK-02</t>
         </is>
       </c>
       <c r="E47" s="25" t="inlineStr">
         <is>
-          <t>SP-05</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="F47" s="25" t="inlineStr">
         <is>
-          <t>DV-03</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G47" s="25" t="inlineStr">
         <is>
-          <t>TV-03</t>
+          <t>TV-02</t>
         </is>
       </c>
       <c r="H47" s="25" t="inlineStr">
         <is>
-          <t>KP-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I47" s="25" t="inlineStr">
         <is>
-          <t>DG-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J47" s="25" t="inlineStr">
         <is>
-          <t>EL-02</t>
+          <t>EL-04</t>
         </is>
       </c>
       <c r="K47" s="25" t="inlineStr">
         <is>
-          <t>MK-02 + MK-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L47" s="25" t="inlineStr">
         <is>
-          <t>ST-03</t>
-        </is>
-      </c>
-      <c r="M47" s="26" t="inlineStr">
-        <is>
-          <t>Çift lavabo, serbest duran küvet, yağmurlama duş, ayna ısıtıcı.</t>
-        </is>
-      </c>
+          <t>ST-01</t>
+        </is>
+      </c>
+      <c r="M47" s="26" t="inlineStr"/>
     </row>
     <row r="48" ht="32" customHeight="1">
       <c r="A48" s="22" t="inlineStr">
@@ -5567,62 +5637,58 @@
       </c>
       <c r="B48" s="23" t="inlineStr">
         <is>
-          <t>Aile oturma odası / TV</t>
+          <t>Asansör</t>
         </is>
       </c>
       <c r="C48" s="24" t="n">
-        <v>26</v>
+        <v>3.8</v>
       </c>
       <c r="D48" s="25" t="inlineStr">
         <is>
-          <t>DK-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E48" s="25" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" s="25" t="inlineStr">
         <is>
-          <t>DV-01 + DV-04</t>
+          <t>DV-06</t>
         </is>
       </c>
       <c r="G48" s="25" t="inlineStr">
         <is>
-          <t>TV-01</t>
+          <t>TV-05</t>
         </is>
       </c>
       <c r="H48" s="25" t="inlineStr">
         <is>
+          <t>Asansör kat kapısı</t>
+        </is>
+      </c>
+      <c r="I48" s="25" t="inlineStr">
+        <is>
+          <t>DG-07</t>
+        </is>
+      </c>
+      <c r="J48" s="25" t="inlineStr">
+        <is>
+          <t>EL-05</t>
+        </is>
+      </c>
+      <c r="K48" s="25" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I48" s="25" t="inlineStr">
-        <is>
-          <t>DG-01</t>
-        </is>
-      </c>
-      <c r="J48" s="25" t="inlineStr">
-        <is>
-          <t>EL-04</t>
-        </is>
-      </c>
-      <c r="K48" s="25" t="inlineStr">
-        <is>
-          <t>MK-01 + MK-03</t>
-        </is>
-      </c>
       <c r="L48" s="25" t="inlineStr">
         <is>
           <t>ST-01</t>
         </is>
       </c>
-      <c r="M48" s="26" t="inlineStr">
-        <is>
-          <t>TV ünitesi için gömme kanal; senaryolu aydınlatma. Balkona sürme kapı.</t>
-        </is>
-      </c>
+      <c r="M48" s="26" t="inlineStr"/>
     </row>
     <row r="49" ht="32" customHeight="1">
       <c r="A49" s="22" t="inlineStr">
@@ -5632,62 +5698,58 @@
       </c>
       <c r="B49" s="23" t="inlineStr">
         <is>
-          <t>Çalışma odası / kütüphane</t>
+          <t>Tesisat şaftı</t>
         </is>
       </c>
       <c r="C49" s="24" t="n">
-        <v>17.1</v>
+        <v>0.9</v>
       </c>
       <c r="D49" s="25" t="inlineStr">
         <is>
-          <t>DK-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="E49" s="25" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F49" s="25" t="inlineStr">
         <is>
-          <t>DV-01 + DV-04</t>
+          <t>DV-06</t>
         </is>
       </c>
       <c r="G49" s="25" t="inlineStr">
         <is>
-          <t>TV-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H49" s="25" t="inlineStr">
         <is>
-          <t>KP-04</t>
+          <t>Servis kapağı</t>
         </is>
       </c>
       <c r="I49" s="25" t="inlineStr">
         <is>
-          <t>DG-01</t>
+          <t>DG-07</t>
         </is>
       </c>
       <c r="J49" s="25" t="inlineStr">
         <is>
-          <t>EL-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K49" s="25" t="inlineStr">
         <is>
-          <t>MK-01 + MK-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L49" s="25" t="inlineStr">
         <is>
-          <t>ST-01</t>
-        </is>
-      </c>
-      <c r="M49" s="26" t="inlineStr">
-        <is>
-          <t>Kitaplık ankrajı, okuma aydınlatması, data hattı.</t>
-        </is>
-      </c>
+          <t>Düşey tesisat</t>
+        </is>
+      </c>
+      <c r="M49" s="26" t="inlineStr"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="22" t="inlineStr">
@@ -5697,60 +5759,60 @@
       </c>
       <c r="B50" s="23" t="inlineStr">
         <is>
-          <t>Ebeveyn balkonu</t>
+          <t>Yatak odası 2</t>
         </is>
       </c>
       <c r="C50" s="24" t="n">
-        <v>14.6</v>
+        <v>25.7</v>
       </c>
       <c r="D50" s="25" t="inlineStr">
         <is>
-          <t>DK-05</t>
+          <t>DK-03</t>
         </is>
       </c>
       <c r="E50" s="25" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="F50" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DV-01 + DV-04</t>
         </is>
       </c>
       <c r="G50" s="25" t="inlineStr">
         <is>
-          <t>TV-04</t>
+          <t>TV-01</t>
         </is>
       </c>
       <c r="H50" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KP-02</t>
         </is>
       </c>
       <c r="I50" s="25" t="inlineStr">
         <is>
-          <t>DG-02</t>
+          <t>DG-01 + DG-05 + DG-06</t>
         </is>
       </c>
       <c r="J50" s="25" t="inlineStr">
         <is>
-          <t>EL-06</t>
+          <t>EL-01</t>
         </is>
       </c>
       <c r="K50" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-01 + MK-03</t>
         </is>
       </c>
       <c r="L50" s="25" t="inlineStr">
         <is>
-          <t>ST-08</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="M50" s="26" t="inlineStr">
         <is>
-          <t>Ebeveyn ve aile oturma odasına açılan balkon; cam korkuluk, gizli drenaj.</t>
+          <t>Süit: hol + banyo; kuzey ve batı pencereli köşe oda.</t>
         </is>
       </c>
     </row>
@@ -5762,60 +5824,60 @@
       </c>
       <c r="B51" s="23" t="inlineStr">
         <is>
-          <t>Üst hol, merdiven ve galeri</t>
+          <t>Yatak odası 2 banyosu</t>
         </is>
       </c>
       <c r="C51" s="24" t="n">
-        <v>29.7</v>
+        <v>5.1</v>
       </c>
       <c r="D51" s="25" t="inlineStr">
         <is>
-          <t>DK-02</t>
+          <t>DK-04</t>
         </is>
       </c>
       <c r="E51" s="25" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>SP-05</t>
         </is>
       </c>
       <c r="F51" s="25" t="inlineStr">
         <is>
-          <t>DV-01</t>
+          <t>DV-02</t>
         </is>
       </c>
       <c r="G51" s="25" t="inlineStr">
         <is>
-          <t>TV-01</t>
+          <t>TV-03</t>
         </is>
       </c>
       <c r="H51" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KP-03</t>
         </is>
       </c>
       <c r="I51" s="25" t="inlineStr">
         <is>
-          <t>DG-01</t>
+          <t>DG-01 (buzlu)</t>
         </is>
       </c>
       <c r="J51" s="25" t="inlineStr">
         <is>
-          <t>EL-04</t>
+          <t>EL-02</t>
         </is>
       </c>
       <c r="K51" s="25" t="inlineStr">
         <is>
-          <t>MK-01</t>
+          <t>MK-02 + MK-04</t>
         </is>
       </c>
       <c r="L51" s="25" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>ST-02</t>
         </is>
       </c>
       <c r="M51" s="26" t="inlineStr">
         <is>
-          <t>Galeri boşluğu çevresinde temperli cam korkuluk h=110 cm.</t>
+          <t>Duş, lavabo, asma klozet (zemin kattaki misafir banyosunun üstünde).</t>
         </is>
       </c>
     </row>
@@ -5827,35 +5889,35 @@
       </c>
       <c r="B52" s="23" t="inlineStr">
         <is>
-          <t>Çamaşır ve ütü nişi</t>
+          <t>Yatak odası 2 holü</t>
         </is>
       </c>
       <c r="C52" s="24" t="n">
-        <v>6</v>
+        <v>3.4</v>
       </c>
       <c r="D52" s="25" t="inlineStr">
         <is>
-          <t>DK-04</t>
+          <t>DK-03</t>
         </is>
       </c>
       <c r="E52" s="25" t="inlineStr">
         <is>
-          <t>SP-05</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="F52" s="25" t="inlineStr">
         <is>
-          <t>DV-05</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G52" s="25" t="inlineStr">
         <is>
-          <t>TV-03</t>
+          <t>TV-01</t>
         </is>
       </c>
       <c r="H52" s="25" t="inlineStr">
         <is>
-          <t>KP-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I52" s="25" t="inlineStr">
@@ -5865,22 +5927,22 @@
       </c>
       <c r="J52" s="25" t="inlineStr">
         <is>
-          <t>EL-02</t>
+          <t>EL-04</t>
         </is>
       </c>
       <c r="K52" s="25" t="inlineStr">
         <is>
-          <t>MK-04</t>
+          <t>MK-01</t>
         </is>
       </c>
       <c r="L52" s="25" t="inlineStr">
         <is>
-          <t>ST-06</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="M52" s="26" t="inlineStr">
         <is>
-          <t>Üst kat çamaşır nişi; makine bağlantısı, yer süzgeci, taşma sensörü.</t>
+          <t>Yatak 2 holü, gömme dolap.</t>
         </is>
       </c>
     </row>
@@ -5892,60 +5954,60 @@
       </c>
       <c r="B53" s="23" t="inlineStr">
         <is>
-          <t>Yatak odası 4</t>
+          <t>Ebeveyn banyosu</t>
         </is>
       </c>
       <c r="C53" s="24" t="n">
-        <v>19.6</v>
+        <v>17.6</v>
       </c>
       <c r="D53" s="25" t="inlineStr">
         <is>
-          <t>DK-03</t>
+          <t>DK-04</t>
         </is>
       </c>
       <c r="E53" s="25" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>SP-05</t>
         </is>
       </c>
       <c r="F53" s="25" t="inlineStr">
         <is>
-          <t>DV-01 + DV-04</t>
+          <t>DV-03</t>
         </is>
       </c>
       <c r="G53" s="25" t="inlineStr">
         <is>
-          <t>TV-01</t>
+          <t>TV-03</t>
         </is>
       </c>
       <c r="H53" s="25" t="inlineStr">
         <is>
-          <t>KP-02</t>
+          <t>KP-03</t>
         </is>
       </c>
       <c r="I53" s="25" t="inlineStr">
         <is>
-          <t>DG-01 + DG-05 + DG-06</t>
+          <t>DG-01 (buzlu, geniş)</t>
         </is>
       </c>
       <c r="J53" s="25" t="inlineStr">
         <is>
-          <t>EL-01</t>
+          <t>EL-02</t>
         </is>
       </c>
       <c r="K53" s="25" t="inlineStr">
         <is>
-          <t>MK-01 + MK-03</t>
+          <t>MK-02 + MK-04</t>
         </is>
       </c>
       <c r="L53" s="25" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>ST-03</t>
         </is>
       </c>
       <c r="M53" s="26" t="inlineStr">
         <is>
-          <t>Gömme gardırop; ortak banyoya yakın.</t>
+          <t>Serbest küvet, çift lavabo, duş, asma klozet.</t>
         </is>
       </c>
     </row>
@@ -5957,11 +6019,11 @@
       </c>
       <c r="B54" s="23" t="inlineStr">
         <is>
-          <t>Yatak odası 2</t>
+          <t>Ebeveyn giyinme odası</t>
         </is>
       </c>
       <c r="C54" s="24" t="n">
-        <v>19.3</v>
+        <v>16</v>
       </c>
       <c r="D54" s="25" t="inlineStr">
         <is>
@@ -5975,7 +6037,7 @@
       </c>
       <c r="F54" s="25" t="inlineStr">
         <is>
-          <t>DV-01 + DV-04</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G54" s="25" t="inlineStr">
@@ -5990,7 +6052,7 @@
       </c>
       <c r="I54" s="25" t="inlineStr">
         <is>
-          <t>DG-01 + DG-05 + DG-06</t>
+          <t>DG-07</t>
         </is>
       </c>
       <c r="J54" s="25" t="inlineStr">
@@ -6000,7 +6062,7 @@
       </c>
       <c r="K54" s="25" t="inlineStr">
         <is>
-          <t>MK-01 + MK-03</t>
+          <t>MK-01 + MK-04</t>
         </is>
       </c>
       <c r="L54" s="25" t="inlineStr">
@@ -6010,7 +6072,7 @@
       </c>
       <c r="M54" s="26" t="inlineStr">
         <is>
-          <t>Ensuite banyolu; gömme gardırop.</t>
+          <t>Süit girişi ve giyinme odası; ada dolap, tavana kadar gardırop.</t>
         </is>
       </c>
     </row>
@@ -6022,60 +6084,60 @@
       </c>
       <c r="B55" s="23" t="inlineStr">
         <is>
-          <t>Yatak odası 2 banyosu</t>
+          <t>Ebeveyn yatak odası</t>
         </is>
       </c>
       <c r="C55" s="24" t="n">
-        <v>7.6</v>
+        <v>33.7</v>
       </c>
       <c r="D55" s="25" t="inlineStr">
         <is>
-          <t>DK-04</t>
+          <t>DK-03</t>
         </is>
       </c>
       <c r="E55" s="25" t="inlineStr">
         <is>
-          <t>SP-05</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="F55" s="25" t="inlineStr">
         <is>
-          <t>DV-02</t>
+          <t>DV-01 + DV-04</t>
         </is>
       </c>
       <c r="G55" s="25" t="inlineStr">
         <is>
-          <t>TV-03</t>
+          <t>TV-01</t>
         </is>
       </c>
       <c r="H55" s="25" t="inlineStr">
         <is>
-          <t>KP-03</t>
+          <t>KP-02</t>
         </is>
       </c>
       <c r="I55" s="25" t="inlineStr">
         <is>
-          <t>DG-01</t>
+          <t>DG-02 + DG-05</t>
         </is>
       </c>
       <c r="J55" s="25" t="inlineStr">
         <is>
-          <t>EL-02</t>
+          <t>EL-01</t>
         </is>
       </c>
       <c r="K55" s="25" t="inlineStr">
         <is>
-          <t>MK-02 + MK-04</t>
+          <t>MK-01 + MK-03</t>
         </is>
       </c>
       <c r="L55" s="25" t="inlineStr">
         <is>
-          <t>ST-02</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="M55" s="26" t="inlineStr">
         <is>
-          <t>Duş kabinli, gizli süzgeçli.</t>
+          <t>Balkona 420 cm kaldır-sür; batıda pencere, oturma köşesi.</t>
         </is>
       </c>
     </row>
@@ -6087,50 +6149,50 @@
       </c>
       <c r="B56" s="23" t="inlineStr">
         <is>
-          <t>Asansör ve tesisat şaftı</t>
+          <t>Yatak odası 4</t>
         </is>
       </c>
       <c r="C56" s="24" t="n">
-        <v>5</v>
+        <v>15.2</v>
       </c>
       <c r="D56" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DK-03</t>
         </is>
       </c>
       <c r="E56" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="F56" s="25" t="inlineStr">
         <is>
-          <t>DV-06</t>
+          <t>DV-01 + DV-04</t>
         </is>
       </c>
       <c r="G56" s="25" t="inlineStr">
         <is>
-          <t>TV-05</t>
+          <t>TV-01</t>
         </is>
       </c>
       <c r="H56" s="25" t="inlineStr">
         <is>
-          <t>Asansör kabin kapısı</t>
+          <t>KP-02</t>
         </is>
       </c>
       <c r="I56" s="25" t="inlineStr">
         <is>
-          <t>DG-07</t>
+          <t>DG-01 + DG-05 + DG-06</t>
         </is>
       </c>
       <c r="J56" s="25" t="inlineStr">
         <is>
-          <t>EL-05</t>
+          <t>EL-01</t>
         </is>
       </c>
       <c r="K56" s="25" t="inlineStr">
         <is>
-          <t>MK-08</t>
+          <t>MK-01 + MK-03</t>
         </is>
       </c>
       <c r="L56" s="25" t="inlineStr">
@@ -6140,7 +6202,7 @@
       </c>
       <c r="M56" s="26" t="inlineStr">
         <is>
-          <t>Asansör kuyusu ve tesisat şaftı.</t>
+          <t>Güney pencereli; kendi banyosu var.</t>
         </is>
       </c>
     </row>
@@ -6152,35 +6214,35 @@
       </c>
       <c r="B57" s="23" t="inlineStr">
         <is>
-          <t>Koridor</t>
+          <t>Yatak odası 4 banyosu</t>
         </is>
       </c>
       <c r="C57" s="24" t="n">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="D57" s="25" t="inlineStr">
         <is>
-          <t>DK-02</t>
+          <t>DK-04</t>
         </is>
       </c>
       <c r="E57" s="25" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>SP-05</t>
         </is>
       </c>
       <c r="F57" s="25" t="inlineStr">
         <is>
-          <t>DV-01</t>
+          <t>DV-02</t>
         </is>
       </c>
       <c r="G57" s="25" t="inlineStr">
         <is>
-          <t>TV-01</t>
+          <t>TV-03</t>
         </is>
       </c>
       <c r="H57" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KP-03</t>
         </is>
       </c>
       <c r="I57" s="25" t="inlineStr">
@@ -6190,22 +6252,22 @@
       </c>
       <c r="J57" s="25" t="inlineStr">
         <is>
-          <t>EL-04</t>
+          <t>EL-02</t>
         </is>
       </c>
       <c r="K57" s="25" t="inlineStr">
         <is>
-          <t>MK-01</t>
+          <t>MK-02 + MK-04</t>
         </is>
       </c>
       <c r="L57" s="25" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>ST-02</t>
         </is>
       </c>
       <c r="M57" s="26" t="inlineStr">
         <is>
-          <t>Net genişlik 2,45 m; ortak banyo ve yatak odalarına erişim.</t>
+          <t>Duş, lavabo, asma klozet; şafta bitişik, mekanik havalandırma.</t>
         </is>
       </c>
     </row>
@@ -6217,60 +6279,60 @@
       </c>
       <c r="B58" s="23" t="inlineStr">
         <is>
-          <t>Ortak banyo</t>
+          <t>Koridor</t>
         </is>
       </c>
       <c r="C58" s="24" t="n">
-        <v>8.9</v>
+        <v>11.7</v>
       </c>
       <c r="D58" s="25" t="inlineStr">
         <is>
-          <t>DK-04</t>
+          <t>DK-02</t>
         </is>
       </c>
       <c r="E58" s="25" t="inlineStr">
         <is>
-          <t>SP-05</t>
+          <t>SP-02</t>
         </is>
       </c>
       <c r="F58" s="25" t="inlineStr">
         <is>
-          <t>DV-02</t>
+          <t>DV-01</t>
         </is>
       </c>
       <c r="G58" s="25" t="inlineStr">
         <is>
-          <t>TV-03</t>
+          <t>TV-01</t>
         </is>
       </c>
       <c r="H58" s="25" t="inlineStr">
         <is>
-          <t>KP-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I58" s="25" t="inlineStr">
         <is>
-          <t>DG-01</t>
+          <t>DG-07</t>
         </is>
       </c>
       <c r="J58" s="25" t="inlineStr">
         <is>
-          <t>EL-02</t>
+          <t>EL-04</t>
         </is>
       </c>
       <c r="K58" s="25" t="inlineStr">
         <is>
-          <t>MK-02 + MK-04</t>
+          <t>MK-01</t>
         </is>
       </c>
       <c r="L58" s="25" t="inlineStr">
         <is>
-          <t>ST-02</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="M58" s="26" t="inlineStr">
         <is>
-          <t>Küvet + duş; çocuk kullanımına uygun armatür yüksekliği.</t>
+          <t>Yatak 3, çamaşır odası ve aile salonuna koridor; çatı arası kapağı burada.</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6348,7 @@
         </is>
       </c>
       <c r="C59" s="24" t="n">
-        <v>18.8</v>
+        <v>23.3</v>
       </c>
       <c r="D59" s="25" t="inlineStr">
         <is>
@@ -6335,7 +6397,7 @@
       </c>
       <c r="M59" s="26" t="inlineStr">
         <is>
-          <t>Giyinme odası ile birlikte kullanılır.</t>
+          <t>Süit: giyinme odası üzerinden banyo; kuzey ve doğu pencereli.</t>
         </is>
       </c>
     </row>
@@ -6351,16 +6413,16 @@
         </is>
       </c>
       <c r="C60" s="24" t="n">
-        <v>8.5</v>
+        <v>6</v>
       </c>
       <c r="D60" s="25" t="inlineStr">
         <is>
-          <t>DK-08</t>
+          <t>DK-03</t>
         </is>
       </c>
       <c r="E60" s="25" t="inlineStr">
         <is>
-          <t>SP-04</t>
+          <t>SP-01</t>
         </is>
       </c>
       <c r="F60" s="25" t="inlineStr">
@@ -6370,22 +6432,22 @@
       </c>
       <c r="G60" s="25" t="inlineStr">
         <is>
-          <t>TV-05</t>
+          <t>TV-01</t>
         </is>
       </c>
       <c r="H60" s="25" t="inlineStr">
         <is>
-          <t>KP-04</t>
+          <t>KP-02</t>
         </is>
       </c>
       <c r="I60" s="25" t="inlineStr">
         <is>
-          <t>DG-01</t>
+          <t>DG-07</t>
         </is>
       </c>
       <c r="J60" s="25" t="inlineStr">
         <is>
-          <t>EL-05</t>
+          <t>EL-01</t>
         </is>
       </c>
       <c r="K60" s="25" t="inlineStr">
@@ -6398,11 +6460,7 @@
           <t>ST-01</t>
         </is>
       </c>
-      <c r="M60" s="26" t="inlineStr">
-        <is>
-          <t>Gömme dolap sistemi.</t>
-        </is>
-      </c>
+      <c r="M60" s="26" t="inlineStr"/>
     </row>
     <row r="61" ht="32" customHeight="1">
       <c r="A61" s="22" t="inlineStr">
@@ -6412,60 +6470,60 @@
       </c>
       <c r="B61" s="23" t="inlineStr">
         <is>
-          <t>Yatak odası 5</t>
+          <t>Yatak odası 3 banyosu</t>
         </is>
       </c>
       <c r="C61" s="24" t="n">
-        <v>17.8</v>
+        <v>7.3</v>
       </c>
       <c r="D61" s="25" t="inlineStr">
         <is>
-          <t>DK-03</t>
+          <t>DK-04</t>
         </is>
       </c>
       <c r="E61" s="25" t="inlineStr">
         <is>
-          <t>SP-01</t>
+          <t>SP-05</t>
         </is>
       </c>
       <c r="F61" s="25" t="inlineStr">
         <is>
-          <t>DV-01 + DV-04</t>
+          <t>DV-02</t>
         </is>
       </c>
       <c r="G61" s="25" t="inlineStr">
         <is>
-          <t>TV-01</t>
+          <t>TV-03</t>
         </is>
       </c>
       <c r="H61" s="25" t="inlineStr">
         <is>
-          <t>KP-02</t>
+          <t>KP-03</t>
         </is>
       </c>
       <c r="I61" s="25" t="inlineStr">
         <is>
-          <t>DG-01 + DG-05 + DG-06</t>
+          <t>DG-01</t>
         </is>
       </c>
       <c r="J61" s="25" t="inlineStr">
         <is>
-          <t>EL-01</t>
+          <t>EL-02</t>
         </is>
       </c>
       <c r="K61" s="25" t="inlineStr">
         <is>
-          <t>MK-01 + MK-03</t>
+          <t>MK-02 + MK-04</t>
         </is>
       </c>
       <c r="L61" s="25" t="inlineStr">
         <is>
-          <t>ST-01</t>
+          <t>ST-02 + küvet</t>
         </is>
       </c>
       <c r="M61" s="26" t="inlineStr">
         <is>
-          <t>Gömme gardırop; çalışma masası için priz + data.</t>
+          <t>Küvet, lavabo, asma klozet; doğuda yüksek pencere.</t>
         </is>
       </c>
     </row>
@@ -6477,84 +6535,214 @@
       </c>
       <c r="B62" s="23" t="inlineStr">
         <is>
-          <t>Balkon 2</t>
+          <t>Çamaşır ve ütü odası</t>
         </is>
       </c>
       <c r="C62" s="24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D62" s="25" t="inlineStr">
         <is>
-          <t>DK-05</t>
+          <t>DK-04</t>
         </is>
       </c>
       <c r="E62" s="25" t="inlineStr">
         <is>
-          <t>SP-02</t>
+          <t>SP-05</t>
         </is>
       </c>
       <c r="F62" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>DV-02</t>
         </is>
       </c>
       <c r="G62" s="25" t="inlineStr">
         <is>
-          <t>TV-04</t>
+          <t>TV-03</t>
         </is>
       </c>
       <c r="H62" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>KP-03</t>
         </is>
       </c>
       <c r="I62" s="25" t="inlineStr">
         <is>
-          <t>DG-02</t>
+          <t>DG-07</t>
         </is>
       </c>
       <c r="J62" s="25" t="inlineStr">
         <is>
-          <t>EL-06</t>
+          <t>EL-02</t>
         </is>
       </c>
       <c r="K62" s="25" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>MK-02 + MK-04</t>
         </is>
       </c>
       <c r="L62" s="25" t="inlineStr">
         <is>
-          <t>ST-08</t>
+          <t>ST-06</t>
         </is>
       </c>
       <c r="M62" s="26" t="inlineStr">
         <is>
-          <t>Yatak odası 5'e açılan balkon; korkuluk h=110 cm, tırmanmaya elverişsiz.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="27" t="n"/>
-      <c r="B63" s="28" t="inlineStr">
+          <t>Çamaşır + kurutma makinesi, ütü, tezgah; yer süzgeci ve taşma sensörü.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="32" customHeight="1">
+      <c r="A63" s="22" t="inlineStr">
+        <is>
+          <t>K-19</t>
+        </is>
+      </c>
+      <c r="B63" s="23" t="inlineStr">
+        <is>
+          <t>Aile WC</t>
+        </is>
+      </c>
+      <c r="C63" s="24" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="D63" s="25" t="inlineStr">
+        <is>
+          <t>DK-04</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="inlineStr">
+        <is>
+          <t>SP-05</t>
+        </is>
+      </c>
+      <c r="F63" s="25" t="inlineStr">
+        <is>
+          <t>DV-02</t>
+        </is>
+      </c>
+      <c r="G63" s="25" t="inlineStr">
+        <is>
+          <t>TV-03</t>
+        </is>
+      </c>
+      <c r="H63" s="25" t="inlineStr">
+        <is>
+          <t>KP-03</t>
+        </is>
+      </c>
+      <c r="I63" s="25" t="inlineStr">
+        <is>
+          <t>DG-01</t>
+        </is>
+      </c>
+      <c r="J63" s="25" t="inlineStr">
+        <is>
+          <t>EL-02</t>
+        </is>
+      </c>
+      <c r="K63" s="25" t="inlineStr">
+        <is>
+          <t>MK-02 + MK-04</t>
+        </is>
+      </c>
+      <c r="L63" s="25" t="inlineStr">
+        <is>
+          <t>ST-04</t>
+        </is>
+      </c>
+      <c r="M63" s="26" t="inlineStr">
+        <is>
+          <t>Aile salonuna hizmet eden WC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="32" customHeight="1">
+      <c r="A64" s="22" t="inlineStr">
+        <is>
+          <t>K-20</t>
+        </is>
+      </c>
+      <c r="B64" s="23" t="inlineStr">
+        <is>
+          <t>Aile oturma odası</t>
+        </is>
+      </c>
+      <c r="C64" s="24" t="n">
+        <v>33.3</v>
+      </c>
+      <c r="D64" s="25" t="inlineStr">
+        <is>
+          <t>DK-03</t>
+        </is>
+      </c>
+      <c r="E64" s="25" t="inlineStr">
+        <is>
+          <t>SP-01</t>
+        </is>
+      </c>
+      <c r="F64" s="25" t="inlineStr">
+        <is>
+          <t>DV-01 + DV-04</t>
+        </is>
+      </c>
+      <c r="G64" s="25" t="inlineStr">
+        <is>
+          <t>TV-01</t>
+        </is>
+      </c>
+      <c r="H64" s="25" t="inlineStr">
+        <is>
+          <t>KP-02</t>
+        </is>
+      </c>
+      <c r="I64" s="25" t="inlineStr">
+        <is>
+          <t>DG-01 + DG-02</t>
+        </is>
+      </c>
+      <c r="J64" s="25" t="inlineStr">
+        <is>
+          <t>EL-04</t>
+        </is>
+      </c>
+      <c r="K64" s="25" t="inlineStr">
+        <is>
+          <t>MK-01 + MK-03</t>
+        </is>
+      </c>
+      <c r="L64" s="25" t="inlineStr">
+        <is>
+          <t>ST-01</t>
+        </is>
+      </c>
+      <c r="M64" s="26" t="inlineStr">
+        <is>
+          <t>Aile oturma / TV odası; balkona 540 cm kaldır-sür, doğuda pencere.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="27" t="n"/>
+      <c r="B65" s="28" t="inlineStr">
         <is>
           <t>TOPLAM NET ALAN</t>
         </is>
       </c>
-      <c r="C63" s="29">
-        <f>SUM(C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C23,C24,C25,C26,C28,C29,C30,C31,C32,C33,C34,C35,C36,C37,C38,C39,C40,C41,C42,C43,C45,C46,C47,C48,C49,C50,C51,C52,C53,C54,C55,C56,C57,C58,C59,C60,C61,C62)</f>
+      <c r="C65" s="29">
+        <f>SUM(C6,C7,C8,C9,C10,C11,C12,C13,C14,C15,C16,C17,C18,C19,C20,C21,C22,C23,C24,C25,C26,C28,C29,C30,C31,C32,C33,C34,C35,C36,C37,C38,C39,C40,C41,C42,C43,C45,C46,C47,C48,C49,C50,C51,C52,C53,C54,C55,C56,C57,C58,C59,C60,C61,C62,C63,C64)</f>
         <v/>
       </c>
-      <c r="D63" s="28" t="n"/>
-      <c r="E63" s="28" t="n"/>
-      <c r="F63" s="28" t="n"/>
-      <c r="G63" s="28" t="n"/>
-      <c r="H63" s="28" t="n"/>
-      <c r="I63" s="28" t="n"/>
-      <c r="J63" s="28" t="n"/>
-      <c r="K63" s="28" t="n"/>
-      <c r="L63" s="28" t="n"/>
-      <c r="M63" s="28" t="n"/>
+      <c r="D65" s="28" t="n"/>
+      <c r="E65" s="28" t="n"/>
+      <c r="F65" s="28" t="n"/>
+      <c r="G65" s="28" t="n"/>
+      <c r="H65" s="28" t="n"/>
+      <c r="I65" s="28" t="n"/>
+      <c r="J65" s="28" t="n"/>
+      <c r="K65" s="28" t="n"/>
+      <c r="L65" s="28" t="n"/>
+      <c r="M65" s="28" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -6575,7 +6763,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D88"/>
+  <dimension ref="A1:D89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7255,7 +7443,7 @@
       </c>
       <c r="C40" s="9" t="inlineStr">
         <is>
-          <t>Çelik iskelet, dış cephe uyumlu kompozit/ahşap kaplama, 110×220 cm, ısı-ses yalıtımlı, akıllı kilit.</t>
+          <t>Çelik iskelet, dış cephe uyumlu kompozit/ahşap kaplama, 110×240 cm, ısı-ses yalıtımlı, akıllı kilit.</t>
         </is>
       </c>
       <c r="D40" s="31" t="inlineStr">
@@ -7272,7 +7460,7 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>Lake iç kapı 90×220</t>
+          <t>Lake iç kapı 90×210</t>
         </is>
       </c>
       <c r="C41" s="9" t="inlineStr">
@@ -7418,755 +7606,777 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="20" customHeight="1">
-      <c r="A49" s="3" t="inlineStr">
+    <row r="48" ht="42" customHeight="1">
+      <c r="A48" s="30" t="inlineStr">
+        <is>
+          <t>KP-09</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
+        <is>
+          <t>Servis dış kapısı</t>
+        </is>
+      </c>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>Isı yalıtımlı alüminyum kapı 90×210, antrasit, yarım buzlu cam, çok noktalı kilit.</t>
+        </is>
+      </c>
+      <c r="D48" s="31" t="inlineStr">
+        <is>
+          <t>Schüco ADS 75 veya Asaş kapı serisi · kilit Kale / Roto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="3" t="inlineStr">
         <is>
           <t>DOĞRAMA / PENCERE</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="42" customHeight="1">
-      <c r="A50" s="30" t="inlineStr">
-        <is>
-          <t>DG-01</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Alüminyum pencere (ısı yalıtımlı)</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>Poliamid bariyerli alüminyum profil, antrasit elektrostatik boya, 4+16Ar+4 Low-E ısıcam, çift açılım.</t>
-        </is>
-      </c>
-      <c r="D50" s="31" t="inlineStr">
-        <is>
-          <t>Schüco AWS 75 veya Çuhadaroğlu / Asaş yalıtımlı seri · cam Şişecam Isıcam Konfor + argon</t>
         </is>
       </c>
     </row>
     <row r="51" ht="42" customHeight="1">
       <c r="A51" s="30" t="inlineStr">
         <is>
-          <t>DG-02</t>
+          <t>DG-01</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>Lift &amp; slide sürme cam sistem</t>
+          <t>Alüminyum pencere (ısı yalıtımlı)</t>
         </is>
       </c>
       <c r="C51" s="9" t="inlineStr">
         <is>
-          <t>Sürme kanatlı, geniş açıklıklı, alçak eşikli; salon-teras ve veranda geçişi.</t>
+          <t>Poliamid bariyerli alüminyum profil, antrasit elektrostatik boya, 4+16Ar+4 Low-E ısıcam, çift açılım.</t>
         </is>
       </c>
       <c r="D51" s="31" t="inlineStr">
         <is>
-          <t>Schüco ASS 70 HI veya Çuhadaroğlu sürme sistem</t>
+          <t>Schüco AWS 75 veya Çuhadaroğlu / Asaş yalıtımlı seri · cam Şişecam Isıcam Konfor + argon</t>
         </is>
       </c>
     </row>
     <row r="52" ht="42" customHeight="1">
       <c r="A52" s="30" t="inlineStr">
         <is>
-          <t>DG-03</t>
+          <t>DG-02</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>Bodrum ışıklık penceresi</t>
+          <t>Lift &amp; slide sürme cam sistem</t>
         </is>
       </c>
       <c r="C52" s="9" t="inlineStr">
         <is>
-          <t>Işıklığa bakan pencere, dıştan galvaniz ızgara/korkuluk, drenajlı ışıklık.</t>
+          <t>Sürme kanatlı, geniş açıklıklı, alçak eşikli; salon-teras ve veranda geçişi.</t>
         </is>
       </c>
       <c r="D52" s="31" t="inlineStr">
         <is>
-          <t>Asaş alüminyum · ızgara galvaniz çelik (özel üretim)</t>
+          <t>Schüco ASS 70 HI veya Çuhadaroğlu sürme sistem</t>
         </is>
       </c>
     </row>
     <row r="53" ht="42" customHeight="1">
       <c r="A53" s="30" t="inlineStr">
         <is>
-          <t>DG-04</t>
+          <t>DG-03</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>Çatı penceresi</t>
+          <t>Bodrum ışıklık penceresi</t>
         </is>
       </c>
       <c r="C53" s="9" t="inlineStr">
         <is>
-          <t>Isıcamlı çatı penceresi, sineklik ve karartma perdesi.</t>
+          <t>Işıklığa bakan pencere, dıştan galvaniz ızgara/korkuluk, drenajlı ışıklık.</t>
         </is>
       </c>
       <c r="D53" s="31" t="inlineStr">
         <is>
-          <t>Velux GGU veya Fakro</t>
+          <t>Asaş alüminyum · ızgara galvaniz çelik (özel üretim)</t>
         </is>
       </c>
     </row>
     <row r="54" ht="42" customHeight="1">
       <c r="A54" s="30" t="inlineStr">
         <is>
-          <t>DG-05</t>
+          <t>DG-04</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>Motorlu panjur / güneş kırıcı</t>
+          <t>Çatı penceresi</t>
         </is>
       </c>
       <c r="C54" s="9" t="inlineStr">
         <is>
-          <t>Alüminyum motorlu panjur veya dış jaluzi; yatak odaları ve güneybatı cephesi.</t>
+          <t>Isıcamlı çatı penceresi, sineklik ve karartma perdesi.</t>
         </is>
       </c>
       <c r="D54" s="31" t="inlineStr">
         <is>
-          <t>Somfy motor + Asaş panjur kutusu</t>
+          <t>Velux GGU veya Fakro</t>
         </is>
       </c>
     </row>
     <row r="55" ht="42" customHeight="1">
       <c r="A55" s="30" t="inlineStr">
         <is>
-          <t>DG-06</t>
+          <t>DG-05</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>Sineklik</t>
+          <t>Motorlu panjur / güneş kırıcı</t>
         </is>
       </c>
       <c r="C55" s="9" t="inlineStr">
         <is>
-          <t>Plise veya sürme sineklik, doğrama rengiyle aynı.</t>
+          <t>Alüminyum motorlu panjur veya dış jaluzi; yatak odaları ve güneybatı cephesi.</t>
         </is>
       </c>
       <c r="D55" s="31" t="inlineStr">
         <is>
-          <t>Asaş veya Öztek plise sineklik</t>
+          <t>Somfy motor + Asaş panjur kutusu</t>
         </is>
       </c>
     </row>
     <row r="56" ht="42" customHeight="1">
       <c r="A56" s="30" t="inlineStr">
         <is>
+          <t>DG-06</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>Sineklik</t>
+        </is>
+      </c>
+      <c r="C56" s="9" t="inlineStr">
+        <is>
+          <t>Plise veya sürme sineklik, doğrama rengiyle aynı.</t>
+        </is>
+      </c>
+      <c r="D56" s="31" t="inlineStr">
+        <is>
+          <t>Asaş veya Öztek plise sineklik</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="42" customHeight="1">
+      <c r="A57" s="30" t="inlineStr">
+        <is>
           <t>DG-07</t>
         </is>
       </c>
-      <c r="B56" s="8" t="inlineStr">
+      <c r="B57" s="8" t="inlineStr">
         <is>
           <t>Doğrama yok</t>
         </is>
       </c>
-      <c r="C56" s="9" t="inlineStr">
+      <c r="C57" s="9" t="inlineStr">
         <is>
           <t>Penceresiz mahal; mekanik havalandırma ile çözülür.</t>
         </is>
       </c>
-      <c r="D56" s="31" t="inlineStr">
+      <c r="D57" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="58" ht="20" customHeight="1">
-      <c r="A58" s="3" t="inlineStr">
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="3" t="inlineStr">
         <is>
           <t>ELEKTRİK</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="42" customHeight="1">
-      <c r="A59" s="30" t="inlineStr">
-        <is>
-          <t>EL-01</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t>Standart oda tesisatı</t>
-        </is>
-      </c>
-      <c r="C59" s="9" t="inlineStr">
-        <is>
-          <t>6 priz, 2 TV+data, komütatör/vaviyen anahtar, sarkıt + spot devresi, perde motoru beslemesi, duman dedektörü.</t>
-        </is>
-      </c>
-      <c r="D59" s="31" t="inlineStr">
-        <is>
-          <t>Anahtar-priz Viko by Panasonic Novella veya Legrand Valena · kablo Öznur / Prysmian</t>
         </is>
       </c>
     </row>
     <row r="60" ht="42" customHeight="1">
       <c r="A60" s="30" t="inlineStr">
         <is>
-          <t>EL-02</t>
+          <t>EL-01</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>Islak hacim tesisatı</t>
+          <t>Standart oda tesisatı</t>
         </is>
       </c>
       <c r="C60" s="9" t="inlineStr">
         <is>
-          <t>IP44 priz, ayna aydınlatma + ayna ısıtıcı beslemesi, havlupan beslemesi, aspiratör senkronu, kaçak akım koruma.</t>
+          <t>6 priz, 2 TV+data, komütatör/vaviyen anahtar, sarkıt + spot devresi, perde motoru beslemesi, duman dedektörü.</t>
         </is>
       </c>
       <c r="D60" s="31" t="inlineStr">
         <is>
-          <t>Legrand Plexo IP44 · kaçak akım rölesi Schneider veya ABB</t>
+          <t>Anahtar-priz Viko by Panasonic Novella veya Legrand Valena · kablo Öznur / Prysmian</t>
         </is>
       </c>
     </row>
     <row r="61" ht="42" customHeight="1">
       <c r="A61" s="30" t="inlineStr">
         <is>
-          <t>EL-03</t>
+          <t>EL-02</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>Mutfak tesisatı</t>
+          <t>Islak hacim tesisatı</t>
         </is>
       </c>
       <c r="C61" s="9" t="inlineStr">
         <is>
-          <t>Ankastre fırın, ocak, bulaşık makinesi, davlumbaz ve buzdolabı için ayrı sigortalı hatlar; tezgah üstü 6 priz, gömme priz kutusu, tezgah altı LED.</t>
+          <t>IP44 priz, ayna aydınlatma + ayna ısıtıcı beslemesi, havlupan beslemesi, aspiratör senkronu, kaçak akım koruma.</t>
         </is>
       </c>
       <c r="D61" s="31" t="inlineStr">
         <is>
-          <t>Schneider Unica · gömme priz Evoline Port · LED Osram</t>
+          <t>Legrand Plexo IP44 · kaçak akım rölesi Schneider veya ABB</t>
         </is>
       </c>
     </row>
     <row r="62" ht="42" customHeight="1">
       <c r="A62" s="30" t="inlineStr">
         <is>
-          <t>EL-04</t>
+          <t>EL-03</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>Salon / yaşam alanı tesisatı</t>
+          <t>Mutfak tesisatı</t>
         </is>
       </c>
       <c r="C62" s="9" t="inlineStr">
         <is>
-          <t>Senaryolu dimmerli aydınlatma, gizli LED nişi, TV için gömme kanal, 10 priz, data ve ses altyapısı.</t>
+          <t>Ankastre fırın, ocak, bulaşık makinesi, davlumbaz ve buzdolabı için ayrı sigortalı hatlar; tezgah üstü 6 priz, gömme priz kutusu, tezgah altı LED.</t>
         </is>
       </c>
       <c r="D62" s="31" t="inlineStr">
         <is>
-          <t>KNX: Jung / Gira veya Schneider KNX · kablosuz alternatif: Somfy TaHoma</t>
+          <t>Schneider Unica · gömme priz Evoline Port · LED Osram</t>
         </is>
       </c>
     </row>
     <row r="63" ht="42" customHeight="1">
       <c r="A63" s="30" t="inlineStr">
         <is>
-          <t>EL-05</t>
+          <t>EL-04</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>Teknik hacim tesisatı</t>
+          <t>Salon / yaşam alanı tesisatı</t>
         </is>
       </c>
       <c r="C63" s="9" t="inlineStr">
         <is>
-          <t>Ana pano / kat panosu, seyyar priz, acil aydınlatma, kazan ve hidrofor beslemesi, IP54 armatür.</t>
+          <t>Senaryolu dimmerli aydınlatma, gizli LED nişi, TV için gömme kanal, 10 priz, data ve ses altyapısı.</t>
         </is>
       </c>
       <c r="D63" s="31" t="inlineStr">
         <is>
-          <t>Pano Schneider Prisma veya ABB · armatür Lamp83 IP54</t>
+          <t>KNX: Jung / Gira veya Schneider KNX · kablosuz alternatif: Somfy TaHoma</t>
         </is>
       </c>
     </row>
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="30" t="inlineStr">
         <is>
-          <t>EL-06</t>
+          <t>EL-05</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>Dış mekan tesisatı</t>
+          <t>Teknik hacim tesisatı</t>
         </is>
       </c>
       <c r="C64" s="9" t="inlineStr">
         <is>
-          <t>IP65 armatür, bahçe ve cephe aydınlatması, kapaklı dış priz, kamera ve otomatik kapı beslemesi.</t>
+          <t>Ana pano / kat panosu, seyyar priz, acil aydınlatma, kazan ve hidrofor beslemesi, IP54 armatür.</t>
         </is>
       </c>
       <c r="D64" s="31" t="inlineStr">
         <is>
-          <t>Lamp83 / Fumagalli IP65 · kamera Hikvision veya Dahua</t>
+          <t>Pano Schneider Prisma veya ABB · armatür Lamp83 IP54</t>
         </is>
       </c>
     </row>
     <row r="65" ht="42" customHeight="1">
       <c r="A65" s="30" t="inlineStr">
         <is>
-          <t>EL-07</t>
+          <t>EL-06</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>Sinema / hobi tesisatı</t>
+          <t>Dış mekan tesisatı</t>
         </is>
       </c>
       <c r="C65" s="9" t="inlineStr">
         <is>
-          <t>Projeksiyon ve perde beslemesi, 7.1 hoparlör kablolaması, gömme kanal, ışık senaryosu, ses yalıtımlı buat.</t>
+          <t>IP65 armatür, bahçe ve cephe aydınlatması, kapaklı dış priz, kamera ve otomatik kapı beslemesi.</t>
         </is>
       </c>
       <c r="D65" s="31" t="inlineStr">
         <is>
-          <t>Kablolama Belden / Klotz · kumanda KNX (Jung)</t>
+          <t>Lamp83 / Fumagalli IP65 · kamera Hikvision veya Dahua</t>
         </is>
       </c>
     </row>
     <row r="66" ht="42" customHeight="1">
       <c r="A66" s="30" t="inlineStr">
         <is>
-          <t>EL-08</t>
+          <t>EL-07</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>Garaj tesisatı</t>
+          <t>Sinema / hobi tesisatı</t>
         </is>
       </c>
       <c r="C66" s="9" t="inlineStr">
         <is>
-          <t>IP54 armatür, garaj kapısı motor beslemesi, elektrikli araç şarjı için 3 faz 11 kW hat, kapaklı priz.</t>
+          <t>Projeksiyon ve perde beslemesi, 7.1 hoparlör kablolaması, gömme kanal, ışık senaryosu, ses yalıtımlı buat.</t>
         </is>
       </c>
       <c r="D66" s="31" t="inlineStr">
         <is>
-          <t>Şarj ünitesi Vestel EVC04 veya ABB Terra AC · pano Schneider</t>
+          <t>Kablolama Belden / Klotz · kumanda KNX (Jung)</t>
         </is>
       </c>
     </row>
     <row r="67" ht="42" customHeight="1">
       <c r="A67" s="30" t="inlineStr">
         <is>
+          <t>EL-08</t>
+        </is>
+      </c>
+      <c r="B67" s="8" t="inlineStr">
+        <is>
+          <t>Garaj tesisatı</t>
+        </is>
+      </c>
+      <c r="C67" s="9" t="inlineStr">
+        <is>
+          <t>IP54 armatür, garaj kapısı motor beslemesi, elektrikli araç şarjı için 3 faz 11 kW hat, kapaklı priz.</t>
+        </is>
+      </c>
+      <c r="D67" s="31" t="inlineStr">
+        <is>
+          <t>Şarj ünitesi Vestel EVC04 veya ABB Terra AC · pano Schneider</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="42" customHeight="1">
+      <c r="A68" s="30" t="inlineStr">
+        <is>
           <t>EL-09</t>
         </is>
       </c>
-      <c r="B67" s="8" t="inlineStr">
+      <c r="B68" s="8" t="inlineStr">
         <is>
           <t>Akıllı ev ana altyapısı</t>
         </is>
       </c>
-      <c r="C67" s="9" t="inlineStr">
+      <c r="C68" s="9" t="inlineStr">
         <is>
           <t>KNX ana hat, zayıf akım panosu, CAT6 yıldız topoloji, IP kamera NVR, görüntülü diyafon, alarm paneli.</t>
         </is>
       </c>
-      <c r="D67" s="31" t="inlineStr">
+      <c r="D68" s="31" t="inlineStr">
         <is>
           <t>KNX Jung/Gira · switch Ubiquiti UniFi · diyafon Comelit veya Multitek · alarm Paradox</t>
         </is>
       </c>
     </row>
-    <row r="69" ht="20" customHeight="1">
-      <c r="A69" s="3" t="inlineStr">
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>MEKANİK</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="42" customHeight="1">
-      <c r="A70" s="30" t="inlineStr">
-        <is>
-          <t>MK-01</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t>Yerden ısıtma</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>Kollektörlü serpantin, ısı yalıtım levhası + şap, mahal bazlı oda termostatı (akıllı ev entegre).</t>
-        </is>
-      </c>
-      <c r="D70" s="31" t="inlineStr">
-        <is>
-          <t>Boru Uponor Comfort Pipe veya Rehau Rautitan · kollektör Danfoss · termostat Honeywell Evohome</t>
         </is>
       </c>
     </row>
     <row r="71" ht="42" customHeight="1">
       <c r="A71" s="30" t="inlineStr">
         <is>
-          <t>MK-02</t>
+          <t>MK-01</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>Yerden ısıtma + havlupan</t>
+          <t>Yerden ısıtma</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
         <is>
-          <t>MK-01'e ek olarak havlupan radyatör (karışımlı veya elektrikli).</t>
+          <t>Kollektörlü serpantin, ısı yalıtım levhası + şap, mahal bazlı oda termostatı (akıllı ev entegre).</t>
         </is>
       </c>
       <c r="D71" s="31" t="inlineStr">
         <is>
-          <t>Havlupan Zehnder veya Demirdöküm · vana Danfoss</t>
+          <t>Boru Uponor Comfort Pipe veya Rehau Rautitan · kollektör Danfoss · termostat Honeywell Evohome</t>
         </is>
       </c>
     </row>
     <row r="72" ht="42" customHeight="1">
       <c r="A72" s="30" t="inlineStr">
         <is>
-          <t>MK-03</t>
+          <t>MK-02</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>VRF / multi-split iç ünite</t>
+          <t>Yerden ısıtma + havlupan</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
         <is>
-          <t>Gizli tavan tipi veya duvar tipi iç ünite, drenaj hattı, kablolu kumanda.</t>
+          <t>MK-01'e ek olarak havlupan radyatör (karışımlı veya elektrikli).</t>
         </is>
       </c>
       <c r="D72" s="31" t="inlineStr">
         <is>
-          <t>Daikin VRV 5 veya Mitsubishi Electric City Multi (alternatif: Toshiba)</t>
+          <t>Havlupan Zehnder veya Demirdöküm · vana Danfoss</t>
         </is>
       </c>
     </row>
     <row r="73" ht="42" customHeight="1">
       <c r="A73" s="30" t="inlineStr">
         <is>
-          <t>MK-04</t>
+          <t>MK-03</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>Mekanik havalandırma</t>
+          <t>VRF / multi-split iç ünite</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
         <is>
-          <t>Kanal tipi sessiz aspiratör, çatıya/cepheye atış, anahtar veya nem sensörüyle otomatik.</t>
+          <t>Gizli tavan tipi veya duvar tipi iç ünite, drenaj hattı, kablolu kumanda.</t>
         </is>
       </c>
       <c r="D73" s="31" t="inlineStr">
         <is>
-          <t>Vortice veya Systemair kanal tipi fan</t>
+          <t>Daikin VRV 5 veya Mitsubishi Electric City Multi (alternatif: Toshiba)</t>
         </is>
       </c>
     </row>
     <row r="74" ht="42" customHeight="1">
       <c r="A74" s="30" t="inlineStr">
         <is>
-          <t>MK-05</t>
+          <t>MK-04</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>Davlumbaz ve mutfak havalandırması</t>
+          <t>Mekanik havalandırma</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
         <is>
-          <t>Ankastre davlumbaz + paslanmaz kanalla çatıya atış, geri akış klapesi.</t>
+          <t>Kanal tipi sessiz aspiratör, çatıya/cepheye atış, anahtar veya nem sensörüyle otomatik.</t>
         </is>
       </c>
       <c r="D74" s="31" t="inlineStr">
         <is>
-          <t>Falmec veya Siemens iQ700 ada tipi davlumbaz</t>
+          <t>Vortice veya Systemair kanal tipi fan</t>
         </is>
       </c>
     </row>
     <row r="75" ht="42" customHeight="1">
       <c r="A75" s="30" t="inlineStr">
         <is>
-          <t>MK-06</t>
+          <t>MK-05</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>Kazan dairesi ekipmanı</t>
+          <t>Davlumbaz ve mutfak havalandırması</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
         <is>
-          <t>Yoğuşmalı kazan, 300 lt boyler, genleşme tankı, sirkülasyon pompaları, gaz dedektörü + selenoid vana, taze hava menfezi.</t>
+          <t>Ankastre davlumbaz + paslanmaz kanalla çatıya atış, geri akış klapesi.</t>
         </is>
       </c>
       <c r="D75" s="31" t="inlineStr">
         <is>
-          <t>Kazan Vaillant ecoTEC plus veya Buderus Logamax · boyler Vaillant uniSTOR · pompa Grundfos Alpha</t>
+          <t>Falmec veya Siemens iQ700 ada tipi davlumbaz</t>
         </is>
       </c>
     </row>
     <row r="76" ht="42" customHeight="1">
       <c r="A76" s="30" t="inlineStr">
         <is>
-          <t>MK-07</t>
+          <t>MK-06</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>Sauna ünitesi</t>
+          <t>Kazan dairesi ekipmanı</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
         <is>
-          <t>Elektrikli sauna sobası (hacme göre kW), kumanda paneli, hava giriş-çıkış menfezleri, ısıya dayanıklı armatür.</t>
+          <t>Hermetik yoğuşmalı kazan (baca şafttan çatıya) veya hava kaynaklı ısı pompası, 300 lt boyler, genleşme tankı, pompalar, gaz dedektörü + selenoid vana.</t>
         </is>
       </c>
       <c r="D76" s="31" t="inlineStr">
         <is>
-          <t>Harvia Cilindro + Xenio kumanda (alternatif: Tylö)</t>
+          <t>Kazan Vaillant ecoTEC plus veya Buderus Logamax · boyler Vaillant uniSTOR · pompa Grundfos Alpha</t>
         </is>
       </c>
     </row>
     <row r="77" ht="42" customHeight="1">
       <c r="A77" s="30" t="inlineStr">
         <is>
-          <t>MK-08</t>
+          <t>MK-07</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>Isıtma yok / temperli</t>
+          <t>Sauna ünitesi</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
         <is>
-          <t>Isıtma tesisatı yapılmaz; komşu hacimden temperlenir. Donmaya karşı tesisat izolasyonu.</t>
+          <t>Elektrikli sauna sobası (hacme göre kW), kumanda paneli, hava giriş-çıkış menfezleri, ısıya dayanıklı armatür.</t>
         </is>
       </c>
       <c r="D77" s="31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Harvia Cilindro + Xenio kumanda (alternatif: Tylö)</t>
         </is>
       </c>
     </row>
     <row r="78" ht="42" customHeight="1">
       <c r="A78" s="30" t="inlineStr">
         <is>
+          <t>MK-08</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Isıtma yok / temperli</t>
+        </is>
+      </c>
+      <c r="C78" s="9" t="inlineStr">
+        <is>
+          <t>Isıtma tesisatı yapılmaz; komşu hacimden temperlenir. Donmaya karşı tesisat izolasyonu.</t>
+        </is>
+      </c>
+      <c r="D78" s="31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="42" customHeight="1">
+      <c r="A79" s="30" t="inlineStr">
+        <is>
           <t>MK-09</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>Isı geri kazanımlı havalandırma (opsiyon)</t>
         </is>
       </c>
-      <c r="C78" s="9" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>Merkezi ısı geri kazanım cihazı, kanal dağıtımı, F7 filtre.</t>
         </is>
       </c>
-      <c r="D78" s="31" t="inlineStr">
+      <c r="D79" s="31" t="inlineStr">
         <is>
           <t>Systemair SAVE veya Zehnder ComfoAir</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="20" customHeight="1">
-      <c r="A80" s="3" t="inlineStr">
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>SIHHİ TESİSAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="42" customHeight="1">
-      <c r="A81" s="30" t="inlineStr">
-        <is>
-          <t>ST-01</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t>Tesisat yok</t>
-        </is>
-      </c>
-      <c r="C81" s="9" t="inlineStr">
-        <is>
-          <t>Su ve atık tesisatı bulunmaz.</t>
-        </is>
-      </c>
-      <c r="D81" s="31" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
     <row r="82" ht="42" customHeight="1">
       <c r="A82" s="30" t="inlineStr">
         <is>
-          <t>ST-02</t>
+          <t>ST-01</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>Banyo tam donanım</t>
+          <t>Tesisat yok</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
         <is>
-          <t>Gömme rezervuarlı asma klozet, tezgah üstü lavabo, ankastre batarya, duş nişi + yağmurlama duş, gizli süzgeç, ara vanalar.</t>
+          <t>Su ve atık tesisatı bulunmaz.</t>
         </is>
       </c>
       <c r="D82" s="31" t="inlineStr">
         <is>
-          <t>VitrA Metropole veya Duravit ME · rezervuar Geberit Sigma · armatür Grohe Grohtherm / Hansgrohe</t>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="83" ht="42" customHeight="1">
       <c r="A83" s="30" t="inlineStr">
         <is>
-          <t>ST-03</t>
+          <t>ST-02</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>Ebeveyn banyo donanımı</t>
+          <t>Banyo tam donanım</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
         <is>
-          <t>ST-02'ye ek: çift lavabo, ankastre termostatik batarya, serbest duran küvet, taharet/bide, havlupan bağlantısı.</t>
+          <t>Gömme rezervuarlı asma klozet, tezgah üstü lavabo, ankastre batarya, duş nişi + yağmurlama duş, gizli süzgeç, ara vanalar.</t>
         </is>
       </c>
       <c r="D83" s="31" t="inlineStr">
         <is>
-          <t>Duravit veya Villeroy&amp;Boch küvet · armatür Hansgrohe Axor · duş Grohe Rainshower 360</t>
+          <t>VitrA Metropole veya Duravit ME · rezervuar Geberit Sigma · armatür Grohe Grohtherm / Hansgrohe</t>
         </is>
       </c>
     </row>
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="30" t="inlineStr">
         <is>
-          <t>ST-04</t>
+          <t>ST-03</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>WC donanımı</t>
+          <t>Ebeveyn banyo donanımı</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
         <is>
-          <t>Asma klozet + gömme rezervuar, lavabo, ankastre batarya, taharet musluğu.</t>
+          <t>ST-02'ye ek: çift lavabo, ankastre termostatik batarya, serbest duran küvet, taharet/bide, havlupan bağlantısı.</t>
         </is>
       </c>
       <c r="D84" s="31" t="inlineStr">
         <is>
-          <t>VitrA / Roca · Geberit gömme rezervuar · Grohe armatür</t>
+          <t>Duravit veya Villeroy&amp;Boch küvet · armatür Hansgrohe Axor · duş Grohe Rainshower 360</t>
         </is>
       </c>
     </row>
     <row r="85" ht="42" customHeight="1">
       <c r="A85" s="30" t="inlineStr">
         <is>
-          <t>ST-05</t>
+          <t>ST-04</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t>Mutfak donanımı</t>
+          <t>WC donanımı</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
         <is>
-          <t>Granit veya paslanmaz eviye, ankastre batarya, bulaşık makinesi bağlantısı, su arıtma altyapısı, yağ tutucu sifon.</t>
+          <t>Asma klozet + gömme rezervuar, lavabo, ankastre batarya, taharet musluğu.</t>
         </is>
       </c>
       <c r="D85" s="31" t="inlineStr">
         <is>
-          <t>Eviye Franke veya Blanco · batarya Grohe Minta · arıtma BWT</t>
+          <t>VitrA / Roca · Geberit gömme rezervuar · Grohe armatür</t>
         </is>
       </c>
     </row>
     <row r="86" ht="42" customHeight="1">
       <c r="A86" s="30" t="inlineStr">
         <is>
-          <t>ST-06</t>
+          <t>ST-05</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>Çamaşırhane donanımı</t>
+          <t>Mutfak donanımı</t>
         </is>
       </c>
       <c r="C86" s="9" t="inlineStr">
         <is>
-          <t>Çamaşır ve kurutma makinesi bağlantısı, ön yıkama eviyesi, yer süzgeci, taşma koruma sensörü.</t>
+          <t>Granit veya paslanmaz eviye, ankastre batarya, bulaşık makinesi bağlantısı, su arıtma altyapısı, yağ tutucu sifon.</t>
         </is>
       </c>
       <c r="D86" s="31" t="inlineStr">
         <is>
-          <t>Eviye Franke · süzgeç ACO · su kaçak sensörü Netatmo veya Grohe Sense</t>
+          <t>Eviye Franke veya Blanco · batarya Grohe Minta · arıtma BWT</t>
         </is>
       </c>
     </row>
     <row r="87" ht="42" customHeight="1">
       <c r="A87" s="30" t="inlineStr">
         <is>
-          <t>ST-07</t>
+          <t>ST-06</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t>Teknik / garaj tesisatı</t>
+          <t>Çamaşırhane donanımı</t>
         </is>
       </c>
       <c r="C87" s="9" t="inlineStr">
         <is>
-          <t>Yer süzgeci, bahçe tipi çeşme, hortum bağlantısı.</t>
+          <t>Çamaşır ve kurutma makinesi bağlantısı, ön yıkama eviyesi, yer süzgeci, taşma koruma sensörü.</t>
         </is>
       </c>
       <c r="D87" s="31" t="inlineStr">
         <is>
-          <t>Süzgeç ACO · armatür Artema</t>
+          <t>Eviye Franke · süzgeç ACO · su kaçak sensörü Netatmo veya Grohe Sense</t>
         </is>
       </c>
     </row>
     <row r="88" ht="42" customHeight="1">
       <c r="A88" s="30" t="inlineStr">
         <is>
+          <t>ST-07</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>Teknik / garaj tesisatı</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>Yer süzgeci, bahçe tipi çeşme, hortum bağlantısı.</t>
+        </is>
+      </c>
+      <c r="D88" s="31" t="inlineStr">
+        <is>
+          <t>Süzgeç ACO · armatür Artema</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="42" customHeight="1">
+      <c r="A89" s="30" t="inlineStr">
+        <is>
           <t>ST-08</t>
         </is>
       </c>
-      <c r="B88" s="8" t="inlineStr">
+      <c r="B89" s="8" t="inlineStr">
         <is>
           <t>Dış mekan tesisatı</t>
         </is>
       </c>
-      <c r="C88" s="9" t="inlineStr">
+      <c r="C89" s="9" t="inlineStr">
         <is>
           <t>Bahçe çeşmesi, otomatik sulama vanası, teras süzgeci ve yağmur suyu drenajı.</t>
         </is>
       </c>
-      <c r="D88" s="31" t="inlineStr">
+      <c r="D89" s="31" t="inlineStr">
         <is>
           <t>Sulama Hunter veya Rain Bird · süzgeç ACO Self</t>
         </is>
@@ -8175,14 +8385,14 @@
   </sheetData>
   <mergeCells count="10">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A80:D80"/>
+    <mergeCell ref="A70:D70"/>
     <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="A50:D50"/>
     <mergeCell ref="A4:D4"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A59:D59"/>
+    <mergeCell ref="A81:D81"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8196,7 +8406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E24"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -8248,12 +8458,12 @@
       </c>
       <c r="B4" s="9" t="inlineStr">
         <is>
-          <t>≤ 0.30 (300 m²)</t>
+          <t>≤ 0,30 (300 m²)</t>
         </is>
       </c>
       <c r="C4" s="9" t="inlineStr">
         <is>
-          <t>0.30 (300 m²)</t>
+          <t>0,30 (300 m²)</t>
         </is>
       </c>
       <c r="D4" s="32" t="inlineStr">
@@ -8263,24 +8473,24 @@
       </c>
       <c r="E4" s="9" t="inlineStr">
         <is>
-          <t>Oturum 20,00 × 15,00 m. Parsel bilgisi varsayımdır, imar durumu ile teyit edilmelidir.</t>
+          <t>Oturum 20,00 × 15,00 m; ısı yalıtımı ve 1,50 m'lik açık balkon çıkmaları TAKS'a dahil değildir.</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>Kat alanları katsayısı (KAKS/Emsal)</t>
+          <t>Kat alanları katsayısı (KAKS / emsal)</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>≤ 0.60 (601 m²)</t>
+          <t>≤ 0,60 (601 m²)</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
         <is>
-          <t>0.60 (600 m²)</t>
+          <t>0,60 (600 m²)</t>
         </is>
       </c>
       <c r="D5" s="32" t="inlineStr">
@@ -8290,51 +8500,51 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>Zemin + 1. kat emsale dahil; bodrum ve çatı arası emsal dışı kabul edilmiştir (teyit gerekir).</t>
+          <t>Zemin + 1. kat emsale dahildir. Bodrumdaki sinema, oyun salonu, fitness ve misafir odası iskan edilen hacim sayılabilir — emsal dışı kabulü belediyece teyit edilmelidir.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Çekme mesafeleri</t>
+          <t>Bodrum katın emsal durumu</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>ön 5,00 · yan 3,00 · arka 3,00 m</t>
+          <t>Konut kullanımı emsale dahil; depo, tesisat, otopark hariç</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>ön 5.00 · yan 3.00 · arka 3.00 m</t>
-        </is>
-      </c>
-      <c r="D6" s="32" t="inlineStr">
-        <is>
-          <t>UYGUN</t>
+          <t>Bodrumda yaşama hacimleri var</t>
+        </is>
+      </c>
+      <c r="D6" s="33" t="inlineStr">
+        <is>
+          <t>KONTROL</t>
         </is>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 24 ve plan notları; vaziyet planında gösterilmiştir.</t>
+          <t>Emsal hesabına katılırsa bodrum kullanımları depo/hobi niteliğinde projelendirilmeli veya zemin + 1. kat küçültülmelidir.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>Oturma odası (asgari 1 adet)</t>
+          <t>Bina yüksekliği (Hmax)</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>12,00 m² · dar kenar 3,00 m</t>
+          <t>≤ 6,50 m (Yençok 2 kat)</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
         <is>
-          <t>61.4 m² · dar kenar 7.35 m</t>
+          <t>6,50 m (tabii zeminden çatı döşemesine)</t>
         </is>
       </c>
       <c r="D7" s="32" t="inlineStr">
@@ -8344,24 +8554,24 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 29 — Z-01 Salon.</t>
+          <t>±0.00 = tabii zemin +0,30; zemin 3,20 + 1. kat 3,00 m. Çatı eğimi %30, mahya +8,94.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>Yatak odası (en küçüğü)</t>
+          <t>Çekme mesafeleri</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>9,00 m² · dar kenar 2,50 m</t>
+          <t>ön 5,00 · yan 3,00 · arka 3,00 m</t>
         </is>
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>10.4 m² · dar kenar 2.85 m</t>
+          <t>ön 5,00 · yan 3,00 · arka 18,50 m</t>
         </is>
       </c>
       <c r="D8" s="32" t="inlineStr">
@@ -8371,24 +8581,24 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 29 — B-18 Hizmet / misafir odası. Projede 7 yatak odası var.</t>
+          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 24; vaziyet planında gösterilmiştir. Işıklıklar yan bahçede zemin altındadır.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Mutfak</t>
+          <t>Açık çıkma (balkon)</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>3,30 m² · dar kenar 1,50 m</t>
+          <t>≤ 1,50 m</t>
         </is>
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>20.2 m² · dar kenar 3.45 m</t>
+          <t>1,50 m (güney cephesi, 2 balkon)</t>
         </is>
       </c>
       <c r="D9" s="32" t="inlineStr">
@@ -8398,24 +8608,24 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 29 — Z-06 Mutfak (+ Z-07 kiler/arka mutfak).</t>
+          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 25 — konsol balkon, bahçe mesafesine taşar.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>Banyo / yıkanma yeri (en küçüğü)</t>
+          <t>Oturma odası (asgari 1 adet)</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>3,00 m² · dar kenar 1,50 m</t>
+          <t>12,00 m² · dar kenar 3,00 m</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
         <is>
-          <t>4.0 m² · dar kenar 1.65 m</t>
+          <t>69,10 m² · dar kenar 7,38 m</t>
         </is>
       </c>
       <c r="D10" s="32" t="inlineStr">
@@ -8425,24 +8635,24 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 29 — B-12 WC + duş. Projede 9 ıslak hacim var.</t>
+          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 29 — Z-09 Salon.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>Tuvalet</t>
+          <t>Yatak odası (en küçüğü)</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>1,20 m² · dar kenar 1,00 m</t>
+          <t>9,00 m² · dar kenar 2,50 m</t>
         </is>
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>5.8 m² · dar kenar 2.35 m</t>
+          <t>15,20 m² · dar kenar 2,65 m</t>
         </is>
       </c>
       <c r="D11" s="32" t="inlineStr">
@@ -8452,24 +8662,24 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 29 — Z-08 Misafir WC.</t>
+          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 29 — K-12 Yatak odası 4. Projede 6 yatak odası var.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Hol / koridor genişliği (en dar)</t>
+          <t>Mutfak</t>
         </is>
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>1,20 m</t>
+          <t>3,30 m² · dar kenar 1,50 m</t>
         </is>
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>1.45 m</t>
+          <t>33,30 m² · dar kenar 4,78 m</t>
         </is>
       </c>
       <c r="D12" s="32" t="inlineStr">
@@ -8479,24 +8689,24 @@
       </c>
       <c r="E12" s="9" t="inlineStr">
         <is>
-          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 29 — B-13 Koridor.</t>
+          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 29 — Z-11 Mutfak (+ Z-16 arka mutfak).</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>Konut içi merdiven kol genişliği</t>
+          <t>Banyo (en küçüğü)</t>
         </is>
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>1,00 m (ortak merdivende 1,20 m)</t>
+          <t>3,00 m² · dar kenar 1,50 m</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>1,20 m</t>
+          <t>4,50 m² · dar kenar 1,85 m</t>
         </is>
       </c>
       <c r="D13" s="32" t="inlineStr">
@@ -8506,24 +8716,24 @@
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
-          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 32. Merdiven kovası 3,40 × 5,60 m mahal içinde.</t>
+          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 29 — K-13 Yatak odası 4 banyosu.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>Merdiven rıht / basamak</t>
+          <t>Tuvalet (en küçüğü)</t>
         </is>
       </c>
       <c r="B14" s="9" t="inlineStr">
         <is>
-          <t>rıht ≤ 17,50 cm · basamak ≥ 26,0 cm</t>
+          <t>1,20 m² · dar kenar 1,00 m</t>
         </is>
       </c>
       <c r="C14" s="9" t="inlineStr">
         <is>
-          <t>rıht 17,1 cm (bodrum→zemin, 17 basamak) · 16,8 cm (zemin→1. kat, 19 basamak) · basamak 28,0 cm</t>
+          <t>4,00 m² · dar kenar 1,65 m</t>
         </is>
       </c>
       <c r="D14" s="32" t="inlineStr">
@@ -8533,24 +8743,24 @@
       </c>
       <c r="E14" s="9" t="inlineStr">
         <is>
-          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 32. Kat yüksekliklerinden hesaplanmıştır.</t>
+          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 29 — Z-14 Misafir WC.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>Net tavan yüksekliği</t>
+          <t>Hol / koridor genişliği (en dar)</t>
         </is>
       </c>
       <c r="B15" s="9" t="inlineStr">
         <is>
-          <t>2,40 m</t>
+          <t>1,20 m</t>
         </is>
       </c>
       <c r="C15" s="9" t="inlineStr">
         <is>
-          <t>2.55 m (en düşük kat)</t>
+          <t>1,25 m</t>
         </is>
       </c>
       <c r="D15" s="32" t="inlineStr">
@@ -8560,24 +8770,24 @@
       </c>
       <c r="E15" s="9" t="inlineStr">
         <is>
-          <t>Kat yükseklikleri: Bodrum 2.90 m · Zemin 3.20 m · 1. Kat 3.10 m</t>
+          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 29 — B-12 Koridor.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>Çatı arası iç yüksekliği</t>
+          <t>Konut içi merdiven kol genişliği</t>
         </is>
       </c>
       <c r="B16" s="9" t="inlineStr">
         <is>
-          <t>2,40 m (kullanılabilir hacim için)</t>
+          <t>≥ 1,00 m</t>
         </is>
       </c>
       <c r="C16" s="9" t="inlineStr">
         <is>
-          <t>mahyada 3,60 m</t>
+          <t>1,18 m (sahanlık 1,25 m)</t>
         </is>
       </c>
       <c r="D16" s="32" t="inlineStr">
@@ -8587,24 +8797,24 @@
       </c>
       <c r="E16" s="9" t="inlineStr">
         <is>
-          <t>Çatı arası depo olarak kullanılacaktır; bağımsız bölüm değildir.</t>
+          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 32 — iki kollu (U) merdiven.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>Korkuluk yüksekliği</t>
+          <t>Merdiven rıht / basamak</t>
         </is>
       </c>
       <c r="B17" s="9" t="inlineStr">
         <is>
-          <t>1,10 m</t>
+          <t>rıht ≤ 17,5 cm · basamak ≥ 26 cm</t>
         </is>
       </c>
       <c r="C17" s="9" t="inlineStr">
         <is>
-          <t>1,10 m (balkon, teras, galeri, merdiven)</t>
+          <t>bodrum→zemin 18 × 17,0 cm · zemin→1. kat 19 × 16,8 cm · basamak 28 cm</t>
         </is>
       </c>
       <c r="D17" s="32" t="inlineStr">
@@ -8614,24 +8824,24 @@
       </c>
       <c r="E17" s="9" t="inlineStr">
         <is>
-          <t>Temperli cam korkuluk; tırmanmaya elverişsiz tasarım.</t>
+          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 32; 2r + b = 61,7–62,0 cm.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>Otopark</t>
+          <t>Net tavan yüksekliği</t>
         </is>
       </c>
       <c r="B18" s="9" t="inlineStr">
         <is>
-          <t>Her bağımsız bölüm için en az 1 araçlık</t>
+          <t>≥ 2,40 m (konut)</t>
         </is>
       </c>
       <c r="C18" s="9" t="inlineStr">
         <is>
-          <t>3 kapalı (garaj) + 2 açık = 5 araç</t>
+          <t>2,60 m (en düşük, asma tavan altı)</t>
         </is>
       </c>
       <c r="D18" s="32" t="inlineStr">
@@ -8641,51 +8851,51 @@
       </c>
       <c r="E18" s="9" t="inlineStr">
         <is>
-          <t>Otopark Yönetmeliği; kapalı garaj bodrum katta, rampa bahçe içinde.</t>
+          <t>Bodrum 2,66 · zemin 2,80 · 1. kat 2,60 m.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>Sığınak</t>
+          <t>Korkuluk yüksekliği</t>
         </is>
       </c>
       <c r="B19" s="9" t="inlineStr">
         <is>
-          <t>Bağımsız bölüm sayısına göre (tek konutta aranmaz)</t>
+          <t>≥ 1,10 m</t>
         </is>
       </c>
       <c r="C19" s="9" t="inlineStr">
         <is>
-          <t>Bodrumda depo hacimleri ayrılmıştır</t>
-        </is>
-      </c>
-      <c r="D19" s="33" t="inlineStr">
-        <is>
-          <t>KONTROL</t>
+          <t>1,10 m (balkon, galeri, merdiven boşluğu, ışıklık)</t>
+        </is>
+      </c>
+      <c r="D19" s="32" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
         </is>
       </c>
       <c r="E19" s="9" t="inlineStr">
         <is>
-          <t>Sığınak Yönetmeliği kapsamı ilgili idareyle teyit edilmelidir.</t>
+          <t>Temperli lamine cam, tırmanmaya elverişsiz.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Asansör</t>
+          <t>Pencere denizliği (üst kat)</t>
         </is>
       </c>
       <c r="B20" s="9" t="inlineStr">
         <is>
-          <t>Kat adedi 4'ten fazla binalarda zorunlu</t>
+          <t>düşme riskine karşı ≥ 0,85 m veya korkuluk</t>
         </is>
       </c>
       <c r="C20" s="9" t="inlineStr">
         <is>
-          <t>4 duraklı asansör (isteğe bağlı olarak) yapılmıştır</t>
+          <t>0,90 m; kapı boyu camlar yalnız balkona</t>
         </is>
       </c>
       <c r="D20" s="32" t="inlineStr">
@@ -8695,24 +8905,24 @@
       </c>
       <c r="E20" s="9" t="inlineStr">
         <is>
-          <t>Planlı Alanlar İmar Yönetmeliği (PAİY) Md. 34. Kuyu 2,60 × 2,20 m, makine dairesiz.</t>
+          <t>Otomatik kontrol: kontrol.py.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>Isı yalıtımı</t>
+          <t>Otopark</t>
         </is>
       </c>
       <c r="B21" s="9" t="inlineStr">
         <is>
-          <t>TS 825 — 3. iklim bölgesi (Konya)</t>
+          <t>Her bağımsız bölüm için en az 1 araç</t>
         </is>
       </c>
       <c r="C21" s="9" t="inlineStr">
         <is>
-          <t>Dış duvar 8 cm XPS · çatı 14 cm taşyünü · döşeme 4 cm</t>
+          <t>2 kapalı (garaj) + 2 açık</t>
         </is>
       </c>
       <c r="D21" s="32" t="inlineStr">
@@ -8722,24 +8932,24 @@
       </c>
       <c r="E21" s="9" t="inlineStr">
         <is>
-          <t>Binalarda Enerji Performansı Yönetmeliği; enerji kimlik belgesi hesabı yapılacaktır.</t>
+          <t>Otopark Yönetmeliği; garaj zemin katta, araç yolu doğrudan imar yolundan.</t>
         </is>
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>Deprem tasarımı</t>
+          <t>Asansör</t>
         </is>
       </c>
       <c r="B22" s="9" t="inlineStr">
         <is>
-          <t>TBDY-2018</t>
+          <t>Zorunlu değil (≤ 3 kat konut)</t>
         </is>
       </c>
       <c r="C22" s="9" t="inlineStr">
         <is>
-          <t>Betonarme perde + çerçeve sistem, radye temel</t>
+          <t>3 duraklı, 630 kg, makine dairesiz</t>
         </is>
       </c>
       <c r="D22" s="32" t="inlineStr">
@@ -8749,61 +8959,142 @@
       </c>
       <c r="E22" s="9" t="inlineStr">
         <is>
-          <t>Zemin etüdü raporuna göre zemin sınıfı ve tasarım spektrumu belirlenecektir.</t>
+          <t>Engelsiz erişim için isteğe bağlı; kuyu betonarme perde.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>Yangın güvenliği</t>
+          <t>Sığınak</t>
         </is>
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
-          <t>Binaların Yangından Korunması Hakkında Yönetmelik</t>
+          <t>Tek konutta aranmaz</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>Kazan dairesi EI30 yangın kapısı · duman dedektörü · şaftlarda yangın durdurucu</t>
-        </is>
-      </c>
-      <c r="D23" s="32" t="inlineStr">
-        <is>
-          <t>UYGUN</t>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="33" t="inlineStr">
+        <is>
+          <t>KONTROL</t>
         </is>
       </c>
       <c r="E23" s="9" t="inlineStr">
         <is>
-          <t>Müstakil konut; kaçış merdiveni aranmaz.</t>
+          <t>Sığınak Yönetmeliği kapsamı idareyle teyit edilmelidir.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
+          <t>Isı yalıtımı</t>
+        </is>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>TS 825 — 3. bölge (Konya)</t>
+        </is>
+      </c>
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>Dış duvar 8 cm taşyünü · çatı döşemesi 14 cm · bodrum XPS 5 cm</t>
+        </is>
+      </c>
+      <c r="D24" s="32" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>Binalarda Enerji Performansı Yönetmeliği; enerji kimlik belgesiyle kesinleşir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>Deprem tasarımı</t>
+        </is>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>TBDY-2018</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Betonarme çerçeve + asansör perdesi, radye temel</t>
+        </is>
+      </c>
+      <c r="D25" s="32" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="E25" s="9" t="inlineStr">
+        <is>
+          <t>Aks açıklıkları ≤ 7,80 m. Zemin etüdüne göre statik projede kesinleşir.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>Yangın güvenliği</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Binaların Yangından Korunması Hakkında Yönetmelik</t>
+        </is>
+      </c>
+      <c r="C26" s="9" t="inlineStr">
+        <is>
+          <t>Garaj–konut ve ısı merkezi kapıları EI30 · duman dedektörü · şaftta yangın durdurucu</t>
+        </is>
+      </c>
+      <c r="D26" s="32" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="E26" s="9" t="inlineStr">
+        <is>
+          <t>Müstakil konut; bodrum misafir odasında ışıklıktan acil çıkış merdiveni.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
           <t>Su yalıtımı</t>
         </is>
       </c>
-      <c r="B24" s="9" t="inlineStr">
-        <is>
-          <t>TS 11344 / Su Yalıtımı Yönetmeliği</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>Bodrum perde ve temelde çift kat membran + drenaj; ıslak hacimlerde 2K yalıtım</t>
-        </is>
-      </c>
-      <c r="D24" s="32" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Su Yalıtımı Yönetmeliği / TS 11344</t>
+        </is>
+      </c>
+      <c r="C27" s="9" t="inlineStr">
+        <is>
+          <t>Bodrum perde ve radyede çift kat membran + drenaj; ıslak hacimlerde 2K sürme</t>
+        </is>
+      </c>
+      <c r="D27" s="32" t="inlineStr">
         <is>
           <t>UYGUN</t>
         </is>
       </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>Yalıtım detayları uygulama projesinde çizilecektir.</t>
+      <c r="E27" s="9" t="inlineStr">
+        <is>
+          <t>Sistem kesitinde (A-10) gösterilmiştir.</t>
         </is>
       </c>
     </row>
@@ -8814,4 +9105,863 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="29.4" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>TASARIM MANTIK KONTROLÜ (plan geometrisinden otomatik)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="7" t="inlineStr">
+        <is>
+          <t>Grup</t>
+        </is>
+      </c>
+      <c r="B3" s="7" t="inlineStr">
+        <is>
+          <t>Kontrol</t>
+        </is>
+      </c>
+      <c r="C3" s="7" t="inlineStr">
+        <is>
+          <t>Durum</t>
+        </is>
+      </c>
+      <c r="D3" s="7" t="inlineStr">
+        <is>
+          <t>Ayrıntı</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
+      <c r="A4" s="23" t="inlineStr">
+        <is>
+          <t>Geometri</t>
+        </is>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>Bodrum: mahaller 20×15 alanı boşluksuz doldurur</t>
+        </is>
+      </c>
+      <c r="C4" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D4" s="25" t="inlineStr">
+        <is>
+          <t>aks toplamı 300.00 m², çakışma yok</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="23" t="inlineStr">
+        <is>
+          <t>Geometri</t>
+        </is>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>Zemin: mahaller 20×15 alanı boşluksuz doldurur</t>
+        </is>
+      </c>
+      <c r="C5" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>aks toplamı 300.00 m², çakışma yok</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="23" t="inlineStr">
+        <is>
+          <t>Geometri</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>1. Kat: mahaller 20×15 alanı boşluksuz doldurur</t>
+        </is>
+      </c>
+      <c r="C6" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>aks toplamı 300.00 m², çakışma yok</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="23" t="inlineStr">
+        <is>
+          <t>Geometri</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>Merdiven tüm katlarda aynı yerde</t>
+        </is>
+      </c>
+      <c r="C7" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>Bodrum [(10.0, 3.2, 12.6, 8.0)]; Zemin [(10.0, 3.2, 12.6, 8.0)]; 1. Kat [(10.0, 3.2, 12.6, 8.0)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="23" t="inlineStr">
+        <is>
+          <t>Geometri</t>
+        </is>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>Asansor tüm katlarda aynı yerde</t>
+        </is>
+      </c>
+      <c r="C8" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>Bodrum [(10.0, 8.0, 12.0, 10.2)]; Zemin [(10.0, 8.0, 12.0, 10.2)]; 1. Kat [(10.0, 8.0, 12.0, 10.2)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="23" t="inlineStr">
+        <is>
+          <t>Geometri</t>
+        </is>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>Saft tüm katlarda aynı yerde</t>
+        </is>
+      </c>
+      <c r="C9" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>Bodrum [(12.0, 8.0, 12.6, 10.2)]; Zemin [(12.0, 8.0, 12.6, 10.2)]; 1. Kat [(12.0, 8.0, 12.6, 10.2)]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="23" t="inlineStr">
+        <is>
+          <t>Kapılar</t>
+        </is>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>Bodrum: kapılar doğru duvarda, köşelere ve kolonlara çarpmıyor</t>
+        </is>
+      </c>
+      <c r="C10" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>19 kapı/açıklık</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="23" t="inlineStr">
+        <is>
+          <t>Kapılar</t>
+        </is>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>Zemin: kapılar doğru duvarda, köşelere ve kolonlara çarpmıyor</t>
+        </is>
+      </c>
+      <c r="C11" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D11" s="25" t="inlineStr">
+        <is>
+          <t>16 kapı/açıklık</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>Kapılar</t>
+        </is>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>1. Kat: kapılar doğru duvarda, köşelere ve kolonlara çarpmıyor</t>
+        </is>
+      </c>
+      <c r="C12" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D12" s="25" t="inlineStr">
+        <is>
+          <t>17 kapı/açıklık</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="23" t="inlineStr">
+        <is>
+          <t>Kapılar</t>
+        </is>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>Bodrum: kapı kanatları serbest açılıyor (duvar, merdiven, mobilya, diğer kapı)</t>
+        </is>
+      </c>
+      <c r="C13" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D13" s="25" t="inlineStr">
+        <is>
+          <t>15 kanat</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="23" t="inlineStr">
+        <is>
+          <t>Kapılar</t>
+        </is>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>Zemin: kapı kanatları serbest açılıyor (duvar, merdiven, mobilya, diğer kapı)</t>
+        </is>
+      </c>
+      <c r="C14" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>10 kanat</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="23" t="inlineStr">
+        <is>
+          <t>Kapılar</t>
+        </is>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>1. Kat: kapı kanatları serbest açılıyor (duvar, merdiven, mobilya, diğer kapı)</t>
+        </is>
+      </c>
+      <c r="C15" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>15 kanat</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="23" t="inlineStr">
+        <is>
+          <t>Erişim</t>
+        </is>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>Her mahale giriş kapısından ulaşılır</t>
+        </is>
+      </c>
+      <c r="C16" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>tüm mahaller bağlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="23" t="inlineStr">
+        <is>
+          <t>Erişim</t>
+        </is>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>Asansör her katta hole açılır (3 durak)</t>
+        </is>
+      </c>
+      <c r="C17" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="23" t="inlineStr">
+        <is>
+          <t>Erişim</t>
+        </is>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>Mahremiyet: yatak odaları hol/giyinme üzerinden, banyolar odadan veya holden</t>
+        </is>
+      </c>
+      <c r="C18" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>tüm kapı ilişkileri uygun</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="23" t="inlineStr">
+        <is>
+          <t>Gün ışığı</t>
+        </is>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>Yaşama mahalleri (yatak, oturma, mutfak) doğrudan gün ışığı alır; cam ≥ döşeme/10</t>
+        </is>
+      </c>
+      <c r="C19" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>tüm yaşama mahallerinde pencere var</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>Gün ışığı</t>
+        </is>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>Cam oranı 1/8'in altında kalan mahaller</t>
+        </is>
+      </c>
+      <c r="C20" s="35" t="inlineStr">
+        <is>
+          <t>UYARI</t>
+        </is>
+      </c>
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>B-02 Oyun ve bar salonu: cam/döşeme 1/10</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>Gün ışığı</t>
+        </is>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>Penceresiz ıslak hacimler mekanik havalandırma (şafta bağlı aspiratör) ile çözülür</t>
+        </is>
+      </c>
+      <c r="C21" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D21" s="25" t="inlineStr">
+        <is>
+          <t>B-05, B-17, B-18, Z-14, K-13, K-18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>Cephe</t>
+        </is>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>Pencereler kolona, iç duvara ve birbirine çarpmıyor</t>
+        </is>
+      </c>
+      <c r="C22" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D22" s="25" t="inlineStr">
+        <is>
+          <t>tüm pencereler serbest</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>Cephe</t>
+        </is>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>Üst kattaki kapı boyu camlar balkona açılır; pencere denizlikleri ≥ 0,85 m</t>
+        </is>
+      </c>
+      <c r="C23" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D23" s="25" t="inlineStr"/>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="23" t="inlineStr">
+        <is>
+          <t>Taşıyıcı</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>Bodrum: kolonlar duvar içinde / duvar ucunda</t>
+        </is>
+      </c>
+      <c r="C24" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D24" s="25" t="inlineStr">
+        <is>
+          <t>16 kolon</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="23" t="inlineStr">
+        <is>
+          <t>Taşıyıcı</t>
+        </is>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>Zemin: kolonlar duvar içinde / duvar ucunda</t>
+        </is>
+      </c>
+      <c r="C25" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D25" s="25" t="inlineStr">
+        <is>
+          <t>16 kolon</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="23" t="inlineStr">
+        <is>
+          <t>Taşıyıcı</t>
+        </is>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>1. Kat: kolonlar duvar içinde / duvar ucunda</t>
+        </is>
+      </c>
+      <c r="C26" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D26" s="25" t="inlineStr">
+        <is>
+          <t>16 kolon</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="23" t="inlineStr">
+        <is>
+          <t>Taşıyıcı</t>
+        </is>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>En büyük kiriş açıklığı ≤ 8,0 m</t>
+        </is>
+      </c>
+      <c r="C27" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D27" s="25" t="inlineStr">
+        <is>
+          <t>x yönünde 7.60 m · y yönünde 5.00 m (asansör kuyusu betonarme perde)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="23" t="inlineStr">
+        <is>
+          <t>Merdiven</t>
+        </is>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>Bodrum → Zemin: rıht 17.0 cm · basamak 28 cm · 2r+b 62.0 · kol 1.18 m · sahanlık 1.25 m</t>
+        </is>
+      </c>
+      <c r="C28" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D28" s="25" t="inlineStr">
+        <is>
+          <t>18 rıht (9 + 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="23" t="inlineStr">
+        <is>
+          <t>Merdiven</t>
+        </is>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>Zemin → 1. Kat: rıht 16.8 cm · basamak 28 cm · 2r+b 61.7 · kol 1.18 m · sahanlık 1.25 m</t>
+        </is>
+      </c>
+      <c r="C29" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D29" s="25" t="inlineStr">
+        <is>
+          <t>19 rıht (10 + 9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="23" t="inlineStr">
+        <is>
+          <t>Merdiven</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>Kollar kutuya sığar, kuzeyde ≥ 0,90 m varış/çıkış sahanlığı kalır</t>
+        </is>
+      </c>
+      <c r="C30" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D30" s="25" t="inlineStr">
+        <is>
+          <t>varış bandı y 3,20–4.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="23" t="inlineStr">
+        <is>
+          <t>Merdiven</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>Baş yüksekliği ≥ 2,10 m</t>
+        </is>
+      </c>
+      <c r="C31" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D31" s="25" t="inlineStr">
+        <is>
+          <t>üst kol altı ile alt basamak arası ≈ 2.64 m (merdivenler üst üste, aynı kutuda)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="23" t="inlineStr">
+        <is>
+          <t>İmar</t>
+        </is>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>Bina yüksekliği (tabii zeminden saçak döşemesine) ≤ Hmax 6.50 m</t>
+        </is>
+      </c>
+      <c r="C32" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D32" s="25" t="inlineStr">
+        <is>
+          <t>6.50 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="23" t="inlineStr">
+        <is>
+          <t>İmar</t>
+        </is>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>Ebeveyn balkonu konsol derinliği ≤ 1,50 m (açık çıkma)</t>
+        </is>
+      </c>
+      <c r="C33" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D33" s="25" t="inlineStr">
+        <is>
+          <t>1.50 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="23" t="inlineStr">
+        <is>
+          <t>İmar</t>
+        </is>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>Aile balkonu konsol derinliği ≤ 1,50 m (açık çıkma)</t>
+        </is>
+      </c>
+      <c r="C34" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D34" s="25" t="inlineStr">
+        <is>
+          <t>1.50 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="23" t="inlineStr">
+        <is>
+          <t>İmar</t>
+        </is>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>Giriş kapısı saçak altında</t>
+        </is>
+      </c>
+      <c r="C35" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D35" s="25" t="inlineStr">
+        <is>
+          <t>saçak 7.90–12.40 · kapı 8.55–9.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="23" t="inlineStr">
+        <is>
+          <t>İmar</t>
+        </is>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>Garaj 2 araç için yeterli (net ≥ 5,40 × 5,50 m, kapı ≥ 4,60 m)</t>
+        </is>
+      </c>
+      <c r="C36" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D36" s="25" t="inlineStr">
+        <is>
+          <t>net 5.57 × 5.58 m · kapı 4.80 m</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="23" t="inlineStr">
+        <is>
+          <t>Yerleşim</t>
+        </is>
+      </c>
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>Bodrum: mobilyalar duvar, merdiven ve birbirleriyle çakışmıyor</t>
+        </is>
+      </c>
+      <c r="C37" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D37" s="25" t="inlineStr">
+        <is>
+          <t>32 donatı</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="23" t="inlineStr">
+        <is>
+          <t>Yerleşim</t>
+        </is>
+      </c>
+      <c r="B38" s="25" t="inlineStr">
+        <is>
+          <t>Zemin: mobilyalar duvar, merdiven ve birbirleriyle çakışmıyor</t>
+        </is>
+      </c>
+      <c r="C38" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D38" s="25" t="inlineStr">
+        <is>
+          <t>31 donatı</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="22" customHeight="1">
+      <c r="A39" s="23" t="inlineStr">
+        <is>
+          <t>Yerleşim</t>
+        </is>
+      </c>
+      <c r="B39" s="25" t="inlineStr">
+        <is>
+          <t>1. Kat: mobilyalar duvar, merdiven ve birbirleriyle çakışmıyor</t>
+        </is>
+      </c>
+      <c r="C39" s="34" t="inlineStr">
+        <is>
+          <t>UYGUN</t>
+        </is>
+      </c>
+      <c r="D39" s="25" t="inlineStr">
+        <is>
+          <t>47 donatı</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="23" t="inlineStr">
+        <is>
+          <t>Tesisat</t>
+        </is>
+      </c>
+      <c r="B40" s="25" t="inlineStr">
+        <is>
+          <t>Islak hacimler yaşama mahallerinin üstüne gelmiyor (gelenler asma tavanda şafta bağlanır)</t>
+        </is>
+      </c>
+      <c r="C40" s="35" t="inlineStr">
+        <is>
+          <t>UYARI</t>
+        </is>
+      </c>
+      <c r="D40" s="25" t="inlineStr">
+        <is>
+          <t>K-09 Ebeveyn banyosu → altında Z-09 Salon (şömineli); K-13 Yatak odası 4 banyosu → altında Z-10 Yemek alanı; K-19 Aile WC → altında Z-16 Arka mutfak / servis girişi</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:D1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
 </file>